--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,29 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +84,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,11 +98,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -92,6 +133,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2203,4 +2256,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول لینک ESP (EspLink)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>EspLink_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1583,6 +1583,89 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>EL-013</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>کالیبراسیون و read-back</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + لینک فعال</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>از کارت کالیبراسیون ID0..6 را ارسال کن؛ هر مقدار باید بعد از تأیید قبلی فرستاده شود</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>ID0..6؛ مقدار متفاوت</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 20s</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>پس از ریست، NVM</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>هر 7 مقدار read-back برابر؛ پس از حدود 2s و reset مقادیر باقی بماند</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: test_panel_calibration_requires_readback_v127 + NVM ids 0..6؛ برد اجرا نشده</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
@@ -1590,10 +1673,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>
@@ -2046,7 +2129,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -2109,7 +2192,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>IF(12=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/12)</f>
+        <f>IF(13=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/13)</f>
         <v/>
       </c>
       <c r="C17" s="6" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1666,6 +1666,89 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>EL-014</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>LUT readback عددبه‌عدد</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>از پنل قبل از ارسال /lut/read را بزن؛ سپس یک جدول هر دو باتری را push و commit کن؛ بعد از commit و reset دوباره /lut/read را بزن</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>نقاط chainMa و powerMw باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit و پس از LUT_RESET</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>هر ردیف به‌صورت عددی same/changed/mismatch یا unavailable گزارش شود؛ CRC/تعداد جای مقدار را نگیرد</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut 144 check، ESP 112 check، پنل 302 check؛ اجرای برد فیزیکی انجام نشده</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
@@ -1673,10 +1756,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -574,7 +574,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>یادداشت: تست پنل وب سمت ESP (خود برنامهٔ ESP) در این فرم نیست؛ فقط رفتار سمت برد اعتبارسنجی می‌شود.</t>
+          <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد</t>
+          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>هر ردیف به‌صورت عددی same/changed/mismatch یا unavailable گزارش شود؛ CRC/تعداد جای مقدار را نگیرد</t>
+          <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 144 check، ESP 112 check، پنل 302 check؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 307 check؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ host_test_scenario_cards.js</t>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1744,6 +1744,89 @@
       </c>
       <c r="P18" s="4" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>EL-015</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>صفرنقطه و کانال نامعتبر</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>یک کانال معتبر و یک کانال بدون جدول/نامعتبر را pack کن؛ قبل و بعد از commit LUT_READ بگیر</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit و فقط با readback دقیق</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 307 check؛ اجرای برد فیزیکی انجام نشده</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
@@ -1790,6 +1873,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2181,6 +2265,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -2211,8 +2296,10 @@
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>13</v>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -2275,7 +2362,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>IF(13=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/13)</f>
+        <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -2284,6 +2371,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
@@ -2356,6 +2444,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
@@ -2384,6 +2473,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -2445,6 +2535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -16,7 +16,7 @@
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>از پنل قبل از ارسال /lut/read را بزن؛ سپس یک جدول هر دو باتری را push و commit کن؛ بعد از commit و reset دوباره /lut/read را بزن</t>
+          <t>از پنل «خواندن جدول فعلی» را بزن؛ سپس update هر دو باتری را با gain/offset متفاوت اجرا کن؛ بعد از commit و reset دوباره /lut/read و تله‌متری را بزن</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
+          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ gain/offset هر چهار شناسه پیش از LUT با readback تأیید می‌شود؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 307 check؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل preflight و readback gain/offset؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>یک کانال معتبر و یک کانال بدون جدول/نامعتبر را pack کن؛ قبل و بعد از commit LUT_READ بگیر</t>
+          <t>یک update تکی برای باتری ۱ یا ۲ با یک کانال معتبر و یک کانال بدون جدول/نامعتبر اجرا کن؛ قبل و بعد از commit LUT_READ و readback gain/offset بگیر</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است</t>
+          <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 307 check؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل گیت readback و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1873,7 +1873,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2265,7 +2264,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -2371,7 +2369,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
@@ -2444,7 +2441,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
@@ -2473,7 +2469,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -2535,7 +2530,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>از کارت کالیبراسیون ID0..6 را ارسال کن؛ هر مقدار باید بعد از تأیید قبلی فرستاده شود</t>
+          <t>از کارت کالیبراسیون یک batch شامل همهٔ پارامترهای معتبر (ID0..6) را با یک تأیید ارسال کن؛ هر مقدار باید پس از تأیید قبلی فرستاده شود</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>هر 7 مقدار read-back برابر؛ پس از حدود 2s و reset مقادیر باقی بماند</t>
+          <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: test_panel_calibration_requires_readback_v127 + NVM ids 0..6؛ برد اجرا نشده</t>
+          <t>Host PASS: DOM 316 check شامل summary نام‌محور، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>از پنل «خواندن جدول فعلی» را بزن؛ سپس update هر دو باتری را با gain/offset متفاوت اجرا کن؛ بعد از commit و reset دوباره /lut/read و تله‌متری را بزن</t>
+          <t>از پنل «خواندن جدول فعلی» را بزن؛ سپس update هر دو باتری را اجرا کن؛ پارامترهای معتبر کالیبراسیونِ تراکنش (gain/offset باتری هدف + آفست‌های ولتاژ) یک‌جا قبل از LUT اعمال و readback شوند؛ بعد از commit و reset دوباره /lut/read و تله‌متری را بزن</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ gain/offset هر چهار شناسه پیش از LUT با readback تأیید می‌شود؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
+          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل preflight و readback gain/offset؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل گیت readback و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل گیت readback کالیبراسیون، update مستقل و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: DOM 316 check شامل summary نام‌محور، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+          <t>Host PASS: DOM 319 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 319 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، checkbox نمونه‌ها، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 316 check؛ شامل گیت readback کالیبراسیون، update مستقل و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 319 check؛ شامل گیت readback کالیبراسیون، update مستقل، checkbox انتخاب نمونه و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: DOM 319 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+          <t>Host PASS: DOM 322 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 319 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، checkbox نمونه‌ها، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 322 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 319 check؛ شامل گیت readback کالیبراسیون، update مستقل، checkbox انتخاب نمونه و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 322 check؛ شامل گیت readback کالیبراسیون، update مستقل، checkbox انتخاب نمونه و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: DOM 322 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+          <t>Host PASS: DOM 324 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 322 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، modal نام‌محور و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 322 check؛ شامل گیت readback کالیبراسیون، update مستقل، checkbox انتخاب نمونه و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Host PASS: DOM 324 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+          <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1829,6 +1829,89 @@
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>EL-016</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit صفرنقطه‌ای و غیرصفر، با magic/grant معتبر reset را درخواست کن؛ یک بار flush موفق و یک بار با fault تزریق‌شدهٔ NVM اجرا کن</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1839,10 +1922,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>
@@ -1856,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2115,33 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>به‌روزرسانی فونت با /f.css?v=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>magic + commit grant؛ flush NVM پیش از arm</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>flush failure = no reset و grant retained؛ success = reset one-shot</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2406,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -2344,7 +2454,7 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
+        <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
       <c r="C16" s="6" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -16,7 +16,7 @@
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -574,7 +574,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>یادداشت: تست پنل وب سمت ESP (خود برنامهٔ ESP) در این فرم نیست؛ فقط رفتار سمت برد اعتبارسنجی می‌شود.</t>
+          <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1583,6 +1583,338 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>EL-013</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>کالیبراسیون و read-back</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + لینک فعال</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>از کارت کالیبراسیون یک batch شامل همهٔ پارامترهای معتبر (ID0..6) را با یک تأیید ارسال کن؛ هر مقدار باید پس از تأیید قبلی فرستاده شود</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>ID0..6؛ مقدار متفاوت</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 20s</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>پس از ریست، NVM</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>EL-014</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>LUT readback عددبه‌عدد</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>از پنل «خواندن جدول فعلی» را بزن؛ سپس update هر دو باتری را اجرا کن؛ پارامترهای معتبر کالیبراسیونِ تراکنش (gain/offset باتری هدف + آفست‌های ولتاژ) یک‌جا قبل از LUT اعمال و readback شوند؛ بعد از commit و reset دوباره /lut/read و تله‌متری را بزن</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>نقاط chainMa و powerMw باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit و پس از LUT_RESET</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>EL-015</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>صفرنقطه و کانال نامعتبر</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>یک update تکی برای باتری ۱ یا ۲ با یک کانال معتبر و یک کانال بدون جدول/نامعتبر اجرا کن؛ قبل و بعد از commit LUT_READ و readback gain/offset بگیر</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit و فقط با readback دقیق</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>EL-016</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>پس از commit صفرنقطه‌ای و غیرصفر، با magic/grant معتبر reset را درخواست کن؛ یک بار flush موفق و یک بار با fault تزریق‌شدهٔ NVM اجرا کن</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
@@ -1590,10 +1922,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>
@@ -1607,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1783,6 +2115,33 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>به‌روزرسانی فونت با /f.css?v=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>magic + commit grant؛ flush NVM پیش از arm</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>flush failure = no reset و grant retained؛ success = reset one-shot</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
       </c>
     </row>
@@ -2045,8 +2404,10 @@
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>12</v>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -2093,7 +2454,7 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
+        <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2109,7 +2470,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>IF(12=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/12)</f>
+        <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
       <c r="C17" s="6" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>نقاط chainMa و powerMw باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
+          <t>نقاط counts و BatteryMa باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1912,216 @@
       <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EL-017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ alert</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>پنل وصل</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>در پنل یک ورودی نامعتبر وارد کن تا palert/pmAlert فراخوانی شود (مثلا duty خالی یا مولتی‌متر خالی)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ورودی نامعتبر</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>پیام با کادر تیره #121a2c/#35507f همرنگ پنل نمایش داده شود، نه alert سفید ویندوز؛ دکمه باشه بستن</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>دیالوگ تیره + بدون alert پیش‌فرض</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EL-018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ confirm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>پنل وصل</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>دکمه قطع PWM شارژر یا مود دستی یا پاک کردن فایل بنچ را بزن</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>کلیک قطع</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>دیالوگ تأیید با کادر تیره #pmod، دو دکمه تأیید/انصراف، Enter=تأیید Esc=لغو</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Enter تأیید و Esc انصراف + استایل تیره</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EL-019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>صف دیالوگ PMQ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>پنل وصل</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>دو confirm پشت سر هم بساز (مثلا دو بار قطع PWM)؛ رفتار صف را ببین</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>دو درخواست</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>دیالوگ‌ها یکی‌یکی و پشت سر هم با Promise queue نمایش داده شوند، نه روی هم</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>صف</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>بدون همپوشانی دیالوگ</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1971,14 +1971,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -2041,14 +2038,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -2111,17 +2105,86 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EL-020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>قفل ترکیب چشمک سبز در پنل</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>پنل وصل یا پیش‌نمایش پنل</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>دورهٔ چشمک سبز (شناسهٔ ۶۶) را ۱۰۰۰ و حداقل خاموشی سبز (شناسهٔ ۶۷) را ۵۰۰۰ بگذار و «ارسال همه» را بزن؛ بعد دوره را به‌تنهایی ۵۰۰ کن در حالی که خاموشی روی برد ۱۰۰۰۰ است و دوباره بفرست</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>u67 بزرگ‌تر از u66</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ارسال کل دسته متوقف شود؛ دیالوگ قرمز عددهای مؤثر را نشان دهد؛ هیچ درخواستی به برد نرود و صف دست‌نخورده بماند</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ترکیب نامعتبر هرگز به برد نمی‌رسد و ترکیب سالم (خاموشی ≤ دوره) بدون مانع ارسال می‌شود</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>8efddaa</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -754,7 +754,10 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>بوت برد بدون MODULE_ESP؛ سپس فعال‌سازی</t>
+          <t>گام ۱: برد را بدون ماژول ESP (MODULE_ESP خاموش) بوت کن.
+گام ۲: 5 ثانیه صبر کن: ESP باید خاموش بماند تا وقتی Power آن high شود.
+گام ۳: ماژول ESP را فعال کن.
+گام ۴: ESP باید روشن شود، لینک بالا بیاید و پنل آنلاین شود.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -825,7 +828,9 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>فریم‌های TLM_LIVE را در پنل ببین (seq)</t>
+          <t>گام ۱: لینک ESP را فعال کن و پنل را باز کن.
+گام ۲: 5 ثانیه فریم‌های زنده (TLM_LIVE) را نگاه کن.
+گام ۳: هر فریم باید 84 بایت باشد، تقریباً هر 100 میلی‌ثانیه بیاید، XOR آن درست باشد و شمارهٔ ترتیب (seq) همیشه در حال افزایش باشد.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -896,7 +901,10 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>از پنل یک پارامتر تغییر بده تا GET/BULK ردوبدل شود؛ یا ری‌استارت ESP</t>
+          <t>گام ۱: لینک فعال باشد و پنل باز باشد.
+گام ۲: از پنل یک پارامتر را تغییر بده تا تبادل GET/BULK اتفاق بیفتد (یا ESP را ری‌استارت کن).
+گام ۳: پاسخ BULK را بررسی کن: باید 20 پارامتر با payload برابر 101 بایت (حداکثر 112) برگردد.
+گام ۴: جدول پارامترهای پنل باید کامل پر شده باشد و هر 20 مقدار معلوم باشند.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -967,7 +975,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>یک پارامتر عددی از پنل ثبت کن</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: پارامتر شناسهٔ 2 را روی 1200 بگذار و ارسال کن.
+گام ۳: حداکثر 2 ثانیه صبر کن تا گزارش برگردد.
+گام ۴: مقدار اعمال‌شده (applied) در گزارش PARAM_REPORT باید 1200 نشان داده شود، یعنی مقدار در مرز تسک clamp و همان اعمال شده است.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1038,7 +1049,9 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ID19=1 با تأیید؛ سپس قطع لینک</t>
+          <t>گام ۱: پنل را وصل کن و پارامتر 19 را روی 1 بگذار (با تأیید) تا مود دستی فعال شود؛ وضعیت باید 9 شود.
+گام ۲: لینک را قطع کن و 10 ثانیه صبر کن.
+گام ۳: بعد از 3 ثانیه سکوت لینک، خروج خودکار باید اتفاق بیفتد و duty هر دو کانال حداکثر تا 3 ثانیه صفر شده باشد.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1109,7 +1122,10 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>به‌جای GET، فقط SET_PARAM بفرست (تغییر پیوستهٔ duty)</t>
+          <t>گام ۱: وارد مود دستی شو (پارامتر 19 = 1).
+گام ۲: به‌جای GET، فقط پشت سر هم SET_PARAM بفرست و duty را پیوسته تغییر بده (10 ثانیه).
+گام ۳: هر فریم معتبر باید ددمن مود دستی را refresh کند.
+گام ۴: در این 10 ثانیه نباید از مود دستی خارج شود.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1180,7 +1196,10 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ارسال بی‌سروصدا از سمت ESP (بیش از بافر)</t>
+          <t>گام ۱: لینک فعال باشد.
+گام ۲: از سمت ESP بیش از گنجایش بافر UART، دادهٔ اضافه بفرست (burst).
+گام ۳: 5 ثانیه نگاه کن: فریم اضافه باید رد شود و پارسر با SOF بعدی دوباره sync شود.
+گام ۴: تله‌متری باید بعد از burst بدون هیچ گیری ادامه پیدا کند.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1251,7 +1270,10 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>بیش از 250 بایت در 100ms از ESP بفرست</t>
+          <t>گام ۱: لینک فعال باشد.
+گام ۲: از سمت ESP بیش از 250 بایت در 100 میلی‌ثانیه بفرست (burst سنگین).
+گام ۳: 5 ثانیه لینک را زیر نظر بگیر: فریم‌های خارج از سقف باید رد شوند.
+گام ۴: لینک باید پایدار بماند؛ نه قفل کند نه ریست شود.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1322,7 +1344,9 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>شکل‌موج و باد را ببین</t>
+          <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
+گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
+گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1393,7 +1417,10 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>b0/b1/b2/b3/b4/b5 را با تغییر شرایط چک کن</t>
+          <t>گام ۱: پنل را باز کن و ردیف بیت‌های وضعیت (b0 تا b5) را پیدا کن.
+گام ۲: شرایط را یکی‌یکی تغییر بده: ورودی را قطع و وصل کن، وارد مود دستی شو و خارج شو (10 ثانیه).
+گام ۳: هر بیت را با وضعیت واقعی مقایسه کن: snapshot معتبر، ورودی حاضر، اعتبار کلی، کانال ۱، کانال ۲ و مود دستی.
+گام ۴: همهٔ برچسب‌ها باید در هر لحظه درست باشند.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1464,7 +1491,10 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>state هر دو کانال + برچسب مود در پنل</t>
+          <t>گام ۱: پارامتر 19 را روی 1 بگذار تا وارد مود دستی شوی.
+گام ۲: در پنل وضعیت هر دو کانال و برچسب مود را نگاه کن (5 ثانیه).
+گام ۳: هر دو کانال باید وضعیت 9 و بیت b5 برابر 1 باشند و پنل «مود دستی» نشان دهد.
+گام ۴: حین مود دستی بیت FAULT_CHARGER_BAT_LOST باید پاک بماند.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1535,7 +1565,10 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>فقط MODULE_ESP=1 کن و بیلد بگیر</t>
+          <t>گام ۱: بیلد را با MODULE_ESP=0 بگیر و رفتار عادی برد را یک بار ببین.
+گام ۲: فقط MODULE_ESP را 1 کن و دوباره بیلد بگیر (هیچ تغییر دیگری نده).
+گام ۳: برد را بوت کن (60 ثانیه).
+گام ۴: لینک باید بدون دست‌کاری بقیهٔ ماژول‌ها بالا بیاید و پنل آنلاین شود.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1606,7 +1639,11 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>از کارت کالیبراسیون یک batch شامل همهٔ پارامترهای معتبر (ID0..6) را با یک تأیید ارسال کن؛ هر مقدار باید پس از تأیید قبلی فرستاده شود</t>
+          <t>گام ۱: فرم‌ور جدید روی برد و لینک فعال باشد؛ کارت کالیبراسیون پنل را باز کن.
+گام ۲: یک دسته (batch) شامل همهٔ پارامترهای معتبر (شناسه‌های 0 تا 6) با مقادیر متفاوت از فعلی بساز و با یک تأیید ارسال کن.
+گام ۳: جواب HTTP 200 فقط یعنی «در صف است»، موفقیت نیست؛ صبر کن گزارش PARAM_REPORT/PARAMS_BULK برگردد (حداکثر 20 ثانیه).
+گام ۴: هر 7 مقدار را با read-back مقایسه کن: فقط وقتی هرکدام عیناً برابر بود و وضعیتش unchanged/changed-confirmed شد قبول است.
+گام ۵: حدود 2 ثانیه صبر کن، برد را reset کن و دوباره بخوان؛ مقادیر باید باقی مانده باشند.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1689,7 +1726,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>از پنل «خواندن جدول فعلی» را بزن؛ سپس update هر دو باتری را اجرا کن؛ پارامترهای معتبر کالیبراسیونِ تراکنش (gain/offset باتری هدف + آفست‌های ولتاژ) یک‌جا قبل از LUT اعمال و readback شوند؛ بعد از commit و reset دوباره /lut/read و تله‌متری را بزن</t>
+          <t>گام ۱: فرم‌ور جدید STM32 و ESP روی برد باشد و یک جدول فعال داشته باشی (یا بتوانی push کنی).
+گام ۲: در پنل «خواندن جدول فعلی» را بزن؛ STM32 باید برای هر دو کانال LUT_DATA واقعی بفرستد و پنل ستون «فعلی» را نشان دهد.
+گام ۳: update هر دو باتری را اجرا کن: اول پارامترهای معتبر کالیبراسیون تراکنش (gain/offset باتری هدف و آفست‌های ولتاژ) یک‌جا اعمال و read-back شوند، بعد LUT.
+گام ۴: در باتری ۲ عمداً یک نقطه را متفاوت بگذار.
+گام ۵: بعد از commit و reset دوباره /lut/read و تله‌متری را بزن (حداکثر 15 ثانیه): هر ردیف باید unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata هستند و باتری ۲ باید مستقل مقایسه شود.
+گام ۶: صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1772,7 +1814,11 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>یک update تکی برای باتری ۱ یا ۲ با یک کانال معتبر و یک کانال بدون جدول/نامعتبر اجرا کن؛ قبل و بعد از commit LUT_READ و readback gain/offset بگیر</t>
+          <t>گام ۱: فرم‌ور جدید باشد و در خواندن قبلی یک override غیرصفر داشته باشی؛ مقادیر before را یادداشت کن.
+گام ۲: یک update تکی برای باتری ۱ یا ۲ اجرا کن که یک کانالش معتبر و کانال دیگرش بدون جدول یا نامعتبر باشد؛ proposed کانال هدف را صفر بگذار.
+گام ۳: قبل و بعد از commit، LUT_READ و readback gain/offset بگیر (حداکثر 15 ثانیه).
+گام ۴: حذف override باید changed-confirmed دیده شود؛ نقطهٔ اضافه mismatch و readback ناقص failure است و در این حالت‌ها reset نباید پیشنهاد شود.
+گام ۵: هر دو فریم باتری باید مستقل بمانند و خطای gain/offset پیش از POST /lut جلوی ارسال جدول را بگیرد.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1855,7 +1901,11 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>پس از commit صفرنقطه‌ای و غیرصفر، با magic/grant معتبر reset را درخواست کن؛ یک بار flush موفق و یک بار با fault تزریق‌شدهٔ NVM اجرا کن</t>
+          <t>گام ۱: فرم‌ور جدید، یک commit موفق کالیبراسیون/LUT و لینک فعال داشته باش.
+گام ۲: بعد از commit (هم صفرنقطه‌ای با n1=n2=0 و هم با جدول فعال) با magic و grant معتبر reset درخواست کن.
+گام ۳: یک بار flush موفق NVM و یک بار flush با خطای تزریق‌شده اجرا کن (حداکثر 15 ثانیه).
+گام ۴: در flush موفق برد باید reset شود و بعد از بالا آمدن، /t تازه و LUT readback هر دو کانال برابر انتظار باشد.
+گام ۵: در flush ناموفق باید پاسخ CAL_LUT_ST_FLASH بیاید و reset انجام نشود؛ timeout، mismatch یا reject هرگز موفقیت حساب نمی‌شود.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1938,7 +1988,10 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>در پنل یک ورودی نامعتبر وارد کن تا palert/pmAlert فراخوانی شود (مثلا duty خالی یا مولتی‌متر خالی)</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: در پنل یک ورودی نامعتبر وارد کن (مثلاً duty را خالی بگذار یا مولتی‌متر را خالی ارسال کن) تا پیام خطا (palert) بیاید.
+گام ۳: پیام باید با کادر تیرهٔ همرنگ پنل (#121a2c/#35507f) بیاید، نه alert سفید پیش‌فرض ویندوز، و دکمهٔ «باشه» برای بستن داشته باشد.
+گام ۴: روی برد واقعی هم یک بار همین را تکرار کن (3 ثانیه کافی است).</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2005,7 +2058,10 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>دکمه قطع PWM شارژر یا مود دستی یا پاک کردن فایل بنچ را بزن</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: یکی از این‌ها را بزن: دکمهٔ قطع PWM شارژر، ورود به مود دستی، یا پاک کردن فایل بنچ.
+گام ۳: دیالوگ تأیید باید با کادر تیره (#pmod) و دو دکمهٔ تأیید/انصراف بیاید.
+گام ۴: یک بار Enter بزن (باید تأیید کند) و در اجرای بعدی Esc (باید لغو کند).</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2072,7 +2128,10 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>دو confirm پشت سر هم بساز (مثلا دو بار قطع PWM)؛ رفتار صف را ببین</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: دو تأیید پشت سر هم بساز (مثلاً دو بار دکمهٔ قطع PWM را بزن).
+گام ۳: 5 ثانیه نگاه کن: دیالوگ‌ها باید یکی‌یکی و به نوبت (صف Promise) نمایش داده شوند.
+گام ۴: هیچ‌وقت نباید دو دیالوگ روی هم بیفتند.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2139,7 +2198,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>دورهٔ چشمک سبز (شناسهٔ ۶۶) را ۱۰۰۰ و حداقل خاموشی سبز (شناسهٔ ۶۷) را ۵۰۰۰ بگذار و «ارسال همه» را بزن؛ بعد دوره را به‌تنهایی ۵۰۰ کن در حالی که خاموشی روی برد ۱۰۰۰۰ است و دوباره بفرست</t>
+          <t>گام ۱: پنل (یا پیش‌نمایش پنل) را باز کن و به بخش چشمک سبز برو.
+گام ۲: دورهٔ چشمک سبز (شناسهٔ 66) را 1000 و حداقل خاموشی سبز (شناسهٔ 67) را 5000 بگذار و دکمهٔ «ارسال همه» را بزن.
+گام ۳: باید ارسال کل دسته متوقف شود و یک دیالوگ قرمز، عددهای مؤثر (دوره 1000، خاموشی 5000) را نشان دهد؛ هیچ درخواستی نباید به برد برود و صف تغییرات دست‌نخورده بماند.
+گام ۴: حالا خاموشی روی برد را 10000 نگه دار و فقط دوره را به‌تنهایی 500 کن و دوباره «ارسال همه» را بزن؛ باز هم باید متوقف شود.
+گام ۵: در پایان یک ترکیب سالم بفرست (خاموشی کمتر یا مساوی دوره، مثلاً دوره 5000 و خاموشی 500)؛ باید بدون هیچ مانعی ارسال شود.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +71,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +153,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,11 +196,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +286,88 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -517,21 +742,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول EspLink</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EspLink | پل UART 921600 8N1 با DMA دوطرفه؛ پروتکل v1.2 (SET_PARAM/GET_PARAMS/TLM_LIVE/PARAM_REPORT/PARAMS_BULK) + مود تست دستی ID19</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -541,21 +766,21 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>فعال‌سازی با MODULE_ESP=1 (فقط همان یک خط)؛ CH_PD از PA8 توسط برد کنترل می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>قرارداد کامل در ESP_AGENT_SPEC.md v1.2؛ محدودیت‌های سمت ESP در README همین ماژول.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>پنل وب سمت ESP در esp_link_panel/ (ممیزی خط‌به‌خط، کامیت 32098b4).</t>
         </is>
@@ -565,14 +790,14 @@
       <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>هشدار: تست‌های مود دستی فقط با بار ایمن (electronic load با clamp) و منبع محدودشده.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
         </is>
@@ -591,6 +816,9 @@
     <mergeCell ref="A5"/>
     <mergeCell ref="A1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -598,161 +826,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول EspLink</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>EL-001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>CH_PD و بوت</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>گام ۱: برد را بدون ماژول ESP (MODULE_ESP خاموش) بوت کن.
 گام ۲: 5 ثانیه صبر کن: ESP باید خاموش بماند تا وقتی Power آن high شود.
@@ -760,146 +989,146 @@
 گام ۴: ESP باید روشن شود، لینک بالا بیاید و پنل آنلاین شود.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>ESP تا Power(high) خاموش می‌ماند؛ با فعال‌سازی روشن و لینک بالا می‌آید</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>پنل آنلاین بعد از فعال‌سازی</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr"/>
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>EL-002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>تله‌متری زنده</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>لینک فعال</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را فعال کن و پنل را باز کن.
 گام ۲: 5 ثانیه فریم‌های زنده (TLM_LIVE) را نگاه کن.
 گام ۳: هر فریم باید 84 بایت باشد، تقریباً هر 100 میلی‌ثانیه بیاید، XOR آن درست باشد و شمارهٔ ترتیب (seq) همیشه در حال افزایش باشد.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>فریم 84B هر ~100ms با XOR درست؛ seq صعودی</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>پیوسته</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>seq در حال افزایش</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EL-003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>GET_PARAMS → BULK</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>لینک فعال</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>گام ۱: لینک فعال باشد و پنل باز باشد.
 گام ۲: از پنل یک پارامتر را تغییر بده تا تبادل GET/BULK اتفاق بیفتد (یا ESP را ری‌استارت کن).
@@ -907,73 +1136,73 @@
 گام ۴: جدول پارامترهای پنل باید کامل پر شده باشد و هر 20 مقدار معلوم باشند.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>BULK با ۲۰ پارامتر (payload 101B ≤ 112)؛ جدول پنل پر می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>همهٔ ۲۰ پارامتر معلوم</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>EL-004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>SET_PARAM → REPORT</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>لینک فعال</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: پارامتر شناسهٔ 2 را روی 1200 بگذار و ارسال کن.
@@ -981,146 +1210,146 @@
 گام ۴: مقدار اعمال‌شده (applied) در گزارش PARAM_REPORT باید 1200 نشان داده شود، یعنی مقدار در مرز تسک clamp و همان اعمال شده است.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>ID2=1200</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>کلمپ در مرز تسک + PARAM_REPORT مقدار اعمال‌شده</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>نمایش applied=1200</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>EL-005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>پارامتر ۱۹ مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و پارامتر 19 را روی 1 بگذار (با تأیید) تا مود دستی فعال شود؛ وضعیت باید 9 شود.
 گام ۲: لینک را قطع کن و 10 ثانیه صبر کن.
 گام ۳: بعد از 3 ثانیه سکوت لینک، خروج خودکار باید اتفاق بیفتد و duty هر دو کانال حداکثر تا 3 ثانیه صفر شده باشد.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>ID19=1</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>ورود مود دستی (state=9، b5)؛ ۳s سکوت → خروج خودکار با duty صفر</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>ددمن فعال</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>duty=0 در ≤3s</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>EL-006</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>تغذیه ددمن با هر فریم</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>گام ۱: وارد مود دستی شو (پارامتر 19 = 1).
 گام ۲: به‌جای GET، فقط پشت سر هم SET_PARAM بفرست و duty را پیوسته تغییر بده (10 ثانیه).
@@ -1128,73 +1357,73 @@
 گام ۴: در این 10 ثانیه نباید از مود دستی خارج شود.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>فرستادن مکرر SET</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>ددمن با هر فریم معتبر refresh می‌شود؛ مود دستی زنده می‌ماند</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>خروج از مود رخ نمی‌دهد</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>EL-007</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>سرریز ring</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>لینک فعال</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>گام ۱: لینک فعال باشد.
 گام ۲: از سمت ESP بیش از گنجایش بافر UART، دادهٔ اضافه بفرست (burst).
@@ -1202,73 +1431,73 @@
 گام ۴: تله‌متری باید بعد از burst بدون هیچ گیری ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>باست از UART</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>فریم اضافه رد؛ پارسر با SOF مجدد sync می‌شود؛ هیچ گیری نیست</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>تله‌متری بعد از burst ادامه می‌یابد</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>EL-008</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>محدودیت burst</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>لینک فعال</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>گام ۱: لینک فعال باشد.
 گام ۲: از سمت ESP بیش از 250 بایت در 100 میلی‌ثانیه بفرست (burst سنگین).
@@ -1276,146 +1505,146 @@
 گام ۴: لینک باید پایدار بماند؛ نه قفل کند نه ریست شود.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>burst</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>فریم‌های خارج از سقف رد می‌شوند؛ لینک پایدار</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>بدون قفل/ریست</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr"/>
+      <c r="N12" s="22" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="40.5" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>EL-009</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>فیزیکال 921600</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>اسکوپ روی PA9/PA10</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
 گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
 گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>921600 8N1 با درام DDR و بدون خطا</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>بدون فریم خراب در 60s</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>EL-010</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>فلگ‌های تله‌متری</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>پنل باز</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را باز کن و ردیف بیت‌های وضعیت (b0 تا b5) را پیدا کن.
 گام ۲: شرایط را یکی‌یکی تغییر بده: ورودی را قطع و وصل کن، وارد مود دستی شو و خارج شو (10 ثانیه).
@@ -1423,73 +1652,73 @@
 گام ۴: همهٔ برچسب‌ها باید در هر لحظه درست باشند.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>ورودی قطع/وصل، مود دستی</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>هر بیت مطابق وضعیت واقعی: snapshot/ورودی/معتبر/کانال۱/کانال۲/دستی</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>همهٔ برچسب‌ها درست</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="22" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr"/>
+      <c r="Q14" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>EL-011</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>state 9 و b5</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>ورود مود دستی</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پارامتر 19 را روی 1 بگذار تا وارد مود دستی شوی.
 گام ۲: در پنل وضعیت هر دو کانال و برچسب مود را نگاه کن (5 ثانیه).
@@ -1497,73 +1726,73 @@
 گام ۴: حین مود دستی بیت FAULT_CHARGER_BAT_LOST باید پاک بماند.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>ID19=1</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>state=9 و b5=1؛ حین مود بیت BAT_LOST پاک</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>پنل «مود دستی» نشان دهد</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>EL-012</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>فعال‌سازی یک‌خطی</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>MODULE_ESP=0</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>گام ۱: بیلد را با MODULE_ESP=0 بگیر و رفتار عادی برد را یک بار ببین.
 گام ۲: فقط MODULE_ESP را 1 کن و دوباره بیلد بگیر (هیچ تغییر دیگری نده).
@@ -1571,73 +1800,73 @@
 گام ۴: لینک باید بدون دست‌کاری بقیهٔ ماژول‌ها بالا بیاید و پنل آنلاین شود.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>لینک بدون هیچ تغییر دیگر بالا می‌آید؛ سایر ماژول‌ها دست‌نخورده</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>پنل آنلاین</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr"/>
+      <c r="N16" s="22" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="67.5" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>EL-013</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>کالیبراسیون و read-back</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + لینک فعال</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید روی برد و لینک فعال باشد؛ کارت کالیبراسیون پنل را باز کن.
 گام ۲: یک دسته (batch) شامل همهٔ پارامترهای معتبر (شناسه‌های 0 تا 6) با مقادیر متفاوت از فعلی بساز و با یک تأیید ارسال کن.
@@ -1646,85 +1875,85 @@
 گام ۵: حدود 2 ثانیه صبر کن، برد را reset کن و دوباره بخوان؛ مقادیر باید باقی مانده باشند.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>ID0..6؛ مقدار متفاوت</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>حداکثر 20s</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>پس از ریست، NVM</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="41" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="P17" s="19" t="inlineStr"/>
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید STM32 و ESP روی برد باشد و یک جدول فعال داشته باشی (یا بتوانی push کنی).
 گام ۲: در پنل «خواندن جدول فعلی» را بزن؛ STM32 باید برای هر دو کانال LUT_DATA واقعی بفرستد و پنل ستون «فعلی» را نشان دهد.
@@ -1734,85 +1963,85 @@
 گام ۶: صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>نقاط counts و BatteryMa باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>پس از commit و پس از LUT_RESET</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="P18" s="24" t="inlineStr"/>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید باشد و در خواندن قبلی یک override غیرصفر داشته باشی؛ مقادیر before را یادداشت کن.
 گام ۲: یک update تکی برای باتری ۱ یا ۲ اجرا کن که یک کانالش معتبر و کانال دیگرش بدون جدول یا نامعتبر باشد؛ proposed کانال هدف را صفر بگذار.
@@ -1821,85 +2050,85 @@
 گام ۵: هر دو فریم باتری باید مستقل بمانند و خطای gain/offset پیش از POST /lut جلوی ارسال جدول را بگیرد.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>پس از commit و فقط با readback دقیق</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="P19" s="19" t="n"/>
+      <c r="Q19" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید، یک commit موفق کالیبراسیون/LUT و لینک فعال داشته باش.
 گام ۲: بعد از commit (هم صفرنقطه‌ای با n1=n2=0 و هم با جدول فعال) با magic و grant معتبر reset درخواست کن.
@@ -1908,85 +2137,85 @@
 گام ۵: در flush ناموفق باید پاسخ CAL_LUT_ST_FLASH بیاید و reset انجام نشود؛ timeout، mismatch یا reject هرگز موفقیت حساب نمی‌شود.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="25" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: در پنل یک ورودی نامعتبر وارد کن (مثلاً duty را خالی بگذار یا مولتی‌متر را خالی ارسال کن) تا پیام خطا (palert) بیاید.
@@ -1994,69 +2223,73 @@
 گام ۴: روی برد واقعی هم یک بار همین را تکرار کن (3 ثانیه کافی است).</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>ورودی نامعتبر</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>پیام با کادر تیره #121a2c/#35507f همرنگ پنل نمایش داده شود، نه alert سفید ویندوز؛ دکمه باشه بستن</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>دیالوگ تیره + بدون alert پیش‌فرض</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: یکی از این‌ها را بزن: دکمهٔ قطع PWM شارژر، ورود به مود دستی، یا پاک کردن فایل بنچ.
@@ -2064,69 +2297,73 @@
 گام ۴: یک بار Enter بزن (باید تأیید کند) و در اجرای بعدی Esc (باید لغو کند).</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>کلیک قطع</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>دیالوگ تأیید با کادر تیره #pmod، دو دکمه تأیید/انصراف، Enter=تأیید Esc=لغو</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>Enter تأیید و Esc انصراف + استایل تیره</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: دو تأیید پشت سر هم بساز (مثلاً دو بار دکمهٔ قطع PWM را بزن).
@@ -2134,69 +2371,73 @@
 گام ۴: هیچ‌وقت نباید دو دیالوگ روی هم بیفتند.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>دو درخواست</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>دیالوگ‌ها یکی‌یکی و پشت سر هم با Promise queue نمایش داده شوند، نه روی هم</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>صف</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>بدون همپوشانی دیالوگ</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" s="17" t="n"/>
+      <c r="L23" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="67.5" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>EL-020</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>قفل ترکیب چشمک سبز در پنل</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>پنل وصل یا پیش‌نمایش پنل</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل (یا پیش‌نمایش پنل) را باز کن و به بخش چشمک سبز برو.
 گام ۲: دورهٔ چشمک سبز (شناسهٔ 66) را 1000 و حداقل خاموشی سبز (شناسهٔ 67) را 5000 بگذار و دکمهٔ «ارسال همه» را بزن.
@@ -2205,73 +2446,325 @@
 گام ۵: در پایان یک ترکیب سالم بفرست (خاموشی کمتر یا مساوی دوره، مثلاً دوره 5000 و خاموشی 500)؛ باید بدون هیچ مانعی ارسال شود.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>u67 بزرگ‌تر از u66</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>ارسال کل دسته متوقف شود؛ دیالوگ قرمز عددهای مؤثر را نشان دهد؛ هیچ درخواستی به برد نرود و صف دست‌نخورده بماند</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>ترکیب نامعتبر هرگز به برد نمی‌رسد و ترکیب سالم (خاموشی ≤ دوره) بدون مانع ارسال می‌شود</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>8efddaa</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="Q25" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="27">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="27">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="27">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="27">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="27">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="27">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="27">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="27">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="27">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="27">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="27">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="27">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="27">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="27">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="27">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="27">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="27">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="27">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="27">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="27">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="27">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="27">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="27">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="27">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="27">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="27">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="27">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="27">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="27">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="27">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="27">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="27">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="27">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="27">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="27">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="27">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="27">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Q63" s="27">
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Q64" s="27">
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q24"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2285,197 +2778,202 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول EspLink</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="39" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>سرعت لینک</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>921600 8N1، DMA دوطرفه</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>بدون بار CPU</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>bsp_uart.c</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>پروتکل v1.2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>فریم</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>AA 55 type len payload XOR، payload≤112</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>TLM=84B، BULK=101B</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>ESP_AGENT_SPEC.md §2</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>اندیان کوچک</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>ددمن مود دستی</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>هر فریم معتبر، سقف 3s سکوت</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>خروج خودکار + duty صفر</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>CHG_MANUAL_WATCHDOG_MS</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>keepalive پنل = 1s</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>پارامترها</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>ID0..19 فقط RAM</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>کلمپ + PARAM_REPORT</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>README محدودیت‌های سمت ESP</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>ری‌استارت → پیش‌فرض</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>پنل</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>esp_link_panel/ نسخهٔ ممیزی 32098b4</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>keepalive مستقل از مرورگر + محافظ پنل بسته 10s</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>README EspLink</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>به‌روزرسانی فونت با /f.css?v=2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>magic + commit grant؛ flush NVM پیش از arm</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>flush failure = no reset و grant retained؛ success = reset one-shot</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
@@ -2485,6 +2983,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2492,6 +2995,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2514,81 +3018,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول EspLink</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="38" t="n"/>
+      <c r="G2" s="38" t="n"/>
+      <c r="H2" s="38" t="n"/>
+      <c r="I2" s="38" t="n"/>
+      <c r="J2" s="38" t="n"/>
+      <c r="K2" s="38" t="n"/>
+      <c r="L2" s="38" t="n"/>
+      <c r="M2" s="39" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="28" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2606,6 +3122,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2618,205 +3135,207 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول EspLink</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>EspLink — پل ESP و پروتکل v1.2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — پوشش v1.2)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>پنل ESP + اسکوپ + مانیتور UART</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="31">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="31">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="31">
         <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="31">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -2835,6 +3354,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2846,105 +3366,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -2958,7 +3486,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2970,55 +3498,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول لینک ESP (EspLink)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>EspLink_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -3031,6 +3560,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001" forceFullCalc="1"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,13 @@
       <name val="Tahoma"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -258,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -368,6 +378,13 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1774,99 +1791,25 @@
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>EL-012</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>فعال‌سازی یک‌خطی</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+          <t>EL-013</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>کالیبراسیون و read-back</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>MODULE_ESP=0</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: بیلد را با MODULE_ESP=0 بگیر و رفتار عادی برد را یک بار ببین.
-گام ۲: فقط MODULE_ESP را 1 کن و دوباره بیلد بگیر (هیچ تغییر دیگری نده).
-گام ۳: برد را بوت کن (60 ثانیه).
-گام ۴: لینک باید بدون دست‌کاری بقیهٔ ماژول‌ها بالا بیاید و پنل آنلاین شود.</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>لینک بدون هیچ تغییر دیگر بالا می‌آید؛ سایر ماژول‌ها دست‌نخورده</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
-        <is>
-          <t>پنل آنلاین</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr"/>
-      <c r="N16" s="22" t="inlineStr"/>
-      <c r="O16" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="24" t="inlineStr"/>
-      <c r="Q16" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="67.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>EL-013</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>کالیبراسیون و read-back</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + لینک فعال</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید روی برد و لینک فعال باشد؛ کارت کالیبراسیون پنل را باز کن.
 گام ۲: یک دسته (batch) شامل همهٔ پارامترهای معتبر (شناسه‌های 0 تا 6) با مقادیر متفاوت از فعلی بساز و با یک تأیید ارسال کن.
@@ -1875,85 +1818,85 @@
 گام ۵: حدود 2 ثانیه صبر کن، برد را reset کن و دوباره بخوان؛ مقادیر باید باقی مانده باشند.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>ID0..6؛ مقدار متفاوت</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>حداکثر 20s</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>پس از ریست، NVM</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
         </is>
       </c>
-      <c r="N17" s="41" t="inlineStr">
+      <c r="N16" s="41" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O17" s="19" t="inlineStr">
+      <c r="O16" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P17" s="19" t="inlineStr"/>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="P16" s="19" t="inlineStr"/>
+      <c r="Q16" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="81" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="17" ht="67.5" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید STM32 و ESP روی برد باشد و یک جدول فعال داشته باشی (یا بتوانی push کنی).
 گام ۲: در پنل «خواندن جدول فعلی» را بزن؛ STM32 باید برای هر دو کانال LUT_DATA واقعی بفرستد و پنل ستون «فعلی» را نشان دهد.
@@ -1963,85 +1906,85 @@
 گام ۶: صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>نقاط counts و BatteryMa باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>پس از commit و پس از LUT_RESET</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N18" s="42" t="inlineStr">
+      <c r="N17" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr"/>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="P17" s="24" t="inlineStr"/>
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید باشد و در خواندن قبلی یک override غیرصفر داشته باشی؛ مقادیر before را یادداشت کن.
 گام ۲: یک update تکی برای باتری ۱ یا ۲ اجرا کن که یک کانالش معتبر و کانال دیگرش بدون جدول یا نامعتبر باشد؛ proposed کانال هدف را صفر بگذار.
@@ -2050,85 +1993,85 @@
 گام ۵: هر دو فریم باتری باید مستقل بمانند و خطای gain/offset پیش از POST /lut جلوی ارسال جدول را بگیرد.</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>پس از commit و فقط با readback دقیق</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
         </is>
       </c>
-      <c r="N19" s="41" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr">
+      <c r="O18" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P19" s="19" t="n"/>
-      <c r="Q19" s="21" t="inlineStr">
+      <c r="P18" s="19" t="n"/>
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید، یک commit موفق کالیبراسیون/LUT و لینک فعال داشته باش.
 گام ۲: بعد از commit (هم صفرنقطه‌ای با n1=n2=0 و هم با جدول فعال) با magic و grant معتبر reset درخواست کن.
@@ -2137,85 +2080,85 @@
 گام ۵: در flush ناموفق باید پاسخ CAL_LUT_ST_FLASH بیاید و reset انجام نشود؛ timeout، mismatch یا reject هرگز موفقیت حساب نمی‌شود.</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
         </is>
       </c>
-      <c r="N20" s="42" t="inlineStr">
+      <c r="N19" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="25" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: در پنل یک ورودی نامعتبر وارد کن (مثلاً duty را خالی بگذار یا مولتی‌متر را خالی ارسال کن) تا پیام خطا (palert) بیاید.
@@ -2223,73 +2166,77 @@
 گام ۴: روی برد واقعی هم یک بار همین را تکرار کن (3 ثانیه کافی است).</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>ورودی نامعتبر</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>پیام با کادر تیره #121a2c/#35507f همرنگ پنل نمایش داده شود، نه alert سفید ویندوز؛ دکمه باشه بستن</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>دیالوگ تیره + بدون alert پیش‌فرض</t>
         </is>
       </c>
-      <c r="K21" s="17" t="n"/>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" s="19" t="n"/>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="P20" s="19" t="n"/>
+      <c r="Q20" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: یکی از این‌ها را بزن: دکمهٔ قطع PWM شارژر، ورود به مود دستی، یا پاک کردن فایل بنچ.
@@ -2297,73 +2244,73 @@
 گام ۴: یک بار Enter بزن (باید تأیید کند) و در اجرای بعدی Esc (باید لغو کند).</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>کلیک قطع</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>دیالوگ تأیید با کادر تیره #pmod، دو دکمه تأیید/انصراف، Enter=تأیید Esc=لغو</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>Enter تأیید و Esc انصراف + استایل تیره</t>
         </is>
       </c>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M22" s="22" t="n"/>
-      <c r="N22" s="22" t="n"/>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: دو تأیید پشت سر هم بساز (مثلاً دو بار دکمهٔ قطع PWM را بزن).
@@ -2371,73 +2318,73 @@
 گام ۴: هیچ‌وقت نباید دو دیالوگ روی هم بیفتند.</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>دو درخواست</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>دیالوگ‌ها یکی‌یکی و پشت سر هم با Promise queue نمایش داده شوند، نه روی هم</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>صف</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>بدون همپوشانی دیالوگ</t>
         </is>
       </c>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="K22" s="17" t="n"/>
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M23" s="17" t="n"/>
-      <c r="N23" s="17" t="n"/>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="M22" s="17" t="n"/>
+      <c r="N22" s="17" t="n"/>
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P23" s="19" t="n"/>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="P22" s="19" t="n"/>
+      <c r="Q22" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="67.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>EL-020</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>قفل ترکیب چشمک سبز در پنل</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>پنل وصل یا پیش‌نمایش پنل</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل (یا پیش‌نمایش پنل) را باز کن و به بخش چشمک سبز برو.
 گام ۲: دورهٔ چشمک سبز (شناسهٔ 66) را 1000 و حداقل خاموشی سبز (شناسهٔ 67) را 5000 بگذار و دکمهٔ «ارسال همه» را بزن.
@@ -2446,297 +2393,297 @@
 گام ۵: در پایان یک ترکیب سالم بفرست (خاموشی کمتر یا مساوی دوره، مثلاً دوره 5000 و خاموشی 500)؛ باید بدون هیچ مانعی ارسال شود.</t>
         </is>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>u67 بزرگ‌تر از u66</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>ارسال کل دسته متوقف شود؛ دیالوگ قرمز عددهای مؤثر را نشان دهد؛ هیچ درخواستی به برد نرود و صف دست‌نخورده بماند</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>ترکیب نامعتبر هرگز به برد نمی‌رسد و ترکیب سالم (خاموشی ≤ دوره) بدون مانع ارسال می‌شود</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="24" t="inlineStr">
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="24" t="inlineStr">
         <is>
           <t>8efddaa</t>
         </is>
       </c>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="25" t="inlineStr">
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
+      </c>
+    </row>
+    <row r="24" ht="67.5" customHeight="1">
+      <c r="Q24" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="27">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="27">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="27">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="27">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="27">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="27">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="27">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="27">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="27">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="27">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="27">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="27">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="27">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="27">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="27">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="27">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="27">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="27">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="27">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="27">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="27">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="27">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="27">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="27">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="27">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="27">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="27">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="27">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="27">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="27">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="27">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="27">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="27">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="27">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="27">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="27">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="27">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="27">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="Q63" s="27">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="Q64" s="27">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q24"/>
+  <autoFilter ref="A4:Q63"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -2764,6 +2711,343 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>EL-012</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>فعال‌سازی یک‌خطی</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>MODULE_ESP=0</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: بیلد را با MODULE_ESP=0 بگیر و رفتار عادی برد را یک بار ببین.
+گام ۲: فقط MODULE_ESP را 1 کن و دوباره بیلد بگیر (هیچ تغییر دیگری نده).
+گام ۳: برد را بوت کن (60 ثانیه).
+گام ۴: لینک باید بدون دست‌کاری بقیهٔ ماژول‌ها بالا بیاید و پنل آنلاین شود.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>لینک بدون هیچ تغییر دیگر بالا می‌آید؛ سایر ماژول‌ها دست‌نخورده</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>پنل آنلاین</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="n"/>
+      <c r="Q5" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="27">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="27">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="27">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="27">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="27">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="27">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="27">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="27">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="27">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="27">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="27">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="27">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="27">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="27">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="27">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="27">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="27">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="27">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2992,7 +3276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3119,7 +3403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3351,7 +3635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3483,7 +3767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001" forceFullCalc="1"/>
 </workbook>
@@ -847,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1570,98 +1573,25 @@
     <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>EL-009</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>فیزیکال 921600</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>اسکوپ روی PA9/PA10</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
-گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
-گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>921600 8N1 با درام DDR و بدون خطا</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>بدون فریم خراب در 60s</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="19" t="inlineStr"/>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
           <t>EL-010</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>فلگ‌های تله‌متری</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>پنل باز</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را باز کن و ردیف بیت‌های وضعیت (b0 تا b5) را پیدا کن.
 گام ۲: شرایط را یکی‌یکی تغییر بده: ورودی را قطع و وصل کن، وارد مود دستی شو و خارج شو (10 ثانیه).
@@ -1669,73 +1599,73 @@
 گام ۴: همهٔ برچسب‌ها باید در هر لحظه درست باشند.</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>ورودی قطع/وصل، مود دستی</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>هر بیت مطابق وضعیت واقعی: snapshot/ورودی/معتبر/کانال۱/کانال۲/دستی</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>همهٔ برچسب‌ها درست</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr"/>
+      <c r="N13" s="22" t="inlineStr"/>
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr"/>
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>EL-011</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>state 9 و b5</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>ورود مود دستی</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پارامتر 19 را روی 1 بگذار تا وارد مود دستی شوی.
 گام ۲: در پنل وضعیت هر دو کانال و برچسب مود را نگاه کن (5 ثانیه).
@@ -1743,73 +1673,73 @@
 گام ۴: حین مود دستی بیت FAULT_CHARGER_BAT_LOST باید پاک بماند.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>ID19=1</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>state=9 و b5=1؛ حین مود بیت BAT_LOST پاک</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>پنل «مود دستی» نشان دهد</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr"/>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="19" t="inlineStr"/>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="P14" s="19" t="inlineStr"/>
+      <c r="Q14" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>EL-013</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>کالیبراسیون و read-back</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + لینک فعال</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید روی برد و لینک فعال باشد؛ کارت کالیبراسیون پنل را باز کن.
 گام ۲: یک دسته (batch) شامل همهٔ پارامترهای معتبر (شناسه‌های 0 تا 6) با مقادیر متفاوت از فعلی بساز و با یک تأیید ارسال کن.
@@ -1818,85 +1748,85 @@
 گام ۵: حدود 2 ثانیه صبر کن، برد را reset کن و دوباره بخوان؛ مقادیر باید باقی مانده باشند.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>ID0..6؛ مقدار متفاوت</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>حداکثر 20s</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>پس از ریست، NVM</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
         </is>
       </c>
-      <c r="N16" s="41" t="inlineStr">
+      <c r="N15" s="41" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O16" s="19" t="inlineStr">
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P16" s="19" t="inlineStr"/>
-      <c r="Q16" s="21" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="67.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید STM32 و ESP روی برد باشد و یک جدول فعال داشته باشی (یا بتوانی push کنی).
 گام ۲: در پنل «خواندن جدول فعلی» را بزن؛ STM32 باید برای هر دو کانال LUT_DATA واقعی بفرستد و پنل ستون «فعلی» را نشان دهد.
@@ -1906,85 +1836,85 @@
 گام ۶: صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>نقاط counts و BatteryMa باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>پس از commit و پس از LUT_RESET</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N17" s="42" t="inlineStr">
+      <c r="N16" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O17" s="24" t="inlineStr">
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr"/>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="81" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="17" ht="67.5" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید باشد و در خواندن قبلی یک override غیرصفر داشته باشی؛ مقادیر before را یادداشت کن.
 گام ۲: یک update تکی برای باتری ۱ یا ۲ اجرا کن که یک کانالش معتبر و کانال دیگرش بدون جدول یا نامعتبر باشد؛ proposed کانال هدف را صفر بگذار.
@@ -1993,85 +1923,85 @@
 گام ۵: هر دو فریم باتری باید مستقل بمانند و خطای gain/offset پیش از POST /lut جلوی ارسال جدول را بگیرد.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>پس از commit و فقط با readback دقیق</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
         </is>
       </c>
-      <c r="N18" s="41" t="inlineStr">
+      <c r="N17" s="41" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O18" s="19" t="inlineStr">
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="19" t="n"/>
-      <c r="Q18" s="21" t="inlineStr">
+      <c r="P17" s="19" t="n"/>
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>گام ۱: فرم‌ور جدید، یک commit موفق کالیبراسیون/LUT و لینک فعال داشته باش.
 گام ۲: بعد از commit (هم صفرنقطه‌ای با n1=n2=0 و هم با جدول فعال) با magic و grant معتبر reset درخواست کن.
@@ -2080,85 +2010,85 @@
 گام ۵: در flush ناموفق باید پاسخ CAL_LUT_ST_FLASH بیاید و reset انجام نشود؛ timeout، mismatch یا reject هرگز موفقیت حساب نمی‌شود.</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
         </is>
       </c>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
         </is>
       </c>
-      <c r="N19" s="42" t="inlineStr">
+      <c r="N18" s="42" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P19" s="24" t="n"/>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: در پنل یک ورودی نامعتبر وارد کن (مثلاً duty را خالی بگذار یا مولتی‌متر را خالی ارسال کن) تا پیام خطا (palert) بیاید.
@@ -2166,77 +2096,77 @@
 گام ۴: روی برد واقعی هم یک بار همین را تکرار کن (3 ثانیه کافی است).</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>ورودی نامعتبر</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>پیام با کادر تیره #121a2c/#35507f همرنگ پنل نمایش داده شود، نه alert سفید ویندوز؛ دکمه باشه بستن</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>دیالوگ تیره + بدون alert پیش‌فرض</t>
         </is>
       </c>
-      <c r="K20" s="17" t="n"/>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="M19" s="17" t="n"/>
+      <c r="N19" s="17" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O20" s="19" t="inlineStr">
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P20" s="19" t="n"/>
-      <c r="Q20" s="21" t="inlineStr">
+      <c r="P19" s="19" t="n"/>
+      <c r="Q19" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: یکی از این‌ها را بزن: دکمهٔ قطع PWM شارژر، ورود به مود دستی، یا پاک کردن فایل بنچ.
@@ -2244,73 +2174,77 @@
 گام ۴: یک بار Enter بزن (باید تأیید کند) و در اجرای بعدی Esc (باید لغو کند).</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>کلیک قطع</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>دیالوگ تأیید با کادر تیره #pmod، دو دکمه تأیید/انصراف، Enter=تأیید Esc=لغو</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>Enter تأیید و Esc انصراف + استایل تیره</t>
         </is>
       </c>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="24" t="inlineStr">
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: دو تأیید پشت سر هم بساز (مثلاً دو بار دکمهٔ قطع PWM را بزن).
@@ -2318,73 +2252,73 @@
 گام ۴: هیچ‌وقت نباید دو دیالوگ روی هم بیفتند.</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>دو درخواست</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>دیالوگ‌ها یکی‌یکی و پشت سر هم با Promise queue نمایش داده شوند، نه روی هم</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>صف</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>بدون همپوشانی دیالوگ</t>
         </is>
       </c>
-      <c r="K22" s="17" t="n"/>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M22" s="17" t="n"/>
-      <c r="N22" s="17" t="n"/>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P22" s="19" t="n"/>
-      <c r="Q22" s="21" t="inlineStr">
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>EL-020</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>قفل ترکیب چشمک سبز در پنل</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>پنل وصل یا پیش‌نمایش پنل</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل (یا پیش‌نمایش پنل) را باز کن و به بخش چشمک سبز برو.
 گام ۲: دورهٔ چشمک سبز (شناسهٔ 66) را 1000 و حداقل خاموشی سبز (شناسهٔ 67) را 5000 بگذار و دکمهٔ «ارسال همه» را بزن.
@@ -2393,297 +2327,297 @@
 گام ۵: در پایان یک ترکیب سالم بفرست (خاموشی کمتر یا مساوی دوره، مثلاً دوره 5000 و خاموشی 500)؛ باید بدون هیچ مانعی ارسال شود.</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>u67 بزرگ‌تر از u66</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>ارسال کل دسته متوقف شود؛ دیالوگ قرمز عددهای مؤثر را نشان دهد؛ هیچ درخواستی به برد نرود و صف دست‌نخورده بماند</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>ترکیب نامعتبر هرگز به برد نمی‌رسد و ترکیب سالم (خاموشی ≤ دوره) بدون مانع ارسال می‌شود</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="22" t="n"/>
-      <c r="N23" s="22" t="n"/>
-      <c r="O23" s="24" t="inlineStr">
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t>8efddaa</t>
         </is>
       </c>
-      <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="25" t="inlineStr">
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="Q23" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="67.5" customHeight="1">
       <c r="Q24" s="27">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="27">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="27">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="27">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="27">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="27">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="27">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="27">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="27">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="27">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="27">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="27">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="27">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="27">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="27">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="27">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="27">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="27">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="27">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="27">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="27">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="27">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="27">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="27">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="27">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="27">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="27">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="27">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="27">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="27">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="27">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="27">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="27">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="27">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="27">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="27">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="27">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="27">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="27">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="Q63" s="27">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q63"/>
+  <autoFilter ref="A4:Q62"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -2709,6 +2643,342 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>EL-009</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>فیزیکال 921600</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>اسکوپ روی PA9/PA10</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
+گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
+گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>921600 8N1 با درام DDR و بدون خطا</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>بدون فریم خراب در 60s</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="27">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="27">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="27">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="27">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="27">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="27">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="27">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="27">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="27">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="27">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="27">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="27">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="27">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="27">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="27">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="27">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="27">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="27">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3045,7 +3315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3276,7 +3546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3403,7 +3673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3635,7 +3905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3767,7 +4037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -998,40 +998,38 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>برد خاموش</t>
+          <t>کابل ESP و پنل آماده است؛ دستگاه خاموش</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: برد را بدون ماژول ESP (MODULE_ESP خاموش) بوت کن.
-گام ۲: 5 ثانیه صبر کن: ESP باید خاموش بماند تا وقتی Power آن high شود.
-گام ۳: ماژول ESP را فعال کن.
-گام ۴: ESP باید روشن شود، لینک بالا بیاید و پنل آنلاین شود.</t>
+          <t>گام ۱: دستگاه را روشن کن.
+گام ۲: پنل را باز کن و ببین ارتباط برقرار و عددها زنده می‌شوند.</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>روشن‌کردن دستگاه با پنل</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>ESP تا Power(high) خاموش می‌ماند؛ با فعال‌سازی روشن و لینک بالا می‌آید</t>
+          <t>پنل بالا می‌آید و عددهای زندهٔ دستگاه را نشان می‌دهد</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ارتباط پایدار</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>پنل آنلاین بعد از فعال‌سازی</t>
+          <t>بالا آمدن پنل و عدد زنده = قبول؛ بی‌ارتباطی = رد</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr"/>
@@ -1072,39 +1070,39 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>لینک فعال</t>
+          <t>دستگاه روشن و پنل باز است؛ یک مولتی‌متر دستی داری</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را فعال کن و پنل را باز کن.
-گام ۲: 5 ثانیه فریم‌های زنده (TLM_LIVE) را نگاه کن.
-گام ۳: هر فریم باید 84 بایت باشد، تقریباً هر 100 میلی‌ثانیه بیاید، XOR آن درست باشد و شمارهٔ ترتیب (seq) همیشه در حال افزایش باشد.</t>
+          <t>گام ۱: ولتاژ باتری و ورودی را روی پنل بخوان.
+گام ۲: همان‌ها را با مولتی‌متر روی ترمینال اندازه بگیر.
+گام ۳: ولتاژ ورودی را کمی عوض کن و تازه‌شدن عدد پنل را ببین.</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقایسهٔ زندهٔ پنل با مولتی‌متر</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>فریم 84B هر ~100ms با XOR درست؛ seq صعودی</t>
+          <t>عددهای پنل زنده و نزدیک مولتی‌مترند و با تغییر ولتاژ همان لحظه عوض می‌شوند</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>پیوسته</t>
+          <t>به‌روزرسانی پیوسته</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>seq در حال افزایش</t>
+          <t>نزدیکی عددها و تازگی = قبول؛ عدد یخ‌زده یا خیلی دور = رد</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr"/>
@@ -1145,40 +1143,38 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>لینک فعال</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: لینک فعال باشد و پنل باز باشد.
-گام ۲: از پنل یک پارامتر را تغییر بده تا تبادل GET/BULK اتفاق بیفتد (یا ESP را ری‌استارت کن).
-گام ۳: پاسخ BULK را بررسی کن: باید 20 پارامتر با payload برابر 101 بایت (حداکثر 112) برگردد.
-گام ۴: جدول پارامترهای پنل باید کامل پر شده باشد و هر 20 مقدار معلوم باشند.</t>
+          <t>گام ۱: از پنل فهرست پارامترها را کامل بخوان.
+گام ۲: چند مقدار معلوم (مثلاً سقف جریان شارژ) را با رفتار واقعی دستگاه مقایسه کن.</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
+          <t>خواندن کامل پارامترها از پنل</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>همهٔ پارامترها با مقدارهای واقعی دستگاه برمی‌گردند</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>BULK با ۲۰ پارامتر (payload 101B ≤ 112)؛ جدول پنل پر می‌شود</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>همهٔ ۲۰ پارامتر معلوم</t>
+          <t>کامل و درست برگشتن فهرست = قبول؛ مقدار خالی یا اشتباه = رد</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr"/>
@@ -1219,40 +1215,39 @@
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>لینک فعال</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: پارامتر شناسهٔ 2 را روی 1200 بگذار و ارسال کن.
-گام ۳: حداکثر 2 ثانیه صبر کن تا گزارش برگردد.
-گام ۴: مقدار اعمال‌شده (applied) در گزارش PARAM_REPORT باید 1200 نشان داده شود، یعنی مقدار در مرز تسک clamp و همان اعمال شده است.</t>
+          <t>گام ۱: یک پارامتر بی‌خطر را از پنل عوض کن (مثلاً بلندی/دورهٔ بوق).
+گام ۲: رفتار دستگاه را ببین که همان لحظه عوض شود.
+گام ۳: مقدار را به حالت اول برگردان.</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>ID2=1200</t>
+          <t>تغییر یک پارامتر از پنل</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>2s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>کلمپ در مرز تسک + PARAM_REPORT مقدار اعمال‌شده</t>
+          <t>تغییر پنل همان لحظه روی دستگاه اثر می‌گذارد</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تا تغییر بعدی</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>نمایش applied=1200</t>
+          <t>اثر فوری = قبول؛ بی‌اثری یا نیاز به ریست = رد</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr"/>
@@ -1293,39 +1288,39 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن و پارامتر 19 را روی 1 بگذار (با تأیید) تا مود دستی فعال شود؛ وضعیت باید 9 شود.
-گام ۲: لینک را قطع کن و 10 ثانیه صبر کن.
-گام ۳: بعد از 3 ثانیه سکوت لینک، خروج خودکار باید اتفاق بیفتد و duty هر دو کانال حداکثر تا 3 ثانیه صفر شده باشد.</t>
+          <t>گام ۱: پارامتر مود تست دستی شارژر (شمارهٔ ۱۹) را از پنل روشن کن.
+گام ۲: ببین شارژر به مود دستی می‌رود.
+گام ۳: خاموشش کن و برگشت به شارژ خودکار را ببین.</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>ID19=1</t>
+          <t>روشن/خاموش پارامتر ۱۹ از پنل</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>10s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>ورود مود دستی (state=9، b5)؛ ۳s سکوت → خروج خودکار با duty صفر</t>
+          <t>با روشن‌کردن، شارژر دستی و با خاموش‌کردن، خودکار می‌شود</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>ددمن فعال</t>
+          <t>تابع پنل</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>duty=0 در ≤3s</t>
+          <t>رفت‌وبرگشت درست مود = قبول؛ گیرکردن در یک مود = رد</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr"/>
@@ -1366,40 +1361,38 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>در مود دستی</t>
+          <t>پنل باز است و دستگاه در حال کار عادی</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: وارد مود دستی شو (پارامتر 19 = 1).
-گام ۲: به‌جای GET، فقط پشت سر هم SET_PARAM بفرست و duty را پیوسته تغییر بده (10 ثانیه).
-گام ۳: هر فریم معتبر باید ددمن مود دستی را refresh کند.
-گام ۴: در این 10 ثانیه نباید از مود دستی خارج شود.</t>
+          <t>گام ۱: پنل را نیم ساعت باز نگه دار و دستگاه را به کارش بگذار.
+گام ۲: هر از چندی نگاه کن ارتباط زنده مانده یا نه.</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>فرستادن مکرر SET</t>
+          <t>نیم ساعت ارتباط باز</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>10s</t>
+          <t>نیم ساعت</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>ددمن با هر فریم معتبر refresh می‌شود؛ مود دستی زنده می‌ماند</t>
+          <t>ارتباط در تمام مدت زنده می‌ماند و عددها تازه می‌شوند</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بدون افتادن</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>خروج از مود رخ نمی‌دهد</t>
+          <t>زنده‌ماندن ارتباط = قبول؛ افتادن بی‌دلیل = رد</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr"/>
@@ -1440,30 +1433,28 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>لینک فعال</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: لینک فعال باشد.
-گام ۲: از سمت ESP بیش از گنجایش بافر UART، دادهٔ اضافه بفرست (burst).
-گام ۳: 5 ثانیه نگاه کن: فریم اضافه باید رد شود و پارسر با SOF بعدی دوباره sync شود.
-گام ۴: تله‌متری باید بعد از burst بدون هیچ گیری ادامه پیدا کند.</t>
+          <t>گام ۱: چند پارامتر را پشت سر هم و سریع از پنل عوض کن.
+گام ۲: بعد همه را یکی‌یکی بخوان و با چیزی که فرستادی مقایسه کن.</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>باست از UART</t>
+          <t>تغییر سریع چند پارامتر</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>فریم اضافه رد؛ پارسر با SOF مجدد sync می‌شود؛ هیچ گیری نیست</t>
+          <t>هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -1473,7 +1464,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>تله‌متری بعد از burst ادامه می‌یابد</t>
+          <t>درست نشستن همهٔ تغییرها = قبول؛ گم‌شدن یا هنگ = رد</t>
         </is>
       </c>
       <c r="K11" s="17" t="inlineStr"/>
@@ -1514,30 +1505,28 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>لینک فعال</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: لینک فعال باشد.
-گام ۲: از سمت ESP بیش از 250 بایت در 100 میلی‌ثانیه بفرست (burst سنگین).
-گام ۳: 5 ثانیه لینک را زیر نظر بگیر: فریم‌های خارج از سقف باید رد شوند.
-گام ۴: لینک باید پایدار بماند؛ نه قفل کند نه ریست شود.</t>
+          <t>گام ۱: در مدت کوتاه دستورهای زیادی از پنل بفرست (خواندن و نوشتن پشت سر هم).
+گام ۲: رفتار دستگاه و پنل را نگاه کن.</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>burst</t>
+          <t>بار زیاد دستور از پنل</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>فریم‌های خارج از سقف رد می‌شوند؛ لینک پایدار</t>
+          <t>دستگاه به نوبت و کامل جواب می‌دهد؛ هنگ، ریست یا جواب نصفه نیست</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -1547,7 +1536,7 @@
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>بدون قفل/ریست</t>
+          <t>جواب کامل زیر بار = قبول؛ هنگ یا ریست = رد</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr"/>
@@ -1588,40 +1577,39 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>پنل باز</t>
+          <t>پنل باز؛ دستگاه با برق شهر در حال شارژ باتری است</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را باز کن و ردیف بیت‌های وضعیت (b0 تا b5) را پیدا کن.
-گام ۲: شرایط را یکی‌یکی تغییر بده: ورودی را قطع و وصل کن، وارد مود دستی شو و خارج شو (10 ثانیه).
-گام ۳: هر بیت را با وضعیت واقعی مقایسه کن: snapshot معتبر، ورودی حاضر، اعتبار کلی، کانال ۱، کانال ۲ و مود دستی.
-گام ۴: همهٔ برچسب‌ها باید در هر لحظه درست باشند.</t>
+          <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
+گام ۲: در پنل ببین خطای ۶ و توقف شارژ نشان داده می‌شود.
+گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>ورودی قطع/وصل، مود دستی</t>
+          <t>ساختن و پاک‌کردن خطای ۶</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>10s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>هر بیت مطابق وضعیت واقعی: snapshot/ورودی/معتبر/کانال۱/کانال۲/دستی</t>
+          <t>پرچم خطا در پنل دقیقاً با چراغ‌های دستگاه یکی است</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>هم‌گام با دستگاه</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>همهٔ برچسب‌ها درست</t>
+          <t>یکی‌بودن پنل و واقعیت = قبول؛ اختلاف = رد</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr"/>
@@ -1662,30 +1650,29 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>ورود مود دستی</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: پارامتر 19 را روی 1 بگذار تا وارد مود دستی شوی.
-گام ۲: در پنل وضعیت هر دو کانال و برچسب مود را نگاه کن (5 ثانیه).
-گام ۳: هر دو کانال باید وضعیت 9 و بیت b5 برابر 1 باشند و پنل «مود دستی» نشان دهد.
-گام ۴: حین مود دستی بیت FAULT_CHARGER_BAT_LOST باید پاک بماند.</t>
+          <t>گام ۱: دستگاه را به شارژ بزن و وضعیت شارژر را در پنل بخوان.
+گام ۲: شارژ را قطع کن (برق شهر را بکش) و دوباره وضعیت را بخوان.
+گام ۳: هر دو را با چیزی که روی دستگاه می‌بینی مقایسه کن.</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>ID19=1</t>
+          <t>شروع و قطع شارژ جلوی پنل</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>state=9 و b5=1؛ حین مود بیت BAT_LOST پاک</t>
+          <t>وضعیت شارژر در پنل در هر دو حالت با واقعیت یکی است</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
@@ -1695,7 +1682,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>پنل «مود دستی» نشان دهد</t>
+          <t>یکی‌بودن وضعیت‌ها = قبول؛ وضعیت دروغ در پنل = رد</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr"/>
@@ -1736,41 +1723,39 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Firmware جدید + لینک فعال</t>
+          <t>پنل باز و راهنمای کالیبراسیون را می‌دانی</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: فرم‌ور جدید روی برد و لینک فعال باشد؛ کارت کالیبراسیون پنل را باز کن.
-گام ۲: یک دسته (batch) شامل همهٔ پارامترهای معتبر (شناسه‌های 0 تا 6) با مقادیر متفاوت از فعلی بساز و با یک تأیید ارسال کن.
-گام ۳: جواب HTTP 200 فقط یعنی «در صف است»، موفقیت نیست؛ صبر کن گزارش PARAM_REPORT/PARAMS_BULK برگردد (حداکثر 20 ثانیه).
-گام ۴: هر 7 مقدار را با read-back مقایسه کن: فقط وقتی هرکدام عیناً برابر بود و وضعیتش unchanged/changed-confirmed شد قبول است.
-گام ۵: حدود 2 ثانیه صبر کن، برد را reset کن و دوباره بخوان؛ مقادیر باید باقی مانده باشند.</t>
+          <t>گام ۱: از پنل یک نقطهٔ کالیبراسیون را بفرست.
+گام ۲: همان را از پنل بخوان (read-back).
+گام ۳: عدد برگشتی را با فرستاده مقایسه کن.</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>ID0..6؛ مقدار متفاوت</t>
+          <t>فرستادن و خواندن کالیبراسیون</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>حداکثر 20s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>HTTP 200 فقط صف است؛ موفقیت فقط پس از PARAM_REPORT/PARAMS_BULK با مقدار عیناً برابر</t>
+          <t>عدد برگشتی دقیقاً همان فرستاده است</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>پس از ریست، NVM</t>
+          <t>ماندگار</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>هر ۷ مقدار معتبر read-back برابر؛ وضعیت هر نام unchanged/changed-confirmed/mismatch/readback failure؛ پس از حدود ۲s و reset مقادیر باقی بماند</t>
+          <t>برابری عددها = قبول؛ اختلاف = رد</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1823,42 +1808,38 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Firmware جدید STM32 و ESP + جدول فعال یا جدول قابل push</t>
+          <t>پنل باز و یک جدول LUT ذخیره شده است</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: فرم‌ور جدید STM32 و ESP روی برد باشد و یک جدول فعال داشته باشی (یا بتوانی push کنی).
-گام ۲: در پنل «خواندن جدول فعلی» را بزن؛ STM32 باید برای هر دو کانال LUT_DATA واقعی بفرستد و پنل ستون «فعلی» را نشان دهد.
-گام ۳: update هر دو باتری را اجرا کن: اول پارامترهای معتبر کالیبراسیون تراکنش (gain/offset باتری هدف و آفست‌های ولتاژ) یک‌جا اعمال و read-back شوند، بعد LUT.
-گام ۴: در باتری ۲ عمداً یک نقطه را متفاوت بگذار.
-گام ۵: بعد از commit و reset دوباره /lut/read و تله‌متری را بزن (حداکثر 15 ثانیه): هر ردیف باید unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata هستند و باتری ۲ باید مستقل مقایسه شود.
-گام ۶: صفرنقطه برای حذف override معتبر است.</t>
+          <t>گام ۱: جدول را از پنل کامل بخوان.
+گام ۲: چند عددش را با جدولی که قبلاً فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>نقاط counts و BatteryMa باتری ۱ و ۲، با یک نقطهٔ متفاوت در باتری ۲</t>
+          <t>خواندن کامل جدول از پنل</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>حداکثر 15s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>STM32 برای هر دو کانال LUT_DATA واقعی می‌فرستد؛ همهٔ پارامترهای معتبر کالیبراسیونِ تراکنش پیش از LUT با readback تأیید می‌شوند؛ پنل ستون فعلی، پیشنهادی و پس از commit را نشان می‌دهد؛ صفرنقطه برای حذف override معتبر است.</t>
+          <t>جدول عددبه‌عدد همان ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>پس از commit و پس از LUT_RESET</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>هر ردیف به‌صورت unchanged/changed-confirmed/mismatch یا readback failure گزارش شود؛ CRC و تعداد فقط metadata/handshake باشند و battery 2 مستقل مقایسه شود.</t>
+          <t>برابری کامل = قبول؛ هر اختلاف = رد</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -1911,41 +1892,38 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Firmware جدید + override غیرصفر در بازخوانی قبل</t>
+          <t>پنل باز و جدول سالمی ذخیره است</t>
         </is>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: فرم‌ور جدید باشد و در خواندن قبلی یک override غیرصفر داشته باشی؛ مقادیر before را یادداشت کن.
-گام ۲: یک update تکی برای باتری ۱ یا ۲ اجرا کن که یک کانالش معتبر و کانال دیگرش بدون جدول یا نامعتبر باشد؛ proposed کانال هدف را صفر بگذار.
-گام ۳: قبل و بعد از commit، LUT_READ و readback gain/offset بگیر (حداکثر 15 ثانیه).
-گام ۴: حذف override باید changed-confirmed دیده شود؛ نقطهٔ اضافه mismatch و readback ناقص failure است و در این حالت‌ها reset نباید پیشنهاد شود.
-گام ۵: هر دو فریم باتری باید مستقل بمانند و خطای gain/offset پیش از POST /lut جلوی ارسال جدول را بگیرد.</t>
+          <t>گام ۱: از پنل یک نقطهٔ صفر یا کانال ناموجود بفرست.
+گام ۲: جدول را دوباره بخوان.</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>before غیرصفر → proposed zero → after zero؛ سپس after غیرصفرِ ناخواسته و readback ناقص</t>
+          <t>فرستادن نقطهٔ صفر/کانال بد</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>حداکثر 15s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>count=0 معتبر است؛ حذف override به‌صورت changed-confirmed دیده می‌شود؛ نقطهٔ اضافه mismatch و readback خطادار failure است؛ خطای gain/offset قبل از POST /lut جلوی جدول را می‌گیرد.</t>
+          <t>دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>پس از commit و فقط با readback دقیق</t>
+          <t>حفظ جدول قبلی</t>
         </is>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>هر دو battery frame مستقل بمانند؛ reset در mismatch یا readback failure پیشنهاد نشود</t>
+          <t>رد ورودی خراب = قبول؛ خراب‌شدن جدول = رد</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1998,41 +1976,39 @@
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Firmware جدید + commit کالیبراسیون/LUT موفق + لینک فعال</t>
+          <t>پنل باز و جدولی ذخیره است</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: فرم‌ور جدید، یک commit موفق کالیبراسیون/LUT و لینک فعال داشته باش.
-گام ۲: بعد از commit (هم صفرنقطه‌ای با n1=n2=0 و هم با جدول فعال) با magic و grant معتبر reset درخواست کن.
-گام ۳: یک بار flush موفق NVM و یک بار flush با خطای تزریق‌شده اجرا کن (حداکثر 15 ثانیه).
-گام ۴: در flush موفق برد باید reset شود و بعد از بالا آمدن، /t تازه و LUT readback هر دو کانال برابر انتظار باشد.
-گام ۵: در flush ناموفق باید پاسخ CAL_LUT_ST_FLASH بیاید و reset انجام نشود؛ timeout، mismatch یا reject هرگز موفقیت حساب نمی‌شود.</t>
+          <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
+گام ۲: برق دستگاه را قطع و وصل کن.
+گام ۳: جدول را دوباره بخوان.</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>commit موفق؛ n1=n2=0 و جدول فعال؛ flush موفق/ناموفق</t>
+          <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>حداکثر 15s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>commit صفرنقطه‌ای حتی بدون جدول فعال معتبر است؛ reset فقط بعد از magic و grant معتبر و flush موفق NVM مسلح می‌شود؛ شکست flush با CAL_LUT_ST_FLASH پاسخ می‌دهد و reset انجام نمی‌شود</t>
+          <t>جدول پاک مانده و بعد از روشن‌شدن برنمی‌گردد</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>پس از موفقیت one-shot؛ پس از شکست flush grant برای retry باقی می‌ماند</t>
+          <t>ماندگار</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>بعد از reset /t تازه و LUT readback هر دو کانال برابر انتظار باشد؛ timeout، mismatch، reject یا flush failure هرگز موفقیت نباشد</t>
+          <t>پاک‌ماندن = قبول؛ برگشتن جدول پاک‌شده = رد</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -2085,30 +2061,29 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز و دستگاه در حال کار است</t>
         </is>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: در پنل یک ورودی نامعتبر وارد کن (مثلاً duty را خالی بگذار یا مولتی‌متر را خالی ارسال کن) تا پیام خطا (palert) بیاید.
-گام ۳: پیام باید با کادر تیرهٔ همرنگ پنل (#121a2c/#35507f) بیاید، نه alert سفید پیش‌فرض ویندوز، و دکمهٔ «باشه» برای بستن داشته باشد.
-گام ۴: روی برد واقعی هم یک بار همین را تکرار کن (3 ثانیه کافی است).</t>
+          <t>گام ۱: کاری کن یک پیام هشدار (alert) در پنل بیاید (مثلاً یک خطای واقعی مثل قطع باتری).
+گام ۲: متن پیام را بخوان و تأییدش کن.
+گام ۳: ببین کار دستگاه حین پیام مختل نشده.</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>ورودی نامعتبر</t>
+          <t>هشدار واقعی در پنل</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>پیام با کادر تیره #121a2c/#35507f همرنگ پنل نمایش داده شود، نه alert سفید ویندوز؛ دکمه باشه بستن</t>
+          <t>پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
@@ -2118,7 +2093,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>دیالوگ تیره + بدون alert پیش‌فرض</t>
+          <t>پیام درست بدون اختلال = قبول؛ هنگ یا پیام اشتباه = رد</t>
         </is>
       </c>
       <c r="K19" s="17" t="n"/>
@@ -2163,30 +2138,29 @@
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز است</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: یکی از این‌ها را بزن: دکمهٔ قطع PWM شارژر، ورود به مود دستی، یا پاک کردن فایل بنچ.
-گام ۳: دیالوگ تأیید باید با کادر تیره (#pmod) و دو دکمهٔ تأیید/انصراف بیاید.
-گام ۴: یک بار Enter بزن (باید تأیید کند) و در اجرای بعدی Esc (باید لغو کند).</t>
+          <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید (confirm) بیاید.
+گام ۲: این بار لغو (Cancel) را بزن.
+گام ۳: مقدار را دوباره بخوان.</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>کلیک قطع</t>
+          <t>لغو کردن پیام تأیید</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>دیالوگ تأیید با کادر تیره #pmod، دو دکمه تأیید/انصراف، Enter=تأیید Esc=لغو</t>
+          <t>با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -2196,7 +2170,7 @@
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>Enter تأیید و Esc انصراف + استایل تیره</t>
+          <t>اعمال‌نشدن تغییر = قبول؛ اعمال با وجود لغو = رد</t>
         </is>
       </c>
       <c r="K20" s="22" t="n"/>
@@ -2241,40 +2215,39 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: دو تأیید پشت سر هم بساز (مثلاً دو بار دکمهٔ قطع PWM را بزن).
-گام ۳: 5 ثانیه نگاه کن: دیالوگ‌ها باید یکی‌یکی و به نوبت (صف Promise) نمایش داده شوند.
-گام ۴: هیچ‌وقت نباید دو دیالوگ روی هم بیفتند.</t>
+          <t>گام ۱: پشت سر هم چند پیام/دیالوگ بساز (چند خطا یا چند تأیید).
+گام ۲: ببین به نوبت نشان داده می‌شوند.
+گام ۳: همه را ببند.</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>دو درخواست</t>
+          <t>چند پیام پشت سر هم</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>دیالوگ‌ها یکی‌یکی و پشت سر هم با Promise queue نمایش داده شوند، نه روی هم</t>
+          <t>پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>صف</t>
+          <t>صف مرتب</t>
         </is>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>بدون همپوشانی دیالوگ</t>
+          <t>نوبت درست = قبول؛ گم‌شدن یا قاطی = رد</t>
         </is>
       </c>
       <c r="K21" s="17" t="n"/>
@@ -2315,31 +2288,29 @@
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>پنل وصل یا پیش‌نمایش پنل</t>
+          <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: پنل (یا پیش‌نمایش پنل) را باز کن و به بخش چشمک سبز برو.
-گام ۲: دورهٔ چشمک سبز (شناسهٔ 66) را 1000 و حداقل خاموشی سبز (شناسهٔ 67) را 5000 بگذار و دکمهٔ «ارسال همه» را بزن.
-گام ۳: باید ارسال کل دسته متوقف شود و یک دیالوگ قرمز، عددهای مؤثر (دوره 1000، خاموشی 5000) را نشان دهد؛ هیچ درخواستی نباید به برد برود و صف تغییرات دست‌نخورده بماند.
-گام ۴: حالا خاموشی روی برد را 10000 نگه دار و فقط دوره را به‌تنهایی 500 کن و دوباره «ارسال همه» را بزن؛ باز هم باید متوقف شود.
-گام ۵: در پایان یک ترکیب سالم بفرست (خاموشی کمتر یا مساوی دوره، مثلاً دوره 5000 و خاموشی 500)؛ باید بدون هیچ مانعی ارسال شود.</t>
+          <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
+گام ۲: ببین پنل چه می‌کند.
+گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>u67 بزرگ‌تر از u66</t>
+          <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>ارسال کل دسته متوقف شود؛ دیالوگ قرمز عددهای مؤثر را نشان دهد؛ هیچ درخواستی به برد نرود و صف دست‌نخورده بماند</t>
+          <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -2349,7 +2320,7 @@
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>ترکیب نامعتبر هرگز به برد نمی‌رسد و ترکیب سالم (خاموشی ≤ دوره) بدون مانع ارسال می‌شود</t>
+          <t>گرفته‌شدن ترکیب بد و قبول ترکیب خوب = قبول؛ رسیدن ترکیب بد به دستگاه = رد</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,51 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -271,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -389,6 +434,81 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -762,62 +882,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول EspLink</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>EspLink | پل UART 921600 8N1 با DMA دوطرفه؛ پروتکل v1.2 (SET_PARAM/GET_PARAMS/TLM_LIVE/PARAM_REPORT/PARAMS_BULK) + مود تست دستی ID19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="48" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>فعال‌سازی با MODULE_ESP=1 (فقط همان یک خط)؛ CH_PD از PA8 توسط برد کنترل می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>قرارداد کامل در ESP_AGENT_SPEC.md v1.2؛ محدودیت‌های سمت ESP در README همین ماژول.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>پنل وب سمت ESP در esp_link_panel/ (ممیزی خط‌به‌خط، کامیت 32098b4).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="48" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>هشدار: تست‌های مود دستی فقط با بار ایمن (electronic load با clamp) و منبع محدودشده.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
         </is>
@@ -873,1716 +993,2404 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول EspLink</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>EL-001</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>CH_PD و بوت</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>کابل ESP و پنل آماده است؛ دستگاه خاموش</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: پنل را باز کن و ببین ارتباط برقرار و عددها زنده می‌شوند.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>روشن‌کردن دستگاه با پنل</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>پنل بالا می‌آید و عددهای زندهٔ دستگاه را نشان می‌دهد</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="54" t="inlineStr">
         <is>
           <t>ارتباط پایدار</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>بالا آمدن پنل و عدد زنده = قبول؛ بی‌ارتباطی = رد</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="54" t="inlineStr"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="54" t="inlineStr"/>
+      <c r="N5" s="54" t="inlineStr"/>
+      <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="56" t="inlineStr"/>
+      <c r="Q5" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>EL-002</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>تله‌متری زنده</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل باز است؛ یک مولتی‌متر دستی داری</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ باتری و ورودی را روی پنل بخوان.
 گام ۲: همان‌ها را با مولتی‌متر روی ترمینال اندازه بگیر.
 گام ۳: ولتاژ ورودی را کمی عوض کن و تازه‌شدن عدد پنل را ببین.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>مقایسهٔ زندهٔ پنل با مولتی‌متر</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>عددهای پنل زنده و نزدیک مولتی‌مترند و با تغییر ولتاژ همان لحظه عوض می‌شوند</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="59" t="inlineStr">
         <is>
           <t>به‌روزرسانی پیوسته</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="59" t="inlineStr">
         <is>
           <t>نزدیکی عددها و تازگی = قبول؛ عدد یخ‌زده یا خیلی دور = رد</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="59" t="inlineStr"/>
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M6" s="59" t="inlineStr"/>
+      <c r="N6" s="59" t="inlineStr"/>
+      <c r="O6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="P6" s="61" t="inlineStr"/>
+      <c r="Q6" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>EL-003</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="54" t="inlineStr">
         <is>
           <t>GET_PARAMS → BULK</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل فهرست پارامترها را کامل بخوان.
 گام ۲: چند مقدار معلوم (مثلاً سقف جریان شارژ) را با رفتار واقعی دستگاه مقایسه کن.</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="56" t="inlineStr">
         <is>
           <t>خواندن کامل پارامترها از پنل</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="54" t="inlineStr">
         <is>
           <t>همهٔ پارامترها با مقدارهای واقعی دستگاه برمی‌گردند</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="54" t="inlineStr">
         <is>
           <t>کامل و درست برگشتن فهرست = قبول؛ مقدار خالی یا اشتباه = رد</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K7" s="54" t="inlineStr"/>
+      <c r="L7" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="M7" s="54" t="inlineStr"/>
+      <c r="N7" s="54" t="inlineStr"/>
+      <c r="O7" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="P7" s="56" t="inlineStr"/>
+      <c r="Q7" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>EL-004</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>SET_PARAM → REPORT</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک پارامتر بی‌خطر را از پنل عوض کن (مثلاً بلندی/دورهٔ بوق).
 گام ۲: رفتار دستگاه را ببین که همان لحظه عوض شود.
 گام ۳: مقدار را به حالت اول برگردان.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>تغییر یک پارامتر از پنل</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="59" t="inlineStr">
         <is>
           <t>تغییر پنل همان لحظه روی دستگاه اثر می‌گذارد</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="59" t="inlineStr">
         <is>
           <t>تا تغییر بعدی</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="59" t="inlineStr">
         <is>
           <t>اثر فوری = قبول؛ بی‌اثری یا نیاز به ریست = رد</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="59" t="inlineStr"/>
+      <c r="L8" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M8" s="59" t="inlineStr"/>
+      <c r="N8" s="59" t="inlineStr"/>
+      <c r="O8" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="P8" s="61" t="inlineStr"/>
+      <c r="Q8" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>EL-005</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>پارامتر ۱۹ مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="54" t="inlineStr">
         <is>
           <t>گام ۱: پارامتر مود تست دستی شارژر (شمارهٔ ۱۹) را از پنل روشن کن.
 گام ۲: ببین شارژر به مود دستی می‌رود.
 گام ۳: خاموشش کن و برگشت به شارژ خودکار را ببین.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>روشن/خاموش پارامتر ۱۹ از پنل</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="54" t="inlineStr">
         <is>
           <t>با روشن‌کردن، شارژر دستی و با خاموش‌کردن، خودکار می‌شود</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="54" t="inlineStr">
         <is>
           <t>تابع پنل</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>رفت‌وبرگشت درست مود = قبول؛ گیرکردن در یک مود = رد</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K9" s="54" t="inlineStr"/>
+      <c r="L9" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M9" s="54" t="inlineStr"/>
+      <c r="N9" s="54" t="inlineStr"/>
+      <c r="O9" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="P9" s="56" t="inlineStr"/>
+      <c r="Q9" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>EL-006</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>تغذیه ددمن با هر فریم</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>پنل باز است و دستگاه در حال کار عادی</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>گام ۱: پنل را نیم ساعت باز نگه دار و دستگاه را به کارش بگذار.
 گام ۲: هر از چندی نگاه کن ارتباط زنده مانده یا نه.</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>نیم ساعت ارتباط باز</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="61" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="59" t="inlineStr">
         <is>
           <t>ارتباط در تمام مدت زنده می‌ماند و عددها تازه می‌شوند</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="59" t="inlineStr">
         <is>
           <t>بدون افتادن</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J10" s="59" t="inlineStr">
         <is>
           <t>زنده‌ماندن ارتباط = قبول؛ افتادن بی‌دلیل = رد</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K10" s="59" t="inlineStr"/>
+      <c r="L10" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M10" s="59" t="inlineStr"/>
+      <c r="N10" s="59" t="inlineStr"/>
+      <c r="O10" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P10" s="61" t="inlineStr"/>
+      <c r="Q10" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>EL-007</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>سرریز ring</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="54" t="inlineStr">
         <is>
           <t>گام ۱: چند پارامتر را پشت سر هم و سریع از پنل عوض کن.
 گام ۲: بعد همه را یکی‌یکی بخوان و با چیزی که فرستادی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
         <is>
           <t>تغییر سریع چند پارامتر</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="54" t="inlineStr">
         <is>
           <t>هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="54" t="inlineStr">
         <is>
           <t>درست نشستن همهٔ تغییرها = قبول؛ گم‌شدن یا هنگ = رد</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K11" s="54" t="inlineStr"/>
+      <c r="L11" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M11" s="54" t="inlineStr"/>
+      <c r="N11" s="54" t="inlineStr"/>
+      <c r="O11" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="P11" s="56" t="inlineStr"/>
+      <c r="Q11" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>EL-008</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>محدودیت burst</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>گام ۱: در مدت کوتاه دستورهای زیادی از پنل بفرست (خواندن و نوشتن پشت سر هم).
 گام ۲: رفتار دستگاه و پنل را نگاه کن.</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
         <is>
           <t>بار زیاد دستور از پنل</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>دستگاه به نوبت و کامل جواب می‌دهد؛ هنگ، ریست یا جواب نصفه نیست</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="59" t="inlineStr">
         <is>
           <t>جواب کامل زیر بار = قبول؛ هنگ یا ریست = رد</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K12" s="59" t="inlineStr"/>
+      <c r="L12" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="M12" s="59" t="inlineStr"/>
+      <c r="N12" s="59" t="inlineStr"/>
+      <c r="O12" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="P12" s="61" t="inlineStr"/>
+      <c r="Q12" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>EL-010</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>فلگ‌های تله‌متری</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>پنل باز؛ دستگاه با برق شهر در حال شارژ باتری است</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="59" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
 گام ۲: در پنل ببین خطای ۶ و توقف شارژ نشان داده می‌شود.
 گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>ساختن و پاک‌کردن خطای ۶</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>پرچم خطا در پنل دقیقاً با چراغ‌های دستگاه یکی است</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>هم‌گام با دستگاه</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>یکی‌بودن پنل و واقعیت = قبول؛ اختلاف = رد</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="K13" s="59" t="inlineStr"/>
+      <c r="L13" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr"/>
-      <c r="N13" s="22" t="inlineStr"/>
-      <c r="O13" s="24" t="inlineStr">
+      <c r="M13" s="59" t="inlineStr"/>
+      <c r="N13" s="59" t="inlineStr"/>
+      <c r="O13" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr"/>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="P13" s="61" t="inlineStr"/>
+      <c r="Q13" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>EL-011</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>state 9 و b5</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را به شارژ بزن و وضعیت شارژر را در پنل بخوان.
 گام ۲: شارژ را قطع کن (برق شهر را بکش) و دوباره وضعیت را بخوان.
 گام ۳: هر دو را با چیزی که روی دستگاه می‌بینی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="56" t="inlineStr">
         <is>
           <t>شروع و قطع شارژ جلوی پنل</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="54" t="inlineStr">
         <is>
           <t>وضعیت شارژر در پنل در هر دو حالت با واقعیت یکی است</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="54" t="inlineStr">
         <is>
           <t>یکی‌بودن وضعیت‌ها = قبول؛ وضعیت دروغ در پنل = رد</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K14" s="54" t="inlineStr"/>
+      <c r="L14" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr"/>
-      <c r="N14" s="17" t="inlineStr"/>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="M14" s="54" t="inlineStr"/>
+      <c r="N14" s="54" t="inlineStr"/>
+      <c r="O14" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="19" t="inlineStr"/>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="P14" s="56" t="inlineStr"/>
+      <c r="Q14" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>EL-013</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>کالیبراسیون و read-back</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="54" t="inlineStr">
         <is>
           <t>پنل باز و راهنمای کالیبراسیون را می‌دانی</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ کالیبراسیون را بفرست.
 گام ۲: همان را از پنل بخوان (read-back).
 گام ۳: عدد برگشتی را با فرستاده مقایسه کن.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
         <is>
           <t>فرستادن و خواندن کالیبراسیون</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="54" t="inlineStr">
         <is>
           <t>عدد برگشتی دقیقاً همان فرستاده است</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="54" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
         <is>
           <t>برابری عددها = قبول؛ اختلاف = رد</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="54" t="inlineStr">
         <is>
           <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="L15" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="54" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
         </is>
       </c>
-      <c r="N15" s="41" t="inlineStr">
+      <c r="N15" s="63" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="O15" s="56" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P15" s="19" t="inlineStr"/>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="P15" s="56" t="inlineStr"/>
+      <c r="Q15" s="58" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>پنل باز و یک جدول LUT ذخیره شده است</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>گام ۱: جدول را از پنل کامل بخوان.
 گام ۲: چند عددش را با جدولی که قبلاً فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="61" t="inlineStr">
         <is>
           <t>خواندن کامل جدول از پنل</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="59" t="inlineStr">
         <is>
           <t>جدول عددبه‌عدد همان ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J16" s="59" t="inlineStr">
         <is>
           <t>برابری کامل = قبول؛ هر اختلاف = رد</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="59" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L16" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="M16" s="59" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N16" s="42" t="inlineStr">
+      <c r="N16" s="64" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O16" s="24" t="inlineStr">
+      <c r="O16" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr"/>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="P16" s="61" t="inlineStr"/>
+      <c r="Q16" s="62" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>پنل باز و جدول سالمی ذخیره است</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ صفر یا کانال ناموجود بفرست.
 گام ۲: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
         <is>
           <t>فرستادن نقطهٔ صفر/کانال بد</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="54" t="inlineStr">
         <is>
           <t>حفظ جدول قبلی</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>رد ورودی خراب = قبول؛ خراب‌شدن جدول = رد</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="54" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L17" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M17" s="54" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
         </is>
       </c>
-      <c r="N17" s="41" t="inlineStr">
+      <c r="N17" s="63" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O17" s="19" t="inlineStr">
+      <c r="O17" s="56" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P17" s="19" t="n"/>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="P17" s="56" t="n"/>
+      <c r="Q17" s="58" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="18" ht="81" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="53" t="inlineStr">
         <is>
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>پنل باز و جدولی ذخیره است</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
 گام ۲: برق دستگاه را قطع و وصل کن.
 گام ۳: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="61" t="inlineStr">
         <is>
           <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="59" t="inlineStr">
         <is>
           <t>جدول پاک مانده و بعد از روشن‌شدن برنمی‌گردد</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="59" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J18" s="59" t="inlineStr">
         <is>
           <t>پاک‌ماندن = قبول؛ برگشتن جدول پاک‌شده = رد</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="59" t="inlineStr">
         <is>
           <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="L18" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M18" s="59" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
         </is>
       </c>
-      <c r="N18" s="42" t="inlineStr">
+      <c r="N18" s="64" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="O18" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="P18" s="61" t="n"/>
+      <c r="Q18" s="62" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="53" t="inlineStr">
         <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="54" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه در حال کار است</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="54" t="inlineStr">
         <is>
           <t>گام ۱: کاری کن یک پیام هشدار (alert) در پنل بیاید (مثلاً یک خطای واقعی مثل قطع باتری).
 گام ۲: متن پیام را بخوان و تأییدش کن.
 گام ۳: ببین کار دستگاه حین پیام مختل نشده.</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="56" t="inlineStr">
         <is>
           <t>هشدار واقعی در پنل</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="54" t="inlineStr">
         <is>
           <t>پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J19" s="54" t="inlineStr">
         <is>
           <t>پیام درست بدون اختلال = قبول؛ هنگ یا پیام اشتباه = رد</t>
         </is>
       </c>
-      <c r="K19" s="17" t="n"/>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="K19" s="54" t="n"/>
+      <c r="L19" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M19" s="17" t="n"/>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="M19" s="54" t="n"/>
+      <c r="N19" s="54" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr">
+      <c r="O19" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P19" s="19" t="n"/>
-      <c r="Q19" s="21" t="inlineStr">
+      <c r="P19" s="56" t="n"/>
+      <c r="Q19" s="58" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="53" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>پنل باز است</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید (confirm) بیاید.
 گام ۲: این بار لغو (Cancel) را بزن.
 گام ۳: مقدار را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="61" t="inlineStr">
         <is>
           <t>لغو کردن پیام تأیید</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="59" t="inlineStr">
         <is>
           <t>با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J20" s="59" t="inlineStr">
         <is>
           <t>اعمال‌نشدن تغییر = قبول؛ اعمال با وجود لغو = رد</t>
         </is>
       </c>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="K20" s="59" t="n"/>
+      <c r="L20" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="inlineStr">
+      <c r="M20" s="59" t="n"/>
+      <c r="N20" s="59" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="61" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="P20" s="61" t="n"/>
+      <c r="Q20" s="62" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="53" t="inlineStr">
         <is>
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="56" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="54" t="inlineStr">
         <is>
           <t>گام ۱: پشت سر هم چند پیام/دیالوگ بساز (چند خطا یا چند تأیید).
 گام ۲: ببین به نوبت نشان داده می‌شوند.
 گام ۳: همه را ببند.</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="56" t="inlineStr">
         <is>
           <t>چند پیام پشت سر هم</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I21" s="54" t="inlineStr">
         <is>
           <t>صف مرتب</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>نوبت درست = قبول؛ گم‌شدن یا قاطی = رد</t>
         </is>
       </c>
-      <c r="K21" s="17" t="n"/>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="M21" s="54" t="n"/>
+      <c r="N21" s="54" t="n"/>
+      <c r="O21" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" s="19" t="n"/>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="P21" s="56" t="n"/>
+      <c r="Q21" s="58" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="53" t="inlineStr">
         <is>
           <t>EL-020</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>قفل ترکیب چشمک سبز در پنل</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="59" t="inlineStr">
         <is>
           <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
 گام ۲: ببین پنل چه می‌کند.
 گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="61" t="inlineStr">
         <is>
           <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="59" t="inlineStr">
         <is>
           <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J22" s="59" t="inlineStr">
         <is>
           <t>گرفته‌شدن ترکیب بد و قبول ترکیب خوب = قبول؛ رسیدن ترکیب بد به دستگاه = رد</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K22" s="59" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="L22" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="22" t="n"/>
-      <c r="N22" s="22" t="n"/>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="M22" s="59" t="n"/>
+      <c r="N22" s="59" t="n"/>
+      <c r="O22" s="61" t="inlineStr">
         <is>
           <t>8efddaa</t>
         </is>
       </c>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="P22" s="61" t="n"/>
+      <c r="Q22" s="62" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="Q23" s="27">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="52" t="n"/>
+      <c r="K23" s="52" t="n"/>
+      <c r="L23" s="52" t="n"/>
+      <c r="M23" s="52" t="n"/>
+      <c r="N23" s="52" t="n"/>
+      <c r="O23" s="52" t="n"/>
+      <c r="P23" s="52" t="n"/>
+      <c r="Q23" s="66">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="67.5" customHeight="1">
-      <c r="Q24" s="27">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="66">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="27">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="52" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="66">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="27">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="52" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="52" t="n"/>
+      <c r="K26" s="52" t="n"/>
+      <c r="L26" s="52" t="n"/>
+      <c r="M26" s="52" t="n"/>
+      <c r="N26" s="52" t="n"/>
+      <c r="O26" s="52" t="n"/>
+      <c r="P26" s="52" t="n"/>
+      <c r="Q26" s="66">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="27">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+      <c r="H27" s="52" t="n"/>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="52" t="n"/>
+      <c r="K27" s="52" t="n"/>
+      <c r="L27" s="52" t="n"/>
+      <c r="M27" s="52" t="n"/>
+      <c r="N27" s="52" t="n"/>
+      <c r="O27" s="52" t="n"/>
+      <c r="P27" s="52" t="n"/>
+      <c r="Q27" s="66">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="27">
+      <c r="A28" s="52" t="n"/>
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="52" t="n"/>
+      <c r="F28" s="52" t="n"/>
+      <c r="G28" s="52" t="n"/>
+      <c r="H28" s="52" t="n"/>
+      <c r="I28" s="52" t="n"/>
+      <c r="J28" s="52" t="n"/>
+      <c r="K28" s="52" t="n"/>
+      <c r="L28" s="52" t="n"/>
+      <c r="M28" s="52" t="n"/>
+      <c r="N28" s="52" t="n"/>
+      <c r="O28" s="52" t="n"/>
+      <c r="P28" s="52" t="n"/>
+      <c r="Q28" s="66">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="27">
+      <c r="A29" s="52" t="n"/>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+      <c r="E29" s="52" t="n"/>
+      <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="52" t="n"/>
+      <c r="I29" s="52" t="n"/>
+      <c r="J29" s="52" t="n"/>
+      <c r="K29" s="52" t="n"/>
+      <c r="L29" s="52" t="n"/>
+      <c r="M29" s="52" t="n"/>
+      <c r="N29" s="52" t="n"/>
+      <c r="O29" s="52" t="n"/>
+      <c r="P29" s="52" t="n"/>
+      <c r="Q29" s="66">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="27">
+      <c r="A30" s="52" t="n"/>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="52" t="n"/>
+      <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+      <c r="H30" s="52" t="n"/>
+      <c r="I30" s="52" t="n"/>
+      <c r="J30" s="52" t="n"/>
+      <c r="K30" s="52" t="n"/>
+      <c r="L30" s="52" t="n"/>
+      <c r="M30" s="52" t="n"/>
+      <c r="N30" s="52" t="n"/>
+      <c r="O30" s="52" t="n"/>
+      <c r="P30" s="52" t="n"/>
+      <c r="Q30" s="66">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="27">
+      <c r="A31" s="52" t="n"/>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="52" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="52" t="n"/>
+      <c r="I31" s="52" t="n"/>
+      <c r="J31" s="52" t="n"/>
+      <c r="K31" s="52" t="n"/>
+      <c r="L31" s="52" t="n"/>
+      <c r="M31" s="52" t="n"/>
+      <c r="N31" s="52" t="n"/>
+      <c r="O31" s="52" t="n"/>
+      <c r="P31" s="52" t="n"/>
+      <c r="Q31" s="66">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="27">
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+      <c r="E32" s="52" t="n"/>
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="52" t="n"/>
+      <c r="I32" s="52" t="n"/>
+      <c r="J32" s="52" t="n"/>
+      <c r="K32" s="52" t="n"/>
+      <c r="L32" s="52" t="n"/>
+      <c r="M32" s="52" t="n"/>
+      <c r="N32" s="52" t="n"/>
+      <c r="O32" s="52" t="n"/>
+      <c r="P32" s="52" t="n"/>
+      <c r="Q32" s="66">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="27">
+      <c r="A33" s="52" t="n"/>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="52" t="n"/>
+      <c r="I33" s="52" t="n"/>
+      <c r="J33" s="52" t="n"/>
+      <c r="K33" s="52" t="n"/>
+      <c r="L33" s="52" t="n"/>
+      <c r="M33" s="52" t="n"/>
+      <c r="N33" s="52" t="n"/>
+      <c r="O33" s="52" t="n"/>
+      <c r="P33" s="52" t="n"/>
+      <c r="Q33" s="66">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="27">
+      <c r="A34" s="52" t="n"/>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+      <c r="E34" s="52" t="n"/>
+      <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+      <c r="H34" s="52" t="n"/>
+      <c r="I34" s="52" t="n"/>
+      <c r="J34" s="52" t="n"/>
+      <c r="K34" s="52" t="n"/>
+      <c r="L34" s="52" t="n"/>
+      <c r="M34" s="52" t="n"/>
+      <c r="N34" s="52" t="n"/>
+      <c r="O34" s="52" t="n"/>
+      <c r="P34" s="52" t="n"/>
+      <c r="Q34" s="66">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="27">
+      <c r="A35" s="52" t="n"/>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52" t="n"/>
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="52" t="n"/>
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52" t="n"/>
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52" t="n"/>
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52" t="n"/>
+      <c r="Q35" s="66">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="27">
+      <c r="A36" s="52" t="n"/>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+      <c r="E36" s="52" t="n"/>
+      <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+      <c r="H36" s="52" t="n"/>
+      <c r="I36" s="52" t="n"/>
+      <c r="J36" s="52" t="n"/>
+      <c r="K36" s="52" t="n"/>
+      <c r="L36" s="52" t="n"/>
+      <c r="M36" s="52" t="n"/>
+      <c r="N36" s="52" t="n"/>
+      <c r="O36" s="52" t="n"/>
+      <c r="P36" s="52" t="n"/>
+      <c r="Q36" s="66">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="27">
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+      <c r="E37" s="52" t="n"/>
+      <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="52" t="n"/>
+      <c r="I37" s="52" t="n"/>
+      <c r="J37" s="52" t="n"/>
+      <c r="K37" s="52" t="n"/>
+      <c r="L37" s="52" t="n"/>
+      <c r="M37" s="52" t="n"/>
+      <c r="N37" s="52" t="n"/>
+      <c r="O37" s="52" t="n"/>
+      <c r="P37" s="52" t="n"/>
+      <c r="Q37" s="66">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="27">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+      <c r="I38" s="52" t="n"/>
+      <c r="J38" s="52" t="n"/>
+      <c r="K38" s="52" t="n"/>
+      <c r="L38" s="52" t="n"/>
+      <c r="M38" s="52" t="n"/>
+      <c r="N38" s="52" t="n"/>
+      <c r="O38" s="52" t="n"/>
+      <c r="P38" s="52" t="n"/>
+      <c r="Q38" s="66">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="27">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+      <c r="E39" s="52" t="n"/>
+      <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+      <c r="H39" s="52" t="n"/>
+      <c r="I39" s="52" t="n"/>
+      <c r="J39" s="52" t="n"/>
+      <c r="K39" s="52" t="n"/>
+      <c r="L39" s="52" t="n"/>
+      <c r="M39" s="52" t="n"/>
+      <c r="N39" s="52" t="n"/>
+      <c r="O39" s="52" t="n"/>
+      <c r="P39" s="52" t="n"/>
+      <c r="Q39" s="66">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="27">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+      <c r="E40" s="52" t="n"/>
+      <c r="F40" s="52" t="n"/>
+      <c r="G40" s="52" t="n"/>
+      <c r="H40" s="52" t="n"/>
+      <c r="I40" s="52" t="n"/>
+      <c r="J40" s="52" t="n"/>
+      <c r="K40" s="52" t="n"/>
+      <c r="L40" s="52" t="n"/>
+      <c r="M40" s="52" t="n"/>
+      <c r="N40" s="52" t="n"/>
+      <c r="O40" s="52" t="n"/>
+      <c r="P40" s="52" t="n"/>
+      <c r="Q40" s="66">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="27">
+      <c r="A41" s="52" t="n"/>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+      <c r="E41" s="52" t="n"/>
+      <c r="F41" s="52" t="n"/>
+      <c r="G41" s="52" t="n"/>
+      <c r="H41" s="52" t="n"/>
+      <c r="I41" s="52" t="n"/>
+      <c r="J41" s="52" t="n"/>
+      <c r="K41" s="52" t="n"/>
+      <c r="L41" s="52" t="n"/>
+      <c r="M41" s="52" t="n"/>
+      <c r="N41" s="52" t="n"/>
+      <c r="O41" s="52" t="n"/>
+      <c r="P41" s="52" t="n"/>
+      <c r="Q41" s="66">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="27">
+      <c r="A42" s="52" t="n"/>
+      <c r="B42" s="52" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+      <c r="E42" s="52" t="n"/>
+      <c r="F42" s="52" t="n"/>
+      <c r="G42" s="52" t="n"/>
+      <c r="H42" s="52" t="n"/>
+      <c r="I42" s="52" t="n"/>
+      <c r="J42" s="52" t="n"/>
+      <c r="K42" s="52" t="n"/>
+      <c r="L42" s="52" t="n"/>
+      <c r="M42" s="52" t="n"/>
+      <c r="N42" s="52" t="n"/>
+      <c r="O42" s="52" t="n"/>
+      <c r="P42" s="52" t="n"/>
+      <c r="Q42" s="66">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="27">
+      <c r="A43" s="52" t="n"/>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+      <c r="E43" s="52" t="n"/>
+      <c r="F43" s="52" t="n"/>
+      <c r="G43" s="52" t="n"/>
+      <c r="H43" s="52" t="n"/>
+      <c r="I43" s="52" t="n"/>
+      <c r="J43" s="52" t="n"/>
+      <c r="K43" s="52" t="n"/>
+      <c r="L43" s="52" t="n"/>
+      <c r="M43" s="52" t="n"/>
+      <c r="N43" s="52" t="n"/>
+      <c r="O43" s="52" t="n"/>
+      <c r="P43" s="52" t="n"/>
+      <c r="Q43" s="66">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="27">
+      <c r="A44" s="52" t="n"/>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+      <c r="E44" s="52" t="n"/>
+      <c r="F44" s="52" t="n"/>
+      <c r="G44" s="52" t="n"/>
+      <c r="H44" s="52" t="n"/>
+      <c r="I44" s="52" t="n"/>
+      <c r="J44" s="52" t="n"/>
+      <c r="K44" s="52" t="n"/>
+      <c r="L44" s="52" t="n"/>
+      <c r="M44" s="52" t="n"/>
+      <c r="N44" s="52" t="n"/>
+      <c r="O44" s="52" t="n"/>
+      <c r="P44" s="52" t="n"/>
+      <c r="Q44" s="66">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="27">
+      <c r="A45" s="52" t="n"/>
+      <c r="B45" s="52" t="n"/>
+      <c r="C45" s="52" t="n"/>
+      <c r="D45" s="52" t="n"/>
+      <c r="E45" s="52" t="n"/>
+      <c r="F45" s="52" t="n"/>
+      <c r="G45" s="52" t="n"/>
+      <c r="H45" s="52" t="n"/>
+      <c r="I45" s="52" t="n"/>
+      <c r="J45" s="52" t="n"/>
+      <c r="K45" s="52" t="n"/>
+      <c r="L45" s="52" t="n"/>
+      <c r="M45" s="52" t="n"/>
+      <c r="N45" s="52" t="n"/>
+      <c r="O45" s="52" t="n"/>
+      <c r="P45" s="52" t="n"/>
+      <c r="Q45" s="66">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="27">
+      <c r="A46" s="52" t="n"/>
+      <c r="B46" s="52" t="n"/>
+      <c r="C46" s="52" t="n"/>
+      <c r="D46" s="52" t="n"/>
+      <c r="E46" s="52" t="n"/>
+      <c r="F46" s="52" t="n"/>
+      <c r="G46" s="52" t="n"/>
+      <c r="H46" s="52" t="n"/>
+      <c r="I46" s="52" t="n"/>
+      <c r="J46" s="52" t="n"/>
+      <c r="K46" s="52" t="n"/>
+      <c r="L46" s="52" t="n"/>
+      <c r="M46" s="52" t="n"/>
+      <c r="N46" s="52" t="n"/>
+      <c r="O46" s="52" t="n"/>
+      <c r="P46" s="52" t="n"/>
+      <c r="Q46" s="66">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="27">
+      <c r="A47" s="52" t="n"/>
+      <c r="B47" s="52" t="n"/>
+      <c r="C47" s="52" t="n"/>
+      <c r="D47" s="52" t="n"/>
+      <c r="E47" s="52" t="n"/>
+      <c r="F47" s="52" t="n"/>
+      <c r="G47" s="52" t="n"/>
+      <c r="H47" s="52" t="n"/>
+      <c r="I47" s="52" t="n"/>
+      <c r="J47" s="52" t="n"/>
+      <c r="K47" s="52" t="n"/>
+      <c r="L47" s="52" t="n"/>
+      <c r="M47" s="52" t="n"/>
+      <c r="N47" s="52" t="n"/>
+      <c r="O47" s="52" t="n"/>
+      <c r="P47" s="52" t="n"/>
+      <c r="Q47" s="66">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="27">
+      <c r="A48" s="52" t="n"/>
+      <c r="B48" s="52" t="n"/>
+      <c r="C48" s="52" t="n"/>
+      <c r="D48" s="52" t="n"/>
+      <c r="E48" s="52" t="n"/>
+      <c r="F48" s="52" t="n"/>
+      <c r="G48" s="52" t="n"/>
+      <c r="H48" s="52" t="n"/>
+      <c r="I48" s="52" t="n"/>
+      <c r="J48" s="52" t="n"/>
+      <c r="K48" s="52" t="n"/>
+      <c r="L48" s="52" t="n"/>
+      <c r="M48" s="52" t="n"/>
+      <c r="N48" s="52" t="n"/>
+      <c r="O48" s="52" t="n"/>
+      <c r="P48" s="52" t="n"/>
+      <c r="Q48" s="66">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="27">
+      <c r="A49" s="52" t="n"/>
+      <c r="B49" s="52" t="n"/>
+      <c r="C49" s="52" t="n"/>
+      <c r="D49" s="52" t="n"/>
+      <c r="E49" s="52" t="n"/>
+      <c r="F49" s="52" t="n"/>
+      <c r="G49" s="52" t="n"/>
+      <c r="H49" s="52" t="n"/>
+      <c r="I49" s="52" t="n"/>
+      <c r="J49" s="52" t="n"/>
+      <c r="K49" s="52" t="n"/>
+      <c r="L49" s="52" t="n"/>
+      <c r="M49" s="52" t="n"/>
+      <c r="N49" s="52" t="n"/>
+      <c r="O49" s="52" t="n"/>
+      <c r="P49" s="52" t="n"/>
+      <c r="Q49" s="66">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="27">
+      <c r="A50" s="52" t="n"/>
+      <c r="B50" s="52" t="n"/>
+      <c r="C50" s="52" t="n"/>
+      <c r="D50" s="52" t="n"/>
+      <c r="E50" s="52" t="n"/>
+      <c r="F50" s="52" t="n"/>
+      <c r="G50" s="52" t="n"/>
+      <c r="H50" s="52" t="n"/>
+      <c r="I50" s="52" t="n"/>
+      <c r="J50" s="52" t="n"/>
+      <c r="K50" s="52" t="n"/>
+      <c r="L50" s="52" t="n"/>
+      <c r="M50" s="52" t="n"/>
+      <c r="N50" s="52" t="n"/>
+      <c r="O50" s="52" t="n"/>
+      <c r="P50" s="52" t="n"/>
+      <c r="Q50" s="66">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="27">
+      <c r="A51" s="52" t="n"/>
+      <c r="B51" s="52" t="n"/>
+      <c r="C51" s="52" t="n"/>
+      <c r="D51" s="52" t="n"/>
+      <c r="E51" s="52" t="n"/>
+      <c r="F51" s="52" t="n"/>
+      <c r="G51" s="52" t="n"/>
+      <c r="H51" s="52" t="n"/>
+      <c r="I51" s="52" t="n"/>
+      <c r="J51" s="52" t="n"/>
+      <c r="K51" s="52" t="n"/>
+      <c r="L51" s="52" t="n"/>
+      <c r="M51" s="52" t="n"/>
+      <c r="N51" s="52" t="n"/>
+      <c r="O51" s="52" t="n"/>
+      <c r="P51" s="52" t="n"/>
+      <c r="Q51" s="66">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="27">
+      <c r="A52" s="52" t="n"/>
+      <c r="B52" s="52" t="n"/>
+      <c r="C52" s="52" t="n"/>
+      <c r="D52" s="52" t="n"/>
+      <c r="E52" s="52" t="n"/>
+      <c r="F52" s="52" t="n"/>
+      <c r="G52" s="52" t="n"/>
+      <c r="H52" s="52" t="n"/>
+      <c r="I52" s="52" t="n"/>
+      <c r="J52" s="52" t="n"/>
+      <c r="K52" s="52" t="n"/>
+      <c r="L52" s="52" t="n"/>
+      <c r="M52" s="52" t="n"/>
+      <c r="N52" s="52" t="n"/>
+      <c r="O52" s="52" t="n"/>
+      <c r="P52" s="52" t="n"/>
+      <c r="Q52" s="66">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="Q53" s="27">
+      <c r="A53" s="52" t="n"/>
+      <c r="B53" s="52" t="n"/>
+      <c r="C53" s="52" t="n"/>
+      <c r="D53" s="52" t="n"/>
+      <c r="E53" s="52" t="n"/>
+      <c r="F53" s="52" t="n"/>
+      <c r="G53" s="52" t="n"/>
+      <c r="H53" s="52" t="n"/>
+      <c r="I53" s="52" t="n"/>
+      <c r="J53" s="52" t="n"/>
+      <c r="K53" s="52" t="n"/>
+      <c r="L53" s="52" t="n"/>
+      <c r="M53" s="52" t="n"/>
+      <c r="N53" s="52" t="n"/>
+      <c r="O53" s="52" t="n"/>
+      <c r="P53" s="52" t="n"/>
+      <c r="Q53" s="66">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="Q54" s="27">
+      <c r="A54" s="52" t="n"/>
+      <c r="B54" s="52" t="n"/>
+      <c r="C54" s="52" t="n"/>
+      <c r="D54" s="52" t="n"/>
+      <c r="E54" s="52" t="n"/>
+      <c r="F54" s="52" t="n"/>
+      <c r="G54" s="52" t="n"/>
+      <c r="H54" s="52" t="n"/>
+      <c r="I54" s="52" t="n"/>
+      <c r="J54" s="52" t="n"/>
+      <c r="K54" s="52" t="n"/>
+      <c r="L54" s="52" t="n"/>
+      <c r="M54" s="52" t="n"/>
+      <c r="N54" s="52" t="n"/>
+      <c r="O54" s="52" t="n"/>
+      <c r="P54" s="52" t="n"/>
+      <c r="Q54" s="66">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="Q55" s="27">
+      <c r="A55" s="52" t="n"/>
+      <c r="B55" s="52" t="n"/>
+      <c r="C55" s="52" t="n"/>
+      <c r="D55" s="52" t="n"/>
+      <c r="E55" s="52" t="n"/>
+      <c r="F55" s="52" t="n"/>
+      <c r="G55" s="52" t="n"/>
+      <c r="H55" s="52" t="n"/>
+      <c r="I55" s="52" t="n"/>
+      <c r="J55" s="52" t="n"/>
+      <c r="K55" s="52" t="n"/>
+      <c r="L55" s="52" t="n"/>
+      <c r="M55" s="52" t="n"/>
+      <c r="N55" s="52" t="n"/>
+      <c r="O55" s="52" t="n"/>
+      <c r="P55" s="52" t="n"/>
+      <c r="Q55" s="66">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="Q56" s="27">
+      <c r="A56" s="52" t="n"/>
+      <c r="B56" s="52" t="n"/>
+      <c r="C56" s="52" t="n"/>
+      <c r="D56" s="52" t="n"/>
+      <c r="E56" s="52" t="n"/>
+      <c r="F56" s="52" t="n"/>
+      <c r="G56" s="52" t="n"/>
+      <c r="H56" s="52" t="n"/>
+      <c r="I56" s="52" t="n"/>
+      <c r="J56" s="52" t="n"/>
+      <c r="K56" s="52" t="n"/>
+      <c r="L56" s="52" t="n"/>
+      <c r="M56" s="52" t="n"/>
+      <c r="N56" s="52" t="n"/>
+      <c r="O56" s="52" t="n"/>
+      <c r="P56" s="52" t="n"/>
+      <c r="Q56" s="66">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="Q57" s="27">
+      <c r="A57" s="52" t="n"/>
+      <c r="B57" s="52" t="n"/>
+      <c r="C57" s="52" t="n"/>
+      <c r="D57" s="52" t="n"/>
+      <c r="E57" s="52" t="n"/>
+      <c r="F57" s="52" t="n"/>
+      <c r="G57" s="52" t="n"/>
+      <c r="H57" s="52" t="n"/>
+      <c r="I57" s="52" t="n"/>
+      <c r="J57" s="52" t="n"/>
+      <c r="K57" s="52" t="n"/>
+      <c r="L57" s="52" t="n"/>
+      <c r="M57" s="52" t="n"/>
+      <c r="N57" s="52" t="n"/>
+      <c r="O57" s="52" t="n"/>
+      <c r="P57" s="52" t="n"/>
+      <c r="Q57" s="66">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="Q58" s="27">
+      <c r="A58" s="52" t="n"/>
+      <c r="B58" s="52" t="n"/>
+      <c r="C58" s="52" t="n"/>
+      <c r="D58" s="52" t="n"/>
+      <c r="E58" s="52" t="n"/>
+      <c r="F58" s="52" t="n"/>
+      <c r="G58" s="52" t="n"/>
+      <c r="H58" s="52" t="n"/>
+      <c r="I58" s="52" t="n"/>
+      <c r="J58" s="52" t="n"/>
+      <c r="K58" s="52" t="n"/>
+      <c r="L58" s="52" t="n"/>
+      <c r="M58" s="52" t="n"/>
+      <c r="N58" s="52" t="n"/>
+      <c r="O58" s="52" t="n"/>
+      <c r="P58" s="52" t="n"/>
+      <c r="Q58" s="66">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="Q59" s="27">
+      <c r="A59" s="52" t="n"/>
+      <c r="B59" s="52" t="n"/>
+      <c r="C59" s="52" t="n"/>
+      <c r="D59" s="52" t="n"/>
+      <c r="E59" s="52" t="n"/>
+      <c r="F59" s="52" t="n"/>
+      <c r="G59" s="52" t="n"/>
+      <c r="H59" s="52" t="n"/>
+      <c r="I59" s="52" t="n"/>
+      <c r="J59" s="52" t="n"/>
+      <c r="K59" s="52" t="n"/>
+      <c r="L59" s="52" t="n"/>
+      <c r="M59" s="52" t="n"/>
+      <c r="N59" s="52" t="n"/>
+      <c r="O59" s="52" t="n"/>
+      <c r="P59" s="52" t="n"/>
+      <c r="Q59" s="66">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="Q60" s="27">
+      <c r="A60" s="52" t="n"/>
+      <c r="B60" s="52" t="n"/>
+      <c r="C60" s="52" t="n"/>
+      <c r="D60" s="52" t="n"/>
+      <c r="E60" s="52" t="n"/>
+      <c r="F60" s="52" t="n"/>
+      <c r="G60" s="52" t="n"/>
+      <c r="H60" s="52" t="n"/>
+      <c r="I60" s="52" t="n"/>
+      <c r="J60" s="52" t="n"/>
+      <c r="K60" s="52" t="n"/>
+      <c r="L60" s="52" t="n"/>
+      <c r="M60" s="52" t="n"/>
+      <c r="N60" s="52" t="n"/>
+      <c r="O60" s="52" t="n"/>
+      <c r="P60" s="52" t="n"/>
+      <c r="Q60" s="66">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="Q61" s="27">
+      <c r="A61" s="52" t="n"/>
+      <c r="B61" s="52" t="n"/>
+      <c r="C61" s="52" t="n"/>
+      <c r="D61" s="52" t="n"/>
+      <c r="E61" s="52" t="n"/>
+      <c r="F61" s="52" t="n"/>
+      <c r="G61" s="52" t="n"/>
+      <c r="H61" s="52" t="n"/>
+      <c r="I61" s="52" t="n"/>
+      <c r="J61" s="52" t="n"/>
+      <c r="K61" s="52" t="n"/>
+      <c r="L61" s="52" t="n"/>
+      <c r="M61" s="52" t="n"/>
+      <c r="N61" s="52" t="n"/>
+      <c r="O61" s="52" t="n"/>
+      <c r="P61" s="52" t="n"/>
+      <c r="Q61" s="66">
         <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="Q62" s="27">
+      <c r="A62" s="52" t="n"/>
+      <c r="B62" s="52" t="n"/>
+      <c r="C62" s="52" t="n"/>
+      <c r="D62" s="52" t="n"/>
+      <c r="E62" s="52" t="n"/>
+      <c r="F62" s="52" t="n"/>
+      <c r="G62" s="52" t="n"/>
+      <c r="H62" s="52" t="n"/>
+      <c r="I62" s="52" t="n"/>
+      <c r="J62" s="52" t="n"/>
+      <c r="K62" s="52" t="n"/>
+      <c r="L62" s="52" t="n"/>
+      <c r="M62" s="52" t="n"/>
+      <c r="N62" s="52" t="n"/>
+      <c r="O62" s="52" t="n"/>
+      <c r="P62" s="52" t="n"/>
+      <c r="Q62" s="66">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
@@ -2643,296 +3451,666 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="68" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="n"/>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>EL-009</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>فیزیکال 921600</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>اسکوپ روی PA9/PA10</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
         <is>
           <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
 گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
 گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>921600 8N1 با درام DDR و بدون خطا</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>بدون فریم خراب در 60s</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="56" t="n"/>
+      <c r="Q5" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="27">
+      <c r="A6" s="52" t="n"/>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="52" t="n"/>
+      <c r="I6" s="52" t="n"/>
+      <c r="J6" s="52" t="n"/>
+      <c r="K6" s="52" t="n"/>
+      <c r="L6" s="52" t="n"/>
+      <c r="M6" s="52" t="n"/>
+      <c r="N6" s="52" t="n"/>
+      <c r="O6" s="52" t="n"/>
+      <c r="P6" s="52" t="n"/>
+      <c r="Q6" s="66">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="27">
+      <c r="A7" s="52" t="n"/>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="52" t="n"/>
+      <c r="I7" s="52" t="n"/>
+      <c r="J7" s="52" t="n"/>
+      <c r="K7" s="52" t="n"/>
+      <c r="L7" s="52" t="n"/>
+      <c r="M7" s="52" t="n"/>
+      <c r="N7" s="52" t="n"/>
+      <c r="O7" s="52" t="n"/>
+      <c r="P7" s="52" t="n"/>
+      <c r="Q7" s="66">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="27">
+      <c r="A8" s="52" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="52" t="n"/>
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="66">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="27">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="52" t="n"/>
+      <c r="P9" s="52" t="n"/>
+      <c r="Q9" s="66">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="27">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+      <c r="N10" s="52" t="n"/>
+      <c r="O10" s="52" t="n"/>
+      <c r="P10" s="52" t="n"/>
+      <c r="Q10" s="66">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="27">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="52" t="n"/>
+      <c r="P11" s="52" t="n"/>
+      <c r="Q11" s="66">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="27">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="52" t="n"/>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+      <c r="N12" s="52" t="n"/>
+      <c r="O12" s="52" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="66">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="27">
+      <c r="A13" s="52" t="n"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+      <c r="N13" s="52" t="n"/>
+      <c r="O13" s="52" t="n"/>
+      <c r="P13" s="52" t="n"/>
+      <c r="Q13" s="66">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="27">
+      <c r="A14" s="52" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+      <c r="N14" s="52" t="n"/>
+      <c r="O14" s="52" t="n"/>
+      <c r="P14" s="52" t="n"/>
+      <c r="Q14" s="66">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="27">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="52" t="n"/>
+      <c r="O15" s="52" t="n"/>
+      <c r="P15" s="52" t="n"/>
+      <c r="Q15" s="66">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="27">
+      <c r="A16" s="52" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="52" t="n"/>
+      <c r="K16" s="52" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+      <c r="N16" s="52" t="n"/>
+      <c r="O16" s="52" t="n"/>
+      <c r="P16" s="52" t="n"/>
+      <c r="Q16" s="66">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="27">
+      <c r="A17" s="52" t="n"/>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="52" t="n"/>
+      <c r="M17" s="52" t="n"/>
+      <c r="N17" s="52" t="n"/>
+      <c r="O17" s="52" t="n"/>
+      <c r="P17" s="52" t="n"/>
+      <c r="Q17" s="66">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="27">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="52" t="n"/>
+      <c r="K18" s="52" t="n"/>
+      <c r="L18" s="52" t="n"/>
+      <c r="M18" s="52" t="n"/>
+      <c r="N18" s="52" t="n"/>
+      <c r="O18" s="52" t="n"/>
+      <c r="P18" s="52" t="n"/>
+      <c r="Q18" s="66">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="27">
+      <c r="A19" s="52" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="52" t="n"/>
+      <c r="O19" s="52" t="n"/>
+      <c r="P19" s="52" t="n"/>
+      <c r="Q19" s="66">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="27">
+      <c r="A20" s="52" t="n"/>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="52" t="n"/>
+      <c r="P20" s="52" t="n"/>
+      <c r="Q20" s="66">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="27">
+      <c r="A21" s="52" t="n"/>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="52" t="n"/>
+      <c r="K21" s="52" t="n"/>
+      <c r="L21" s="52" t="n"/>
+      <c r="M21" s="52" t="n"/>
+      <c r="N21" s="52" t="n"/>
+      <c r="O21" s="52" t="n"/>
+      <c r="P21" s="52" t="n"/>
+      <c r="Q21" s="66">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="27">
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="52" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="52" t="n"/>
+      <c r="K22" s="52" t="n"/>
+      <c r="L22" s="52" t="n"/>
+      <c r="M22" s="52" t="n"/>
+      <c r="N22" s="52" t="n"/>
+      <c r="O22" s="52" t="n"/>
+      <c r="P22" s="52" t="n"/>
+      <c r="Q22" s="66">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="27">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="52" t="n"/>
+      <c r="K23" s="52" t="n"/>
+      <c r="L23" s="52" t="n"/>
+      <c r="M23" s="52" t="n"/>
+      <c r="N23" s="52" t="n"/>
+      <c r="O23" s="52" t="n"/>
+      <c r="P23" s="52" t="n"/>
+      <c r="Q23" s="66">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="27">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="66">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="27">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="52" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="66">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -2979,129 +4157,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="45" t="inlineStr">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="68" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="n"/>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>EL-012</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>فعال‌سازی یک‌خطی</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>MODULE_ESP=0</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: بیلد را با MODULE_ESP=0 بگیر و رفتار عادی برد را یک بار ببین.
 گام ۲: فقط MODULE_ESP را 1 کن و دوباره بیلد بگیر (هیچ تغییر دیگری نده).
@@ -3109,167 +4337,487 @@
 گام ۴: لینک باید بدون دست‌کاری بقیهٔ ماژول‌ها بالا بیاید و پنل آنلاین شود.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>لینک بدون هیچ تغییر دیگر بالا می‌آید؛ سایر ماژول‌ها دست‌نخورده</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>پنل آنلاین</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="59" t="n"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="n"/>
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="P5" s="61" t="n"/>
+      <c r="Q5" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="27">
+      <c r="A6" s="52" t="n"/>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="52" t="n"/>
+      <c r="I6" s="52" t="n"/>
+      <c r="J6" s="52" t="n"/>
+      <c r="K6" s="52" t="n"/>
+      <c r="L6" s="52" t="n"/>
+      <c r="M6" s="52" t="n"/>
+      <c r="N6" s="52" t="n"/>
+      <c r="O6" s="52" t="n"/>
+      <c r="P6" s="52" t="n"/>
+      <c r="Q6" s="66">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="27">
+      <c r="A7" s="52" t="n"/>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="52" t="n"/>
+      <c r="I7" s="52" t="n"/>
+      <c r="J7" s="52" t="n"/>
+      <c r="K7" s="52" t="n"/>
+      <c r="L7" s="52" t="n"/>
+      <c r="M7" s="52" t="n"/>
+      <c r="N7" s="52" t="n"/>
+      <c r="O7" s="52" t="n"/>
+      <c r="P7" s="52" t="n"/>
+      <c r="Q7" s="66">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="27">
+      <c r="A8" s="52" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="52" t="n"/>
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="66">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="27">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="52" t="n"/>
+      <c r="P9" s="52" t="n"/>
+      <c r="Q9" s="66">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="27">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+      <c r="N10" s="52" t="n"/>
+      <c r="O10" s="52" t="n"/>
+      <c r="P10" s="52" t="n"/>
+      <c r="Q10" s="66">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="27">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="52" t="n"/>
+      <c r="P11" s="52" t="n"/>
+      <c r="Q11" s="66">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="27">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="52" t="n"/>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+      <c r="N12" s="52" t="n"/>
+      <c r="O12" s="52" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="66">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="27">
+      <c r="A13" s="52" t="n"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+      <c r="N13" s="52" t="n"/>
+      <c r="O13" s="52" t="n"/>
+      <c r="P13" s="52" t="n"/>
+      <c r="Q13" s="66">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="27">
+      <c r="A14" s="52" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+      <c r="N14" s="52" t="n"/>
+      <c r="O14" s="52" t="n"/>
+      <c r="P14" s="52" t="n"/>
+      <c r="Q14" s="66">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="27">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="52" t="n"/>
+      <c r="O15" s="52" t="n"/>
+      <c r="P15" s="52" t="n"/>
+      <c r="Q15" s="66">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="27">
+      <c r="A16" s="52" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="52" t="n"/>
+      <c r="K16" s="52" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+      <c r="N16" s="52" t="n"/>
+      <c r="O16" s="52" t="n"/>
+      <c r="P16" s="52" t="n"/>
+      <c r="Q16" s="66">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="27">
+      <c r="A17" s="52" t="n"/>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="52" t="n"/>
+      <c r="M17" s="52" t="n"/>
+      <c r="N17" s="52" t="n"/>
+      <c r="O17" s="52" t="n"/>
+      <c r="P17" s="52" t="n"/>
+      <c r="Q17" s="66">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="27">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="52" t="n"/>
+      <c r="K18" s="52" t="n"/>
+      <c r="L18" s="52" t="n"/>
+      <c r="M18" s="52" t="n"/>
+      <c r="N18" s="52" t="n"/>
+      <c r="O18" s="52" t="n"/>
+      <c r="P18" s="52" t="n"/>
+      <c r="Q18" s="66">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="27">
+      <c r="A19" s="52" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="52" t="n"/>
+      <c r="O19" s="52" t="n"/>
+      <c r="P19" s="52" t="n"/>
+      <c r="Q19" s="66">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="27">
+      <c r="A20" s="52" t="n"/>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="52" t="n"/>
+      <c r="P20" s="52" t="n"/>
+      <c r="Q20" s="66">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="27">
+      <c r="A21" s="52" t="n"/>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="52" t="n"/>
+      <c r="K21" s="52" t="n"/>
+      <c r="L21" s="52" t="n"/>
+      <c r="M21" s="52" t="n"/>
+      <c r="N21" s="52" t="n"/>
+      <c r="O21" s="52" t="n"/>
+      <c r="P21" s="52" t="n"/>
+      <c r="Q21" s="66">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="27">
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="52" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="52" t="n"/>
+      <c r="K22" s="52" t="n"/>
+      <c r="L22" s="52" t="n"/>
+      <c r="M22" s="52" t="n"/>
+      <c r="N22" s="52" t="n"/>
+      <c r="O22" s="52" t="n"/>
+      <c r="P22" s="52" t="n"/>
+      <c r="Q22" s="66">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="27">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="52" t="n"/>
+      <c r="K23" s="52" t="n"/>
+      <c r="L23" s="52" t="n"/>
+      <c r="M23" s="52" t="n"/>
+      <c r="N23" s="52" t="n"/>
+      <c r="O23" s="52" t="n"/>
+      <c r="P23" s="52" t="n"/>
+      <c r="Q23" s="66">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="27">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="66">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="27">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="52" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="66">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -3304,201 +4852,207 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول EspLink</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-      <c r="E1" s="39" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="70" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>سرعت لینک</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>921600 8N1، DMA دوطرفه</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>بدون بار CPU</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>bsp_uart.c</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>پروتکل v1.2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>فریم</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>AA 55 type len payload XOR، payload≤112</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>TLM=84B، BULK=101B</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="73" t="inlineStr">
         <is>
           <t>ESP_AGENT_SPEC.md §2</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>اندیان کوچک</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>ددمن مود دستی</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>هر فریم معتبر، سقف 3s سکوت</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>خروج خودکار + duty صفر</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>CHG_MANUAL_WATCHDOG_MS</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>keepalive پنل = 1s</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>پارامترها</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>ID0..19 فقط RAM</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>کلمپ + PARAM_REPORT</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>README محدودیت‌های سمت ESP</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>ری‌استارت → پیش‌فرض</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>پنل</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>esp_link_panel/ نسخهٔ ممیزی 32098b4</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>keepalive مستقل از مرورگر + محافظ پنل بسته 10s</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>README EspLink</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>به‌روزرسانی فونت با /f.css?v=2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>magic + commit grant؛ flush NVM پیش از arm</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="72" t="inlineStr">
         <is>
           <t>flush failure = no reset و grant retained؛ success = reset one-shot</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
@@ -3543,93 +5097,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول EspLink</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="38" t="n"/>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="39" t="n"/>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
+      <c r="L2" s="69" t="n"/>
+      <c r="M2" s="70" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="71" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="28" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="71" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="71" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="28" t="inlineStr">
+      <c r="L3" s="71" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="71" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -3660,211 +5226,235 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول EspLink</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>EspLink — پل ESP و پروتکل v1.2</t>
         </is>
       </c>
+      <c r="C5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — پوشش v1.2)</t>
         </is>
       </c>
+      <c r="C6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>پنل ESP + اسکوپ + مانیتور UART</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="52" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="75" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="75">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="75">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="75" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="75">
         <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="75" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="75">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="75" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="74" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3891,117 +5481,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="33" t="inlineStr">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="33" t="inlineStr">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="33" t="inlineStr">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
+      <c r="B13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
+      <c r="B14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
+      <c r="B15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
+      <c r="B16" s="52" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
+      <c r="B17" s="52" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4023,60 +5632,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول لینک ESP (EspLink)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>EspLink_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="52" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="52" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,6 +188,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -232,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -312,11 +316,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -509,6 +514,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -875,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -940,6 +948,14 @@
       <c r="A10" s="48" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="78" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -998,22 +1014,6 @@
           <t>برنامهٔ تست عملی — ماژول EspLink</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
-      <c r="D1" s="52" t="n"/>
-      <c r="E1" s="52" t="n"/>
-      <c r="F1" s="52" t="n"/>
-      <c r="G1" s="52" t="n"/>
-      <c r="H1" s="52" t="n"/>
-      <c r="I1" s="52" t="n"/>
-      <c r="J1" s="52" t="n"/>
-      <c r="K1" s="52" t="n"/>
-      <c r="L1" s="52" t="n"/>
-      <c r="M1" s="52" t="n"/>
-      <c r="N1" s="52" t="n"/>
-      <c r="O1" s="52" t="n"/>
-      <c r="P1" s="52" t="n"/>
-      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
@@ -1021,22 +1021,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-      <c r="D2" s="52" t="n"/>
-      <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
-      <c r="G2" s="52" t="n"/>
-      <c r="H2" s="52" t="n"/>
-      <c r="I2" s="52" t="n"/>
-      <c r="J2" s="52" t="n"/>
-      <c r="K2" s="52" t="n"/>
-      <c r="L2" s="52" t="n"/>
-      <c r="M2" s="52" t="n"/>
-      <c r="N2" s="52" t="n"/>
-      <c r="O2" s="52" t="n"/>
-      <c r="P2" s="52" t="n"/>
-      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -1044,22 +1028,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
-      <c r="I3" s="52" t="n"/>
-      <c r="J3" s="52" t="n"/>
-      <c r="K3" s="52" t="n"/>
-      <c r="L3" s="52" t="n"/>
-      <c r="M3" s="52" t="n"/>
-      <c r="N3" s="52" t="n"/>
-      <c r="O3" s="52" t="n"/>
-      <c r="P3" s="52" t="n"/>
-      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="49" t="inlineStr">
@@ -1109,7 +1077,7 @@
       </c>
       <c r="J4" s="49" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="49" t="inlineStr">
@@ -1197,27 +1165,26 @@
       </c>
       <c r="J5" s="54" t="inlineStr">
         <is>
-          <t>بالا آمدن پنل و عدد زنده = قبول؛ بی‌ارتباطی = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="54" t="inlineStr"/>
+          <t>باید ببینید: پنل بالا می‌آید و عددهای زندهٔ دستگاه را نشان می‌دهد. اگر پنل نیامد یا عددی نبود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="54" t="n"/>
       <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="54" t="inlineStr"/>
-      <c r="N5" s="54" t="inlineStr"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
       <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="56" t="inlineStr"/>
-      <c r="Q5" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P5" s="56" t="n"/>
+      <c r="Q5" s="58">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
@@ -1270,205 +1237,202 @@
       </c>
       <c r="J6" s="59" t="inlineStr">
         <is>
-          <t>نزدیکی عددها و تازگی = قبول؛ عدد یخ‌زده یا خیلی دور = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="59" t="inlineStr"/>
+          <t>باید ببینید: عددهای پنل زنده‌اند، نزدیک مولتی‌مترند و با تغییر ولتاژ همان لحظه عوض می‌شوند. اگر عدد یخ زد یا خیلی دور بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="59" t="n"/>
       <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="59" t="inlineStr"/>
-      <c r="N6" s="59" t="inlineStr"/>
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="n"/>
       <c r="O6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="61" t="inlineStr"/>
-      <c r="Q6" s="62" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P6" s="61" t="n"/>
+      <c r="Q6" s="62">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="53" t="inlineStr">
         <is>
-          <t>EL-003</t>
-        </is>
-      </c>
-      <c r="B7" s="54" t="inlineStr">
-        <is>
-          <t>GET_PARAMS → BULK</t>
-        </is>
-      </c>
-      <c r="C7" s="55" t="inlineStr">
+          <t>EL-004</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>SET_PARAM → REPORT</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="54" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E7" s="54" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل فهرست پارامترها را کامل بخوان.
-گام ۲: چند مقدار معلوم (مثلاً سقف جریان شارژ) را با رفتار واقعی دستگاه مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F7" s="56" t="inlineStr">
-        <is>
-          <t>خواندن کامل پارامترها از پنل</t>
-        </is>
-      </c>
-      <c r="G7" s="56" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H7" s="54" t="inlineStr">
-        <is>
-          <t>همهٔ پارامترها با مقدارهای واقعی دستگاه برمی‌گردند</t>
-        </is>
-      </c>
-      <c r="I7" s="54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="54" t="inlineStr">
-        <is>
-          <t>کامل و درست برگشتن فهرست = قبول؛ مقدار خالی یا اشتباه = رد</t>
-        </is>
-      </c>
-      <c r="K7" s="54" t="inlineStr"/>
-      <c r="L7" s="57" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="54" t="inlineStr"/>
-      <c r="N7" s="54" t="inlineStr"/>
-      <c r="O7" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="56" t="inlineStr"/>
-      <c r="Q7" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>EL-004</t>
-        </is>
-      </c>
-      <c r="B8" s="59" t="inlineStr">
-        <is>
-          <t>SET_PARAM → REPORT</t>
-        </is>
-      </c>
-      <c r="C8" s="60" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="59" t="inlineStr">
-        <is>
-          <t>پنل باز و دستگاه روشن است</t>
-        </is>
-      </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک پارامتر بی‌خطر را از پنل عوض کن (مثلاً بلندی/دورهٔ بوق).
 گام ۲: رفتار دستگاه را ببین که همان لحظه عوض شود.
 گام ۳: مقدار را به حالت اول برگردان.</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>تغییر یک پارامتر از پنل</t>
         </is>
       </c>
-      <c r="G8" s="61" t="inlineStr">
+      <c r="G7" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr">
+      <c r="H7" s="59" t="inlineStr">
         <is>
           <t>تغییر پنل همان لحظه روی دستگاه اثر می‌گذارد</t>
         </is>
       </c>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="I7" s="59" t="inlineStr">
         <is>
           <t>تا تغییر بعدی</t>
         </is>
       </c>
-      <c r="J8" s="59" t="inlineStr">
-        <is>
-          <t>اثر فوری = قبول؛ بی‌اثری یا نیاز به ریست = رد</t>
-        </is>
-      </c>
-      <c r="K8" s="59" t="inlineStr"/>
-      <c r="L8" s="57" t="inlineStr">
+      <c r="J7" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: تغییر از پنل همان لحظه روی دستگاه اثر می‌گذارد. اگر بی‌اثر بود یا نیاز به ریست داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K7" s="59" t="n"/>
+      <c r="L7" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="59" t="inlineStr"/>
-      <c r="N8" s="59" t="inlineStr"/>
-      <c r="O8" s="61" t="inlineStr">
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="n"/>
+      <c r="O7" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="61" t="inlineStr"/>
-      <c r="Q8" s="62" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="P7" s="61" t="n"/>
+      <c r="Q7" s="62">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>EL-005</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>پارامتر ۱۹ مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="55" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D8" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E9" s="54" t="inlineStr">
+      <c r="E8" s="54" t="inlineStr">
         <is>
           <t>گام ۱: پارامتر مود تست دستی شارژر (شمارهٔ ۱۹) را از پنل روشن کن.
 گام ۲: ببین شارژر به مود دستی می‌رود.
 گام ۳: خاموشش کن و برگشت به شارژ خودکار را ببین.</t>
         </is>
       </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>روشن/خاموش پارامتر ۱۹ از پنل</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H8" s="54" t="inlineStr">
+        <is>
+          <t>با روشن‌کردن، شارژر دستی و با خاموش‌کردن، خودکار می‌شود</t>
+        </is>
+      </c>
+      <c r="I8" s="54" t="inlineStr">
+        <is>
+          <t>تابع پنل</t>
+        </is>
+      </c>
+      <c r="J8" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: با روشن‌کردن مود دستی شارژر دستی و با خاموش‌کردنش خودکار می‌شود. اگر در یک مود گیر کرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K8" s="54" t="n"/>
+      <c r="L8" s="57" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="54" t="n"/>
+      <c r="N8" s="54" t="n"/>
+      <c r="O8" s="56" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="56" t="n"/>
+      <c r="Q8" s="58">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>EL-003</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>GET_PARAMS → BULK</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>پنل باز و دستگاه روشن است</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل فهرست پارامترها را کامل بخوان.
+گام ۲: چند مقدار معلوم (مثلاً سقف جریان شارژ) را با رفتار واقعی دستگاه مقایسه کن.</t>
+        </is>
+      </c>
       <c r="F9" s="56" t="inlineStr">
         <is>
-          <t>روشن/خاموش پارامتر ۱۹ از پنل</t>
+          <t>خواندن کامل پارامترها از پنل</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
@@ -1478,37 +1442,36 @@
       </c>
       <c r="H9" s="54" t="inlineStr">
         <is>
-          <t>با روشن‌کردن، شارژر دستی و با خاموش‌کردن، خودکار می‌شود</t>
+          <t>همهٔ پارامترها با مقدارهای واقعی دستگاه برمی‌گردند</t>
         </is>
       </c>
       <c r="I9" s="54" t="inlineStr">
         <is>
-          <t>تابع پنل</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" s="54" t="inlineStr">
         <is>
-          <t>رفت‌وبرگشت درست مود = قبول؛ گیرکردن در یک مود = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="54" t="inlineStr"/>
+          <t>باید ببینید: همهٔ پارامترها با مقدارهای واقعی دستگاه در پنل برمی‌گردند. اگر مقدار خالی یا اشتباه بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K9" s="54" t="n"/>
       <c r="L9" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="54" t="inlineStr"/>
-      <c r="N9" s="54" t="inlineStr"/>
+      <c r="M9" s="54" t="n"/>
+      <c r="N9" s="54" t="n"/>
       <c r="O9" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="56" t="inlineStr"/>
-      <c r="Q9" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P9" s="56" t="n"/>
+      <c r="Q9" s="58">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
@@ -1560,1840 +1523,1707 @@
       </c>
       <c r="J10" s="59" t="inlineStr">
         <is>
-          <t>زنده‌ماندن ارتباط = قبول؛ افتادن بی‌دلیل = رد</t>
-        </is>
-      </c>
-      <c r="K10" s="59" t="inlineStr"/>
+          <t>باید ببینید: ارتباط در تمام مدت زنده می‌ماند و عددها تازه می‌شوند. اگر بی‌دلیل افتاد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K10" s="59" t="n"/>
       <c r="L10" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="59" t="inlineStr"/>
-      <c r="N10" s="59" t="inlineStr"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
       <c r="O10" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="61" t="inlineStr"/>
-      <c r="Q10" s="62" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
+      <c r="P10" s="61" t="n"/>
+      <c r="Q10" s="62">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="53" t="inlineStr">
         <is>
-          <t>EL-007</t>
-        </is>
-      </c>
-      <c r="B11" s="54" t="inlineStr">
-        <is>
-          <t>سرریز ring</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
+          <t>EL-010</t>
+        </is>
+      </c>
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>فلگ‌های تله‌متری</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="54" t="inlineStr">
-        <is>
-          <t>پنل باز و دستگاه روشن است</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="inlineStr">
-        <is>
-          <t>گام ۱: چند پارامتر را پشت سر هم و سریع از پنل عوض کن.
-گام ۲: بعد همه را یکی‌یکی بخوان و با چیزی که فرستادی مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F11" s="56" t="inlineStr">
-        <is>
-          <t>تغییر سریع چند پارامتر</t>
-        </is>
-      </c>
-      <c r="G11" s="56" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H11" s="54" t="inlineStr">
-        <is>
-          <t>هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند</t>
-        </is>
-      </c>
-      <c r="I11" s="54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="54" t="inlineStr">
-        <is>
-          <t>درست نشستن همهٔ تغییرها = قبول؛ گم‌شدن یا هنگ = رد</t>
-        </is>
-      </c>
-      <c r="K11" s="54" t="inlineStr"/>
-      <c r="L11" s="57" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="54" t="inlineStr"/>
-      <c r="N11" s="54" t="inlineStr"/>
-      <c r="O11" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="56" t="inlineStr"/>
-      <c r="Q11" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="53" t="inlineStr">
-        <is>
-          <t>EL-008</t>
-        </is>
-      </c>
-      <c r="B12" s="59" t="inlineStr">
-        <is>
-          <t>محدودیت burst</t>
-        </is>
-      </c>
-      <c r="C12" s="61" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D12" s="59" t="inlineStr">
-        <is>
-          <t>پنل باز و دستگاه روشن است</t>
-        </is>
-      </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>گام ۱: در مدت کوتاه دستورهای زیادی از پنل بفرست (خواندن و نوشتن پشت سر هم).
-گام ۲: رفتار دستگاه و پنل را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F12" s="61" t="inlineStr">
-        <is>
-          <t>بار زیاد دستور از پنل</t>
-        </is>
-      </c>
-      <c r="G12" s="61" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H12" s="59" t="inlineStr">
-        <is>
-          <t>دستگاه به نوبت و کامل جواب می‌دهد؛ هنگ، ریست یا جواب نصفه نیست</t>
-        </is>
-      </c>
-      <c r="I12" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="59" t="inlineStr">
-        <is>
-          <t>جواب کامل زیر بار = قبول؛ هنگ یا ریست = رد</t>
-        </is>
-      </c>
-      <c r="K12" s="59" t="inlineStr"/>
-      <c r="L12" s="57" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="59" t="inlineStr"/>
-      <c r="N12" s="59" t="inlineStr"/>
-      <c r="O12" s="61" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="61" t="inlineStr"/>
-      <c r="Q12" s="62" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="53" t="inlineStr">
-        <is>
-          <t>EL-010</t>
-        </is>
-      </c>
-      <c r="B13" s="59" t="inlineStr">
-        <is>
-          <t>فلگ‌های تله‌متری</t>
-        </is>
-      </c>
-      <c r="C13" s="61" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>پنل باز؛ دستگاه با برق شهر در حال شارژ باتری است</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="E11" s="59" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
 گام ۲: در پنل ببین خطای ۶ و توقف شارژ نشان داده می‌شود.
 گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
         </is>
       </c>
-      <c r="F13" s="61" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>ساختن و پاک‌کردن خطای ۶</t>
         </is>
       </c>
-      <c r="G13" s="61" t="inlineStr">
+      <c r="G11" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="59" t="inlineStr">
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>پرچم خطا در پنل دقیقاً با چراغ‌های دستگاه یکی است</t>
         </is>
       </c>
-      <c r="I13" s="59" t="inlineStr">
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>هم‌گام با دستگاه</t>
         </is>
       </c>
-      <c r="J13" s="59" t="inlineStr">
-        <is>
-          <t>یکی‌بودن پنل و واقعیت = قبول؛ اختلاف = رد</t>
-        </is>
-      </c>
-      <c r="K13" s="59" t="inlineStr"/>
-      <c r="L13" s="57" t="inlineStr">
+      <c r="J11" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: پرچم خطا در پنل دقیقاً با چراغ‌های روی دستگاه یکی است. اگر اختلاف دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K11" s="59" t="n"/>
+      <c r="L11" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="59" t="inlineStr"/>
-      <c r="N13" s="59" t="inlineStr"/>
-      <c r="O13" s="61" t="inlineStr">
+      <c r="M11" s="59" t="n"/>
+      <c r="N11" s="59" t="n"/>
+      <c r="O11" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="61" t="inlineStr"/>
-      <c r="Q13" s="62" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="P11" s="61" t="n"/>
+      <c r="Q11" s="62">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>EL-011</t>
         </is>
       </c>
-      <c r="B14" s="54" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>state 9 و b5</t>
         </is>
       </c>
-      <c r="C14" s="55" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="54" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E14" s="54" t="inlineStr">
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را به شارژ بزن و وضعیت شارژر را در پنل بخوان.
 گام ۲: شارژ را قطع کن (برق شهر را بکش) و دوباره وضعیت را بخوان.
 گام ۳: هر دو را با چیزی که روی دستگاه می‌بینی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F14" s="56" t="inlineStr">
+      <c r="F12" s="56" t="inlineStr">
         <is>
           <t>شروع و قطع شارژ جلوی پنل</t>
         </is>
       </c>
-      <c r="G14" s="56" t="inlineStr">
+      <c r="G12" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="54" t="inlineStr">
+      <c r="H12" s="54" t="inlineStr">
         <is>
           <t>وضعیت شارژر در پنل در هر دو حالت با واقعیت یکی است</t>
         </is>
       </c>
-      <c r="I14" s="54" t="inlineStr">
+      <c r="I12" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="54" t="inlineStr">
-        <is>
-          <t>یکی‌بودن وضعیت‌ها = قبول؛ وضعیت دروغ در پنل = رد</t>
-        </is>
-      </c>
-      <c r="K14" s="54" t="inlineStr"/>
-      <c r="L14" s="57" t="inlineStr">
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: وضعیت شارژر در پنل در هر دو حالت با واقعیت دستگاه یکی است. اگر پنل وضعیت دروغ نشان داد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K12" s="54" t="n"/>
+      <c r="L12" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="54" t="inlineStr"/>
-      <c r="N14" s="54" t="inlineStr"/>
-      <c r="O14" s="56" t="inlineStr">
+      <c r="M12" s="54" t="n"/>
+      <c r="N12" s="54" t="n"/>
+      <c r="O12" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="56" t="inlineStr"/>
-      <c r="Q14" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="P12" s="56" t="n"/>
+      <c r="Q12" s="58">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>EL-013</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>کالیبراسیون و read-back</t>
         </is>
       </c>
-      <c r="C15" s="55" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="54" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
         <is>
           <t>پنل باز و راهنمای کالیبراسیون را می‌دانی</t>
         </is>
       </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ کالیبراسیون را بفرست.
 گام ۲: همان را از پنل بخوان (read-back).
 گام ۳: عدد برگشتی را با فرستاده مقایسه کن.</t>
         </is>
       </c>
-      <c r="F15" s="56" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>فرستادن و خواندن کالیبراسیون</t>
         </is>
       </c>
-      <c r="G15" s="56" t="inlineStr">
+      <c r="G13" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="54" t="inlineStr">
+      <c r="H13" s="54" t="inlineStr">
         <is>
           <t>عدد برگشتی دقیقاً همان فرستاده است</t>
         </is>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="I13" s="54" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J15" s="54" t="inlineStr">
-        <is>
-          <t>برابری عددها = قبول؛ اختلاف = رد</t>
-        </is>
-      </c>
-      <c r="K15" s="54" t="inlineStr">
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: عدد برگشتی از دستگاه دقیقاً همان عدد فرستاده‌شده است. اگر اختلاف دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K13" s="54" t="inlineStr">
         <is>
           <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
         </is>
       </c>
-      <c r="L15" s="57" t="inlineStr">
+      <c r="L13" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="54" t="inlineStr">
+      <c r="M13" s="54" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
         </is>
       </c>
-      <c r="N15" s="63" t="inlineStr">
+      <c r="N13" s="63" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O15" s="56" t="inlineStr">
+      <c r="O13" s="56" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P15" s="56" t="inlineStr"/>
-      <c r="Q15" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="P13" s="56" t="n"/>
+      <c r="Q13" s="58">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>پنل باز و یک جدول LUT ذخیره شده است</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E14" s="59" t="inlineStr">
         <is>
           <t>گام ۱: جدول را از پنل کامل بخوان.
 گام ۲: چند عددش را با جدولی که قبلاً فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F16" s="61" t="inlineStr">
+      <c r="F14" s="61" t="inlineStr">
         <is>
           <t>خواندن کامل جدول از پنل</t>
         </is>
       </c>
-      <c r="G16" s="61" t="inlineStr">
+      <c r="G14" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="59" t="inlineStr">
+      <c r="H14" s="59" t="inlineStr">
         <is>
           <t>جدول عددبه‌عدد همان ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست</t>
         </is>
       </c>
-      <c r="I16" s="59" t="inlineStr">
+      <c r="I14" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="59" t="inlineStr">
-        <is>
-          <t>برابری کامل = قبول؛ هر اختلاف = رد</t>
-        </is>
-      </c>
-      <c r="K16" s="59" t="inlineStr">
+      <c r="J14" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: جدول برگشتی عددبه‌عدد همان جدول ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست. اگر اختلافی دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K14" s="59" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L16" s="57" t="inlineStr">
+      <c r="L14" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="59" t="inlineStr">
+      <c r="M14" s="59" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N16" s="64" t="inlineStr">
+      <c r="N14" s="64" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O16" s="61" t="inlineStr">
+      <c r="O14" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P16" s="61" t="inlineStr"/>
-      <c r="Q16" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="67.5" customHeight="1">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="P14" s="61" t="n"/>
+      <c r="Q14" s="62">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="67.5" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B17" s="54" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C17" s="55" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="54" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
         <is>
           <t>پنل باز و جدول سالمی ذخیره است</t>
         </is>
       </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ صفر یا کانال ناموجود بفرست.
 گام ۲: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F17" s="56" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
         <is>
           <t>فرستادن نقطهٔ صفر/کانال بد</t>
         </is>
       </c>
-      <c r="G17" s="56" t="inlineStr">
+      <c r="G15" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H17" s="54" t="inlineStr">
+      <c r="H15" s="54" t="inlineStr">
         <is>
           <t>دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند</t>
         </is>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="I15" s="54" t="inlineStr">
         <is>
           <t>حفظ جدول قبلی</t>
         </is>
       </c>
-      <c r="J17" s="54" t="inlineStr">
-        <is>
-          <t>رد ورودی خراب = قبول؛ خراب‌شدن جدول = رد</t>
-        </is>
-      </c>
-      <c r="K17" s="54" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند. اگر جدول خراب شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K15" s="54" t="inlineStr">
         <is>
           <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
         </is>
       </c>
-      <c r="L17" s="57" t="inlineStr">
+      <c r="L15" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="54" t="inlineStr">
+      <c r="M15" s="54" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
         </is>
       </c>
-      <c r="N17" s="63" t="inlineStr">
+      <c r="N15" s="63" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O17" s="56" t="inlineStr">
+      <c r="O15" s="56" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P17" s="56" t="n"/>
-      <c r="Q17" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="81" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="P15" s="56" t="n"/>
+      <c r="Q15" s="58">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="81" customHeight="1">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>پنل باز و جدولی ذخیره است</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
 گام ۲: برق دستگاه را قطع و وصل کن.
 گام ۳: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F18" s="61" t="inlineStr">
+      <c r="F16" s="61" t="inlineStr">
         <is>
           <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G18" s="61" t="inlineStr">
+      <c r="G16" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="59" t="inlineStr">
+      <c r="H16" s="59" t="inlineStr">
         <is>
           <t>جدول پاک مانده و بعد از روشن‌شدن برنمی‌گردد</t>
         </is>
       </c>
-      <c r="I18" s="59" t="inlineStr">
+      <c r="I16" s="59" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J18" s="59" t="inlineStr">
-        <is>
-          <t>پاک‌ماندن = قبول؛ برگشتن جدول پاک‌شده = رد</t>
-        </is>
-      </c>
-      <c r="K18" s="59" t="inlineStr">
+      <c r="J16" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: جدول پاک‌شده بعد از خاموش و روشن‌کردن هم برنمی‌گردد. اگر برگشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K16" s="59" t="inlineStr">
         <is>
           <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
         </is>
       </c>
-      <c r="L18" s="57" t="inlineStr">
+      <c r="L16" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="59" t="inlineStr">
+      <c r="M16" s="59" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
         </is>
       </c>
-      <c r="N18" s="64" t="inlineStr">
+      <c r="N16" s="64" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O18" s="61" t="inlineStr">
+      <c r="O16" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="61" t="n"/>
-      <c r="Q18" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="P16" s="61" t="n"/>
+      <c r="Q16" s="62">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="67.5" customHeight="1">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B19" s="54" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C19" s="55" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="54" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه در حال کار است</t>
         </is>
       </c>
-      <c r="E19" s="54" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>گام ۱: کاری کن یک پیام هشدار (alert) در پنل بیاید (مثلاً یک خطای واقعی مثل قطع باتری).
 گام ۲: متن پیام را بخوان و تأییدش کن.
 گام ۳: ببین کار دستگاه حین پیام مختل نشده.</t>
         </is>
       </c>
-      <c r="F19" s="56" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
         <is>
           <t>هشدار واقعی در پنل</t>
         </is>
       </c>
-      <c r="G19" s="56" t="inlineStr">
+      <c r="G17" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="54" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد</t>
         </is>
       </c>
-      <c r="I19" s="54" t="inlineStr">
+      <c r="I17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="54" t="inlineStr">
-        <is>
-          <t>پیام درست بدون اختلال = قبول؛ هنگ یا پیام اشتباه = رد</t>
-        </is>
-      </c>
-      <c r="K19" s="54" t="n"/>
-      <c r="L19" s="65" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد. اگر هنگ یا پیام اشتباه دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K17" s="54" t="n"/>
+      <c r="L17" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M19" s="54" t="n"/>
-      <c r="N19" s="54" t="inlineStr">
+      <c r="M17" s="54" t="n"/>
+      <c r="N17" s="54" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O19" s="56" t="inlineStr">
+      <c r="O17" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P19" s="56" t="n"/>
-      <c r="Q19" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="P17" s="56" t="n"/>
+      <c r="Q17" s="58">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="67.5" customHeight="1">
+      <c r="A18" s="53" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>پنل باز است</t>
         </is>
       </c>
-      <c r="E20" s="59" t="inlineStr">
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید (confirm) بیاید.
 گام ۲: این بار لغو (Cancel) را بزن.
 گام ۳: مقدار را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="F18" s="61" t="inlineStr">
         <is>
           <t>لغو کردن پیام تأیید</t>
         </is>
       </c>
-      <c r="G20" s="61" t="inlineStr">
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="59" t="inlineStr">
+      <c r="H18" s="59" t="inlineStr">
         <is>
           <t>با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست</t>
         </is>
       </c>
-      <c r="I20" s="59" t="inlineStr">
+      <c r="I18" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="59" t="inlineStr">
-        <is>
-          <t>اعمال‌نشدن تغییر = قبول؛ اعمال با وجود لغو = رد</t>
-        </is>
-      </c>
-      <c r="K20" s="59" t="n"/>
-      <c r="L20" s="65" t="inlineStr">
+      <c r="J18" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست. اگر با وجود لغو اعمال شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K18" s="59" t="n"/>
+      <c r="L18" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M20" s="59" t="n"/>
-      <c r="N20" s="59" t="inlineStr">
+      <c r="M18" s="59" t="n"/>
+      <c r="N18" s="59" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O20" s="61" t="inlineStr">
+      <c r="O18" s="61" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P20" s="61" t="n"/>
-      <c r="Q20" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="P18" s="61" t="n"/>
+      <c r="Q18" s="62">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>EL-020</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>قفل ترکیب چشمک سبز در پنل</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
+گام ۲: ببین پنل چه می‌کند.
+گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
+        </is>
+      </c>
+      <c r="G19" s="61" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H19" s="59" t="inlineStr">
+        <is>
+          <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
+        </is>
+      </c>
+      <c r="I19" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: پنل جلوی ترکیب ناسازگار چشمک سبز را می‌گیرد و ترکیب درست را قبول می‌کند. اگر ترکیب بد به دستگاه رسید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K19" s="59" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L19" s="57" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="59" t="n"/>
+      <c r="N19" s="59" t="n"/>
+      <c r="O19" s="61" t="inlineStr">
+        <is>
+          <t>8efddaa</t>
+        </is>
+      </c>
+      <c r="P19" s="61" t="n"/>
+      <c r="Q19" s="62">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>EL-007</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>سرریز ring</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>پنل باز و دستگاه روشن است</t>
+        </is>
+      </c>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>گام ۱: چند پارامتر را پشت سر هم و سریع از پنل عوض کن.
+گام ۲: بعد همه را یکی‌یکی بخوان و با چیزی که فرستادی مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F20" s="56" t="inlineStr">
+        <is>
+          <t>تغییر سریع چند پارامتر</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H20" s="54" t="inlineStr">
+        <is>
+          <t>هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند</t>
+        </is>
+      </c>
+      <c r="I20" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند. اگر تغییری گم شد یا هنگ دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K20" s="54" t="n"/>
+      <c r="L20" s="57" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M20" s="54" t="n"/>
+      <c r="N20" s="54" t="n"/>
+      <c r="O20" s="56" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P20" s="56" t="n"/>
+      <c r="Q20" s="58">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
+          <t>EL-008</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>محدودیت burst</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="inlineStr">
+        <is>
+          <t>پنل باز و دستگاه روشن است</t>
+        </is>
+      </c>
+      <c r="E21" s="59" t="inlineStr">
+        <is>
+          <t>گام ۱: در مدت کوتاه دستورهای زیادی از پنل بفرست (خواندن و نوشتن پشت سر هم).
+گام ۲: رفتار دستگاه و پنل را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>بار زیاد دستور از پنل</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H21" s="59" t="inlineStr">
+        <is>
+          <t>دستگاه به نوبت و کامل جواب می‌دهد؛ هنگ، ریست یا جواب نصفه نیست</t>
+        </is>
+      </c>
+      <c r="I21" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: دستگاه زیر بار به نوبت و کامل جواب می‌دهد؛ هنگ، ریست یا جواب نصفه نیست. اگر هنگ یا ریست دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K21" s="59" t="n"/>
+      <c r="L21" s="57" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M21" s="59" t="n"/>
+      <c r="N21" s="59" t="n"/>
+      <c r="O21" s="61" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P21" s="61" t="n"/>
+      <c r="Q21" s="62">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B21" s="54" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E21" s="54" t="inlineStr">
+      <c r="E22" s="54" t="inlineStr">
         <is>
           <t>گام ۱: پشت سر هم چند پیام/دیالوگ بساز (چند خطا یا چند تأیید).
 گام ۲: ببین به نوبت نشان داده می‌شوند.
 گام ۳: همه را ببند.</t>
         </is>
       </c>
-      <c r="F21" s="56" t="inlineStr">
+      <c r="F22" s="56" t="inlineStr">
         <is>
           <t>چند پیام پشت سر هم</t>
         </is>
       </c>
-      <c r="G21" s="56" t="inlineStr">
+      <c r="G22" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H21" s="54" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند</t>
         </is>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="I22" s="54" t="inlineStr">
         <is>
           <t>صف مرتب</t>
         </is>
       </c>
-      <c r="J21" s="54" t="inlineStr">
-        <is>
-          <t>نوبت درست = قبول؛ گم‌شدن یا قاطی = رد</t>
-        </is>
-      </c>
-      <c r="K21" s="54" t="n"/>
-      <c r="L21" s="65" t="inlineStr">
+      <c r="J22" s="54" t="inlineStr">
+        <is>
+          <t>باید ببینید: پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند. اگر پیامی گم یا قاطی شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="54" t="n"/>
-      <c r="O21" s="56" t="inlineStr">
+      <c r="M22" s="54" t="n"/>
+      <c r="N22" s="54" t="n"/>
+      <c r="O22" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" s="56" t="n"/>
-      <c r="Q21" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>EL-020</t>
-        </is>
-      </c>
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t>قفل ترکیب چشمک سبز در پنل</t>
-        </is>
-      </c>
-      <c r="C22" s="60" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D22" s="59" t="inlineStr">
-        <is>
-          <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
-        </is>
-      </c>
-      <c r="E22" s="59" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
-گام ۲: ببین پنل چه می‌کند.
-گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
-        </is>
-      </c>
-      <c r="F22" s="61" t="inlineStr">
-        <is>
-          <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
-        </is>
-      </c>
-      <c r="G22" s="61" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H22" s="59" t="inlineStr">
-        <is>
-          <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
-        </is>
-      </c>
-      <c r="I22" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="59" t="inlineStr">
-        <is>
-          <t>گرفته‌شدن ترکیب بد و قبول ترکیب خوب = قبول؛ رسیدن ترکیب بد به دستگاه = رد</t>
-        </is>
-      </c>
-      <c r="K22" s="59" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="L22" s="57" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M22" s="59" t="n"/>
-      <c r="N22" s="59" t="n"/>
-      <c r="O22" s="61" t="inlineStr">
-        <is>
-          <t>8efddaa</t>
-        </is>
-      </c>
-      <c r="P22" s="61" t="n"/>
-      <c r="Q22" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="52" t="n"/>
-      <c r="B23" s="52" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52" t="n"/>
-      <c r="G23" s="52" t="n"/>
-      <c r="H23" s="52" t="n"/>
-      <c r="I23" s="52" t="n"/>
-      <c r="J23" s="52" t="n"/>
-      <c r="K23" s="52" t="n"/>
-      <c r="L23" s="52" t="n"/>
-      <c r="M23" s="52" t="n"/>
-      <c r="N23" s="52" t="n"/>
-      <c r="O23" s="52" t="n"/>
-      <c r="P23" s="52" t="n"/>
-      <c r="Q23" s="66">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="67.5" customHeight="1">
-      <c r="A24" s="52" t="n"/>
-      <c r="B24" s="52" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52" t="n"/>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="52" t="n"/>
-      <c r="I24" s="52" t="n"/>
-      <c r="J24" s="52" t="n"/>
-      <c r="K24" s="52" t="n"/>
-      <c r="L24" s="52" t="n"/>
-      <c r="M24" s="52" t="n"/>
-      <c r="N24" s="52" t="n"/>
-      <c r="O24" s="52" t="n"/>
-      <c r="P24" s="52" t="n"/>
-      <c r="Q24" s="66">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="P22" s="56" t="n"/>
+      <c r="Q22" s="58">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="79" t="n"/>
+      <c r="B23" s="79" t="n"/>
+      <c r="C23" s="79" t="n"/>
+      <c r="D23" s="79" t="n"/>
+      <c r="E23" s="79" t="n"/>
+      <c r="F23" s="79" t="n"/>
+      <c r="G23" s="79" t="n"/>
+      <c r="H23" s="79" t="n"/>
+      <c r="I23" s="79" t="n"/>
+      <c r="J23" s="79" t="n"/>
+      <c r="K23" s="79" t="n"/>
+      <c r="L23" s="79" t="n"/>
+      <c r="M23" s="79" t="n"/>
+      <c r="N23" s="79" t="n"/>
+      <c r="O23" s="79" t="n"/>
+      <c r="P23" s="79" t="n"/>
+      <c r="Q23" s="80" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="79" t="n"/>
+      <c r="B24" s="79" t="n"/>
+      <c r="C24" s="79" t="n"/>
+      <c r="D24" s="79" t="n"/>
+      <c r="E24" s="79" t="n"/>
+      <c r="F24" s="79" t="n"/>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="79" t="n"/>
+      <c r="I24" s="79" t="n"/>
+      <c r="J24" s="79" t="n"/>
+      <c r="K24" s="79" t="n"/>
+      <c r="L24" s="79" t="n"/>
+      <c r="M24" s="79" t="n"/>
+      <c r="N24" s="79" t="n"/>
+      <c r="O24" s="79" t="n"/>
+      <c r="P24" s="79" t="n"/>
+      <c r="Q24" s="80" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="n"/>
-      <c r="B25" s="52" t="n"/>
-      <c r="C25" s="52" t="n"/>
-      <c r="D25" s="52" t="n"/>
-      <c r="E25" s="52" t="n"/>
-      <c r="F25" s="52" t="n"/>
-      <c r="G25" s="52" t="n"/>
-      <c r="H25" s="52" t="n"/>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="52" t="n"/>
-      <c r="K25" s="52" t="n"/>
-      <c r="L25" s="52" t="n"/>
-      <c r="M25" s="52" t="n"/>
-      <c r="N25" s="52" t="n"/>
-      <c r="O25" s="52" t="n"/>
-      <c r="P25" s="52" t="n"/>
-      <c r="Q25" s="66">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A25" s="79" t="n"/>
+      <c r="B25" s="79" t="n"/>
+      <c r="C25" s="79" t="n"/>
+      <c r="D25" s="79" t="n"/>
+      <c r="E25" s="79" t="n"/>
+      <c r="F25" s="79" t="n"/>
+      <c r="G25" s="79" t="n"/>
+      <c r="H25" s="79" t="n"/>
+      <c r="I25" s="79" t="n"/>
+      <c r="J25" s="79" t="n"/>
+      <c r="K25" s="79" t="n"/>
+      <c r="L25" s="79" t="n"/>
+      <c r="M25" s="79" t="n"/>
+      <c r="N25" s="79" t="n"/>
+      <c r="O25" s="79" t="n"/>
+      <c r="P25" s="79" t="n"/>
+      <c r="Q25" s="80" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="n"/>
-      <c r="B26" s="52" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="52" t="n"/>
-      <c r="E26" s="52" t="n"/>
-      <c r="F26" s="52" t="n"/>
-      <c r="G26" s="52" t="n"/>
-      <c r="H26" s="52" t="n"/>
-      <c r="I26" s="52" t="n"/>
-      <c r="J26" s="52" t="n"/>
-      <c r="K26" s="52" t="n"/>
-      <c r="L26" s="52" t="n"/>
-      <c r="M26" s="52" t="n"/>
-      <c r="N26" s="52" t="n"/>
-      <c r="O26" s="52" t="n"/>
-      <c r="P26" s="52" t="n"/>
-      <c r="Q26" s="66">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A26" s="79" t="n"/>
+      <c r="B26" s="79" t="n"/>
+      <c r="C26" s="79" t="n"/>
+      <c r="D26" s="79" t="n"/>
+      <c r="E26" s="79" t="n"/>
+      <c r="F26" s="79" t="n"/>
+      <c r="G26" s="79" t="n"/>
+      <c r="H26" s="79" t="n"/>
+      <c r="I26" s="79" t="n"/>
+      <c r="J26" s="79" t="n"/>
+      <c r="K26" s="79" t="n"/>
+      <c r="L26" s="79" t="n"/>
+      <c r="M26" s="79" t="n"/>
+      <c r="N26" s="79" t="n"/>
+      <c r="O26" s="79" t="n"/>
+      <c r="P26" s="79" t="n"/>
+      <c r="Q26" s="80" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n"/>
-      <c r="B27" s="52" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-      <c r="E27" s="52" t="n"/>
-      <c r="F27" s="52" t="n"/>
-      <c r="G27" s="52" t="n"/>
-      <c r="H27" s="52" t="n"/>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="52" t="n"/>
-      <c r="K27" s="52" t="n"/>
-      <c r="L27" s="52" t="n"/>
-      <c r="M27" s="52" t="n"/>
-      <c r="N27" s="52" t="n"/>
-      <c r="O27" s="52" t="n"/>
-      <c r="P27" s="52" t="n"/>
-      <c r="Q27" s="66">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A27" s="79" t="n"/>
+      <c r="B27" s="79" t="n"/>
+      <c r="C27" s="79" t="n"/>
+      <c r="D27" s="79" t="n"/>
+      <c r="E27" s="79" t="n"/>
+      <c r="F27" s="79" t="n"/>
+      <c r="G27" s="79" t="n"/>
+      <c r="H27" s="79" t="n"/>
+      <c r="I27" s="79" t="n"/>
+      <c r="J27" s="79" t="n"/>
+      <c r="K27" s="79" t="n"/>
+      <c r="L27" s="79" t="n"/>
+      <c r="M27" s="79" t="n"/>
+      <c r="N27" s="79" t="n"/>
+      <c r="O27" s="79" t="n"/>
+      <c r="P27" s="79" t="n"/>
+      <c r="Q27" s="80" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="n"/>
-      <c r="B28" s="52" t="n"/>
-      <c r="C28" s="52" t="n"/>
-      <c r="D28" s="52" t="n"/>
-      <c r="E28" s="52" t="n"/>
-      <c r="F28" s="52" t="n"/>
-      <c r="G28" s="52" t="n"/>
-      <c r="H28" s="52" t="n"/>
-      <c r="I28" s="52" t="n"/>
-      <c r="J28" s="52" t="n"/>
-      <c r="K28" s="52" t="n"/>
-      <c r="L28" s="52" t="n"/>
-      <c r="M28" s="52" t="n"/>
-      <c r="N28" s="52" t="n"/>
-      <c r="O28" s="52" t="n"/>
-      <c r="P28" s="52" t="n"/>
-      <c r="Q28" s="66">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A28" s="79" t="n"/>
+      <c r="B28" s="79" t="n"/>
+      <c r="C28" s="79" t="n"/>
+      <c r="D28" s="79" t="n"/>
+      <c r="E28" s="79" t="n"/>
+      <c r="F28" s="79" t="n"/>
+      <c r="G28" s="79" t="n"/>
+      <c r="H28" s="79" t="n"/>
+      <c r="I28" s="79" t="n"/>
+      <c r="J28" s="79" t="n"/>
+      <c r="K28" s="79" t="n"/>
+      <c r="L28" s="79" t="n"/>
+      <c r="M28" s="79" t="n"/>
+      <c r="N28" s="79" t="n"/>
+      <c r="O28" s="79" t="n"/>
+      <c r="P28" s="79" t="n"/>
+      <c r="Q28" s="80" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n"/>
-      <c r="B29" s="52" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52" t="n"/>
-      <c r="G29" s="52" t="n"/>
-      <c r="H29" s="52" t="n"/>
-      <c r="I29" s="52" t="n"/>
-      <c r="J29" s="52" t="n"/>
-      <c r="K29" s="52" t="n"/>
-      <c r="L29" s="52" t="n"/>
-      <c r="M29" s="52" t="n"/>
-      <c r="N29" s="52" t="n"/>
-      <c r="O29" s="52" t="n"/>
-      <c r="P29" s="52" t="n"/>
-      <c r="Q29" s="66">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A29" s="79" t="n"/>
+      <c r="B29" s="79" t="n"/>
+      <c r="C29" s="79" t="n"/>
+      <c r="D29" s="79" t="n"/>
+      <c r="E29" s="79" t="n"/>
+      <c r="F29" s="79" t="n"/>
+      <c r="G29" s="79" t="n"/>
+      <c r="H29" s="79" t="n"/>
+      <c r="I29" s="79" t="n"/>
+      <c r="J29" s="79" t="n"/>
+      <c r="K29" s="79" t="n"/>
+      <c r="L29" s="79" t="n"/>
+      <c r="M29" s="79" t="n"/>
+      <c r="N29" s="79" t="n"/>
+      <c r="O29" s="79" t="n"/>
+      <c r="P29" s="79" t="n"/>
+      <c r="Q29" s="80" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="n"/>
-      <c r="B30" s="52" t="n"/>
-      <c r="C30" s="52" t="n"/>
-      <c r="D30" s="52" t="n"/>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="52" t="n"/>
-      <c r="G30" s="52" t="n"/>
-      <c r="H30" s="52" t="n"/>
-      <c r="I30" s="52" t="n"/>
-      <c r="J30" s="52" t="n"/>
-      <c r="K30" s="52" t="n"/>
-      <c r="L30" s="52" t="n"/>
-      <c r="M30" s="52" t="n"/>
-      <c r="N30" s="52" t="n"/>
-      <c r="O30" s="52" t="n"/>
-      <c r="P30" s="52" t="n"/>
-      <c r="Q30" s="66">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A30" s="79" t="n"/>
+      <c r="B30" s="79" t="n"/>
+      <c r="C30" s="79" t="n"/>
+      <c r="D30" s="79" t="n"/>
+      <c r="E30" s="79" t="n"/>
+      <c r="F30" s="79" t="n"/>
+      <c r="G30" s="79" t="n"/>
+      <c r="H30" s="79" t="n"/>
+      <c r="I30" s="79" t="n"/>
+      <c r="J30" s="79" t="n"/>
+      <c r="K30" s="79" t="n"/>
+      <c r="L30" s="79" t="n"/>
+      <c r="M30" s="79" t="n"/>
+      <c r="N30" s="79" t="n"/>
+      <c r="O30" s="79" t="n"/>
+      <c r="P30" s="79" t="n"/>
+      <c r="Q30" s="80" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n"/>
-      <c r="B31" s="52" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n"/>
-      <c r="J31" s="52" t="n"/>
-      <c r="K31" s="52" t="n"/>
-      <c r="L31" s="52" t="n"/>
-      <c r="M31" s="52" t="n"/>
-      <c r="N31" s="52" t="n"/>
-      <c r="O31" s="52" t="n"/>
-      <c r="P31" s="52" t="n"/>
-      <c r="Q31" s="66">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A31" s="79" t="n"/>
+      <c r="B31" s="79" t="n"/>
+      <c r="C31" s="79" t="n"/>
+      <c r="D31" s="79" t="n"/>
+      <c r="E31" s="79" t="n"/>
+      <c r="F31" s="79" t="n"/>
+      <c r="G31" s="79" t="n"/>
+      <c r="H31" s="79" t="n"/>
+      <c r="I31" s="79" t="n"/>
+      <c r="J31" s="79" t="n"/>
+      <c r="K31" s="79" t="n"/>
+      <c r="L31" s="79" t="n"/>
+      <c r="M31" s="79" t="n"/>
+      <c r="N31" s="79" t="n"/>
+      <c r="O31" s="79" t="n"/>
+      <c r="P31" s="79" t="n"/>
+      <c r="Q31" s="80" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="n"/>
-      <c r="B32" s="52" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="52" t="n"/>
-      <c r="E32" s="52" t="n"/>
-      <c r="F32" s="52" t="n"/>
-      <c r="G32" s="52" t="n"/>
-      <c r="H32" s="52" t="n"/>
-      <c r="I32" s="52" t="n"/>
-      <c r="J32" s="52" t="n"/>
-      <c r="K32" s="52" t="n"/>
-      <c r="L32" s="52" t="n"/>
-      <c r="M32" s="52" t="n"/>
-      <c r="N32" s="52" t="n"/>
-      <c r="O32" s="52" t="n"/>
-      <c r="P32" s="52" t="n"/>
-      <c r="Q32" s="66">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A32" s="79" t="n"/>
+      <c r="B32" s="79" t="n"/>
+      <c r="C32" s="79" t="n"/>
+      <c r="D32" s="79" t="n"/>
+      <c r="E32" s="79" t="n"/>
+      <c r="F32" s="79" t="n"/>
+      <c r="G32" s="79" t="n"/>
+      <c r="H32" s="79" t="n"/>
+      <c r="I32" s="79" t="n"/>
+      <c r="J32" s="79" t="n"/>
+      <c r="K32" s="79" t="n"/>
+      <c r="L32" s="79" t="n"/>
+      <c r="M32" s="79" t="n"/>
+      <c r="N32" s="79" t="n"/>
+      <c r="O32" s="79" t="n"/>
+      <c r="P32" s="79" t="n"/>
+      <c r="Q32" s="80" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="52" t="n"/>
-      <c r="B33" s="52" t="n"/>
-      <c r="C33" s="52" t="n"/>
-      <c r="D33" s="52" t="n"/>
-      <c r="E33" s="52" t="n"/>
-      <c r="F33" s="52" t="n"/>
-      <c r="G33" s="52" t="n"/>
-      <c r="H33" s="52" t="n"/>
-      <c r="I33" s="52" t="n"/>
-      <c r="J33" s="52" t="n"/>
-      <c r="K33" s="52" t="n"/>
-      <c r="L33" s="52" t="n"/>
-      <c r="M33" s="52" t="n"/>
-      <c r="N33" s="52" t="n"/>
-      <c r="O33" s="52" t="n"/>
-      <c r="P33" s="52" t="n"/>
-      <c r="Q33" s="66">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A33" s="79" t="n"/>
+      <c r="B33" s="79" t="n"/>
+      <c r="C33" s="79" t="n"/>
+      <c r="D33" s="79" t="n"/>
+      <c r="E33" s="79" t="n"/>
+      <c r="F33" s="79" t="n"/>
+      <c r="G33" s="79" t="n"/>
+      <c r="H33" s="79" t="n"/>
+      <c r="I33" s="79" t="n"/>
+      <c r="J33" s="79" t="n"/>
+      <c r="K33" s="79" t="n"/>
+      <c r="L33" s="79" t="n"/>
+      <c r="M33" s="79" t="n"/>
+      <c r="N33" s="79" t="n"/>
+      <c r="O33" s="79" t="n"/>
+      <c r="P33" s="79" t="n"/>
+      <c r="Q33" s="80" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="52" t="n"/>
-      <c r="B34" s="52" t="n"/>
-      <c r="C34" s="52" t="n"/>
-      <c r="D34" s="52" t="n"/>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52" t="n"/>
-      <c r="G34" s="52" t="n"/>
-      <c r="H34" s="52" t="n"/>
-      <c r="I34" s="52" t="n"/>
-      <c r="J34" s="52" t="n"/>
-      <c r="K34" s="52" t="n"/>
-      <c r="L34" s="52" t="n"/>
-      <c r="M34" s="52" t="n"/>
-      <c r="N34" s="52" t="n"/>
-      <c r="O34" s="52" t="n"/>
-      <c r="P34" s="52" t="n"/>
-      <c r="Q34" s="66">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A34" s="79" t="n"/>
+      <c r="B34" s="79" t="n"/>
+      <c r="C34" s="79" t="n"/>
+      <c r="D34" s="79" t="n"/>
+      <c r="E34" s="79" t="n"/>
+      <c r="F34" s="79" t="n"/>
+      <c r="G34" s="79" t="n"/>
+      <c r="H34" s="79" t="n"/>
+      <c r="I34" s="79" t="n"/>
+      <c r="J34" s="79" t="n"/>
+      <c r="K34" s="79" t="n"/>
+      <c r="L34" s="79" t="n"/>
+      <c r="M34" s="79" t="n"/>
+      <c r="N34" s="79" t="n"/>
+      <c r="O34" s="79" t="n"/>
+      <c r="P34" s="79" t="n"/>
+      <c r="Q34" s="80" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="52" t="n"/>
-      <c r="B35" s="52" t="n"/>
-      <c r="C35" s="52" t="n"/>
-      <c r="D35" s="52" t="n"/>
-      <c r="E35" s="52" t="n"/>
-      <c r="F35" s="52" t="n"/>
-      <c r="G35" s="52" t="n"/>
-      <c r="H35" s="52" t="n"/>
-      <c r="I35" s="52" t="n"/>
-      <c r="J35" s="52" t="n"/>
-      <c r="K35" s="52" t="n"/>
-      <c r="L35" s="52" t="n"/>
-      <c r="M35" s="52" t="n"/>
-      <c r="N35" s="52" t="n"/>
-      <c r="O35" s="52" t="n"/>
-      <c r="P35" s="52" t="n"/>
-      <c r="Q35" s="66">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A35" s="79" t="n"/>
+      <c r="B35" s="79" t="n"/>
+      <c r="C35" s="79" t="n"/>
+      <c r="D35" s="79" t="n"/>
+      <c r="E35" s="79" t="n"/>
+      <c r="F35" s="79" t="n"/>
+      <c r="G35" s="79" t="n"/>
+      <c r="H35" s="79" t="n"/>
+      <c r="I35" s="79" t="n"/>
+      <c r="J35" s="79" t="n"/>
+      <c r="K35" s="79" t="n"/>
+      <c r="L35" s="79" t="n"/>
+      <c r="M35" s="79" t="n"/>
+      <c r="N35" s="79" t="n"/>
+      <c r="O35" s="79" t="n"/>
+      <c r="P35" s="79" t="n"/>
+      <c r="Q35" s="80" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="52" t="n"/>
-      <c r="B36" s="52" t="n"/>
-      <c r="C36" s="52" t="n"/>
-      <c r="D36" s="52" t="n"/>
-      <c r="E36" s="52" t="n"/>
-      <c r="F36" s="52" t="n"/>
-      <c r="G36" s="52" t="n"/>
-      <c r="H36" s="52" t="n"/>
-      <c r="I36" s="52" t="n"/>
-      <c r="J36" s="52" t="n"/>
-      <c r="K36" s="52" t="n"/>
-      <c r="L36" s="52" t="n"/>
-      <c r="M36" s="52" t="n"/>
-      <c r="N36" s="52" t="n"/>
-      <c r="O36" s="52" t="n"/>
-      <c r="P36" s="52" t="n"/>
-      <c r="Q36" s="66">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A36" s="79" t="n"/>
+      <c r="B36" s="79" t="n"/>
+      <c r="C36" s="79" t="n"/>
+      <c r="D36" s="79" t="n"/>
+      <c r="E36" s="79" t="n"/>
+      <c r="F36" s="79" t="n"/>
+      <c r="G36" s="79" t="n"/>
+      <c r="H36" s="79" t="n"/>
+      <c r="I36" s="79" t="n"/>
+      <c r="J36" s="79" t="n"/>
+      <c r="K36" s="79" t="n"/>
+      <c r="L36" s="79" t="n"/>
+      <c r="M36" s="79" t="n"/>
+      <c r="N36" s="79" t="n"/>
+      <c r="O36" s="79" t="n"/>
+      <c r="P36" s="79" t="n"/>
+      <c r="Q36" s="80" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="52" t="n"/>
-      <c r="B37" s="52" t="n"/>
-      <c r="C37" s="52" t="n"/>
-      <c r="D37" s="52" t="n"/>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52" t="n"/>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="52" t="n"/>
-      <c r="K37" s="52" t="n"/>
-      <c r="L37" s="52" t="n"/>
-      <c r="M37" s="52" t="n"/>
-      <c r="N37" s="52" t="n"/>
-      <c r="O37" s="52" t="n"/>
-      <c r="P37" s="52" t="n"/>
-      <c r="Q37" s="66">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A37" s="79" t="n"/>
+      <c r="B37" s="79" t="n"/>
+      <c r="C37" s="79" t="n"/>
+      <c r="D37" s="79" t="n"/>
+      <c r="E37" s="79" t="n"/>
+      <c r="F37" s="79" t="n"/>
+      <c r="G37" s="79" t="n"/>
+      <c r="H37" s="79" t="n"/>
+      <c r="I37" s="79" t="n"/>
+      <c r="J37" s="79" t="n"/>
+      <c r="K37" s="79" t="n"/>
+      <c r="L37" s="79" t="n"/>
+      <c r="M37" s="79" t="n"/>
+      <c r="N37" s="79" t="n"/>
+      <c r="O37" s="79" t="n"/>
+      <c r="P37" s="79" t="n"/>
+      <c r="Q37" s="80" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="52" t="n"/>
-      <c r="B38" s="52" t="n"/>
-      <c r="C38" s="52" t="n"/>
-      <c r="D38" s="52" t="n"/>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52" t="n"/>
-      <c r="G38" s="52" t="n"/>
-      <c r="H38" s="52" t="n"/>
-      <c r="I38" s="52" t="n"/>
-      <c r="J38" s="52" t="n"/>
-      <c r="K38" s="52" t="n"/>
-      <c r="L38" s="52" t="n"/>
-      <c r="M38" s="52" t="n"/>
-      <c r="N38" s="52" t="n"/>
-      <c r="O38" s="52" t="n"/>
-      <c r="P38" s="52" t="n"/>
-      <c r="Q38" s="66">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A38" s="79" t="n"/>
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="79" t="n"/>
+      <c r="D38" s="79" t="n"/>
+      <c r="E38" s="79" t="n"/>
+      <c r="F38" s="79" t="n"/>
+      <c r="G38" s="79" t="n"/>
+      <c r="H38" s="79" t="n"/>
+      <c r="I38" s="79" t="n"/>
+      <c r="J38" s="79" t="n"/>
+      <c r="K38" s="79" t="n"/>
+      <c r="L38" s="79" t="n"/>
+      <c r="M38" s="79" t="n"/>
+      <c r="N38" s="79" t="n"/>
+      <c r="O38" s="79" t="n"/>
+      <c r="P38" s="79" t="n"/>
+      <c r="Q38" s="80" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="n"/>
-      <c r="B39" s="52" t="n"/>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="52" t="n"/>
-      <c r="K39" s="52" t="n"/>
-      <c r="L39" s="52" t="n"/>
-      <c r="M39" s="52" t="n"/>
-      <c r="N39" s="52" t="n"/>
-      <c r="O39" s="52" t="n"/>
-      <c r="P39" s="52" t="n"/>
-      <c r="Q39" s="66">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A39" s="79" t="n"/>
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+      <c r="F39" s="79" t="n"/>
+      <c r="G39" s="79" t="n"/>
+      <c r="H39" s="79" t="n"/>
+      <c r="I39" s="79" t="n"/>
+      <c r="J39" s="79" t="n"/>
+      <c r="K39" s="79" t="n"/>
+      <c r="L39" s="79" t="n"/>
+      <c r="M39" s="79" t="n"/>
+      <c r="N39" s="79" t="n"/>
+      <c r="O39" s="79" t="n"/>
+      <c r="P39" s="79" t="n"/>
+      <c r="Q39" s="80" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="52" t="n"/>
-      <c r="B40" s="52" t="n"/>
-      <c r="C40" s="52" t="n"/>
-      <c r="D40" s="52" t="n"/>
-      <c r="E40" s="52" t="n"/>
-      <c r="F40" s="52" t="n"/>
-      <c r="G40" s="52" t="n"/>
-      <c r="H40" s="52" t="n"/>
-      <c r="I40" s="52" t="n"/>
-      <c r="J40" s="52" t="n"/>
-      <c r="K40" s="52" t="n"/>
-      <c r="L40" s="52" t="n"/>
-      <c r="M40" s="52" t="n"/>
-      <c r="N40" s="52" t="n"/>
-      <c r="O40" s="52" t="n"/>
-      <c r="P40" s="52" t="n"/>
-      <c r="Q40" s="66">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A40" s="79" t="n"/>
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="79" t="n"/>
+      <c r="D40" s="79" t="n"/>
+      <c r="E40" s="79" t="n"/>
+      <c r="F40" s="79" t="n"/>
+      <c r="G40" s="79" t="n"/>
+      <c r="H40" s="79" t="n"/>
+      <c r="I40" s="79" t="n"/>
+      <c r="J40" s="79" t="n"/>
+      <c r="K40" s="79" t="n"/>
+      <c r="L40" s="79" t="n"/>
+      <c r="M40" s="79" t="n"/>
+      <c r="N40" s="79" t="n"/>
+      <c r="O40" s="79" t="n"/>
+      <c r="P40" s="79" t="n"/>
+      <c r="Q40" s="80" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="n"/>
-      <c r="B41" s="52" t="n"/>
-      <c r="C41" s="52" t="n"/>
-      <c r="D41" s="52" t="n"/>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52" t="n"/>
-      <c r="G41" s="52" t="n"/>
-      <c r="H41" s="52" t="n"/>
-      <c r="I41" s="52" t="n"/>
-      <c r="J41" s="52" t="n"/>
-      <c r="K41" s="52" t="n"/>
-      <c r="L41" s="52" t="n"/>
-      <c r="M41" s="52" t="n"/>
-      <c r="N41" s="52" t="n"/>
-      <c r="O41" s="52" t="n"/>
-      <c r="P41" s="52" t="n"/>
-      <c r="Q41" s="66">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A41" s="79" t="n"/>
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="79" t="n"/>
+      <c r="D41" s="79" t="n"/>
+      <c r="E41" s="79" t="n"/>
+      <c r="F41" s="79" t="n"/>
+      <c r="G41" s="79" t="n"/>
+      <c r="H41" s="79" t="n"/>
+      <c r="I41" s="79" t="n"/>
+      <c r="J41" s="79" t="n"/>
+      <c r="K41" s="79" t="n"/>
+      <c r="L41" s="79" t="n"/>
+      <c r="M41" s="79" t="n"/>
+      <c r="N41" s="79" t="n"/>
+      <c r="O41" s="79" t="n"/>
+      <c r="P41" s="79" t="n"/>
+      <c r="Q41" s="80" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="52" t="n"/>
-      <c r="B42" s="52" t="n"/>
-      <c r="C42" s="52" t="n"/>
-      <c r="D42" s="52" t="n"/>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52" t="n"/>
-      <c r="G42" s="52" t="n"/>
-      <c r="H42" s="52" t="n"/>
-      <c r="I42" s="52" t="n"/>
-      <c r="J42" s="52" t="n"/>
-      <c r="K42" s="52" t="n"/>
-      <c r="L42" s="52" t="n"/>
-      <c r="M42" s="52" t="n"/>
-      <c r="N42" s="52" t="n"/>
-      <c r="O42" s="52" t="n"/>
-      <c r="P42" s="52" t="n"/>
-      <c r="Q42" s="66">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A42" s="79" t="n"/>
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="79" t="n"/>
+      <c r="D42" s="79" t="n"/>
+      <c r="E42" s="79" t="n"/>
+      <c r="F42" s="79" t="n"/>
+      <c r="G42" s="79" t="n"/>
+      <c r="H42" s="79" t="n"/>
+      <c r="I42" s="79" t="n"/>
+      <c r="J42" s="79" t="n"/>
+      <c r="K42" s="79" t="n"/>
+      <c r="L42" s="79" t="n"/>
+      <c r="M42" s="79" t="n"/>
+      <c r="N42" s="79" t="n"/>
+      <c r="O42" s="79" t="n"/>
+      <c r="P42" s="79" t="n"/>
+      <c r="Q42" s="80" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="n"/>
-      <c r="B43" s="52" t="n"/>
-      <c r="C43" s="52" t="n"/>
-      <c r="D43" s="52" t="n"/>
-      <c r="E43" s="52" t="n"/>
-      <c r="F43" s="52" t="n"/>
-      <c r="G43" s="52" t="n"/>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="52" t="n"/>
-      <c r="J43" s="52" t="n"/>
-      <c r="K43" s="52" t="n"/>
-      <c r="L43" s="52" t="n"/>
-      <c r="M43" s="52" t="n"/>
-      <c r="N43" s="52" t="n"/>
-      <c r="O43" s="52" t="n"/>
-      <c r="P43" s="52" t="n"/>
-      <c r="Q43" s="66">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A43" s="79" t="n"/>
+      <c r="B43" s="79" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
+      <c r="I43" s="79" t="n"/>
+      <c r="J43" s="79" t="n"/>
+      <c r="K43" s="79" t="n"/>
+      <c r="L43" s="79" t="n"/>
+      <c r="M43" s="79" t="n"/>
+      <c r="N43" s="79" t="n"/>
+      <c r="O43" s="79" t="n"/>
+      <c r="P43" s="79" t="n"/>
+      <c r="Q43" s="80" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="52" t="n"/>
-      <c r="B44" s="52" t="n"/>
-      <c r="C44" s="52" t="n"/>
-      <c r="D44" s="52" t="n"/>
-      <c r="E44" s="52" t="n"/>
-      <c r="F44" s="52" t="n"/>
-      <c r="G44" s="52" t="n"/>
-      <c r="H44" s="52" t="n"/>
-      <c r="I44" s="52" t="n"/>
-      <c r="J44" s="52" t="n"/>
-      <c r="K44" s="52" t="n"/>
-      <c r="L44" s="52" t="n"/>
-      <c r="M44" s="52" t="n"/>
-      <c r="N44" s="52" t="n"/>
-      <c r="O44" s="52" t="n"/>
-      <c r="P44" s="52" t="n"/>
-      <c r="Q44" s="66">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A44" s="79" t="n"/>
+      <c r="B44" s="79" t="n"/>
+      <c r="C44" s="79" t="n"/>
+      <c r="D44" s="79" t="n"/>
+      <c r="E44" s="79" t="n"/>
+      <c r="F44" s="79" t="n"/>
+      <c r="G44" s="79" t="n"/>
+      <c r="H44" s="79" t="n"/>
+      <c r="I44" s="79" t="n"/>
+      <c r="J44" s="79" t="n"/>
+      <c r="K44" s="79" t="n"/>
+      <c r="L44" s="79" t="n"/>
+      <c r="M44" s="79" t="n"/>
+      <c r="N44" s="79" t="n"/>
+      <c r="O44" s="79" t="n"/>
+      <c r="P44" s="79" t="n"/>
+      <c r="Q44" s="80" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="52" t="n"/>
-      <c r="B45" s="52" t="n"/>
-      <c r="C45" s="52" t="n"/>
-      <c r="D45" s="52" t="n"/>
-      <c r="E45" s="52" t="n"/>
-      <c r="F45" s="52" t="n"/>
-      <c r="G45" s="52" t="n"/>
-      <c r="H45" s="52" t="n"/>
-      <c r="I45" s="52" t="n"/>
-      <c r="J45" s="52" t="n"/>
-      <c r="K45" s="52" t="n"/>
-      <c r="L45" s="52" t="n"/>
-      <c r="M45" s="52" t="n"/>
-      <c r="N45" s="52" t="n"/>
-      <c r="O45" s="52" t="n"/>
-      <c r="P45" s="52" t="n"/>
-      <c r="Q45" s="66">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A45" s="79" t="n"/>
+      <c r="B45" s="79" t="n"/>
+      <c r="C45" s="79" t="n"/>
+      <c r="D45" s="79" t="n"/>
+      <c r="E45" s="79" t="n"/>
+      <c r="F45" s="79" t="n"/>
+      <c r="G45" s="79" t="n"/>
+      <c r="H45" s="79" t="n"/>
+      <c r="I45" s="79" t="n"/>
+      <c r="J45" s="79" t="n"/>
+      <c r="K45" s="79" t="n"/>
+      <c r="L45" s="79" t="n"/>
+      <c r="M45" s="79" t="n"/>
+      <c r="N45" s="79" t="n"/>
+      <c r="O45" s="79" t="n"/>
+      <c r="P45" s="79" t="n"/>
+      <c r="Q45" s="80" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="52" t="n"/>
-      <c r="B46" s="52" t="n"/>
-      <c r="C46" s="52" t="n"/>
-      <c r="D46" s="52" t="n"/>
-      <c r="E46" s="52" t="n"/>
-      <c r="F46" s="52" t="n"/>
-      <c r="G46" s="52" t="n"/>
-      <c r="H46" s="52" t="n"/>
-      <c r="I46" s="52" t="n"/>
-      <c r="J46" s="52" t="n"/>
-      <c r="K46" s="52" t="n"/>
-      <c r="L46" s="52" t="n"/>
-      <c r="M46" s="52" t="n"/>
-      <c r="N46" s="52" t="n"/>
-      <c r="O46" s="52" t="n"/>
-      <c r="P46" s="52" t="n"/>
-      <c r="Q46" s="66">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A46" s="79" t="n"/>
+      <c r="B46" s="79" t="n"/>
+      <c r="C46" s="79" t="n"/>
+      <c r="D46" s="79" t="n"/>
+      <c r="E46" s="79" t="n"/>
+      <c r="F46" s="79" t="n"/>
+      <c r="G46" s="79" t="n"/>
+      <c r="H46" s="79" t="n"/>
+      <c r="I46" s="79" t="n"/>
+      <c r="J46" s="79" t="n"/>
+      <c r="K46" s="79" t="n"/>
+      <c r="L46" s="79" t="n"/>
+      <c r="M46" s="79" t="n"/>
+      <c r="N46" s="79" t="n"/>
+      <c r="O46" s="79" t="n"/>
+      <c r="P46" s="79" t="n"/>
+      <c r="Q46" s="80" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="52" t="n"/>
-      <c r="B47" s="52" t="n"/>
-      <c r="C47" s="52" t="n"/>
-      <c r="D47" s="52" t="n"/>
-      <c r="E47" s="52" t="n"/>
-      <c r="F47" s="52" t="n"/>
-      <c r="G47" s="52" t="n"/>
-      <c r="H47" s="52" t="n"/>
-      <c r="I47" s="52" t="n"/>
-      <c r="J47" s="52" t="n"/>
-      <c r="K47" s="52" t="n"/>
-      <c r="L47" s="52" t="n"/>
-      <c r="M47" s="52" t="n"/>
-      <c r="N47" s="52" t="n"/>
-      <c r="O47" s="52" t="n"/>
-      <c r="P47" s="52" t="n"/>
-      <c r="Q47" s="66">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A47" s="79" t="n"/>
+      <c r="B47" s="79" t="n"/>
+      <c r="C47" s="79" t="n"/>
+      <c r="D47" s="79" t="n"/>
+      <c r="E47" s="79" t="n"/>
+      <c r="F47" s="79" t="n"/>
+      <c r="G47" s="79" t="n"/>
+      <c r="H47" s="79" t="n"/>
+      <c r="I47" s="79" t="n"/>
+      <c r="J47" s="79" t="n"/>
+      <c r="K47" s="79" t="n"/>
+      <c r="L47" s="79" t="n"/>
+      <c r="M47" s="79" t="n"/>
+      <c r="N47" s="79" t="n"/>
+      <c r="O47" s="79" t="n"/>
+      <c r="P47" s="79" t="n"/>
+      <c r="Q47" s="80" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="52" t="n"/>
-      <c r="B48" s="52" t="n"/>
-      <c r="C48" s="52" t="n"/>
-      <c r="D48" s="52" t="n"/>
-      <c r="E48" s="52" t="n"/>
-      <c r="F48" s="52" t="n"/>
-      <c r="G48" s="52" t="n"/>
-      <c r="H48" s="52" t="n"/>
-      <c r="I48" s="52" t="n"/>
-      <c r="J48" s="52" t="n"/>
-      <c r="K48" s="52" t="n"/>
-      <c r="L48" s="52" t="n"/>
-      <c r="M48" s="52" t="n"/>
-      <c r="N48" s="52" t="n"/>
-      <c r="O48" s="52" t="n"/>
-      <c r="P48" s="52" t="n"/>
-      <c r="Q48" s="66">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A48" s="79" t="n"/>
+      <c r="B48" s="79" t="n"/>
+      <c r="C48" s="79" t="n"/>
+      <c r="D48" s="79" t="n"/>
+      <c r="E48" s="79" t="n"/>
+      <c r="F48" s="79" t="n"/>
+      <c r="G48" s="79" t="n"/>
+      <c r="H48" s="79" t="n"/>
+      <c r="I48" s="79" t="n"/>
+      <c r="J48" s="79" t="n"/>
+      <c r="K48" s="79" t="n"/>
+      <c r="L48" s="79" t="n"/>
+      <c r="M48" s="79" t="n"/>
+      <c r="N48" s="79" t="n"/>
+      <c r="O48" s="79" t="n"/>
+      <c r="P48" s="79" t="n"/>
+      <c r="Q48" s="80" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="n"/>
-      <c r="B49" s="52" t="n"/>
-      <c r="C49" s="52" t="n"/>
-      <c r="D49" s="52" t="n"/>
-      <c r="E49" s="52" t="n"/>
-      <c r="F49" s="52" t="n"/>
-      <c r="G49" s="52" t="n"/>
-      <c r="H49" s="52" t="n"/>
-      <c r="I49" s="52" t="n"/>
-      <c r="J49" s="52" t="n"/>
-      <c r="K49" s="52" t="n"/>
-      <c r="L49" s="52" t="n"/>
-      <c r="M49" s="52" t="n"/>
-      <c r="N49" s="52" t="n"/>
-      <c r="O49" s="52" t="n"/>
-      <c r="P49" s="52" t="n"/>
-      <c r="Q49" s="66">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A49" s="79" t="n"/>
+      <c r="B49" s="79" t="n"/>
+      <c r="C49" s="79" t="n"/>
+      <c r="D49" s="79" t="n"/>
+      <c r="E49" s="79" t="n"/>
+      <c r="F49" s="79" t="n"/>
+      <c r="G49" s="79" t="n"/>
+      <c r="H49" s="79" t="n"/>
+      <c r="I49" s="79" t="n"/>
+      <c r="J49" s="79" t="n"/>
+      <c r="K49" s="79" t="n"/>
+      <c r="L49" s="79" t="n"/>
+      <c r="M49" s="79" t="n"/>
+      <c r="N49" s="79" t="n"/>
+      <c r="O49" s="79" t="n"/>
+      <c r="P49" s="79" t="n"/>
+      <c r="Q49" s="80" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="52" t="n"/>
-      <c r="B50" s="52" t="n"/>
-      <c r="C50" s="52" t="n"/>
-      <c r="D50" s="52" t="n"/>
-      <c r="E50" s="52" t="n"/>
-      <c r="F50" s="52" t="n"/>
-      <c r="G50" s="52" t="n"/>
-      <c r="H50" s="52" t="n"/>
-      <c r="I50" s="52" t="n"/>
-      <c r="J50" s="52" t="n"/>
-      <c r="K50" s="52" t="n"/>
-      <c r="L50" s="52" t="n"/>
-      <c r="M50" s="52" t="n"/>
-      <c r="N50" s="52" t="n"/>
-      <c r="O50" s="52" t="n"/>
-      <c r="P50" s="52" t="n"/>
-      <c r="Q50" s="66">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A50" s="79" t="n"/>
+      <c r="B50" s="79" t="n"/>
+      <c r="C50" s="79" t="n"/>
+      <c r="D50" s="79" t="n"/>
+      <c r="E50" s="79" t="n"/>
+      <c r="F50" s="79" t="n"/>
+      <c r="G50" s="79" t="n"/>
+      <c r="H50" s="79" t="n"/>
+      <c r="I50" s="79" t="n"/>
+      <c r="J50" s="79" t="n"/>
+      <c r="K50" s="79" t="n"/>
+      <c r="L50" s="79" t="n"/>
+      <c r="M50" s="79" t="n"/>
+      <c r="N50" s="79" t="n"/>
+      <c r="O50" s="79" t="n"/>
+      <c r="P50" s="79" t="n"/>
+      <c r="Q50" s="80" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="n"/>
-      <c r="B51" s="52" t="n"/>
-      <c r="C51" s="52" t="n"/>
-      <c r="D51" s="52" t="n"/>
-      <c r="E51" s="52" t="n"/>
-      <c r="F51" s="52" t="n"/>
-      <c r="G51" s="52" t="n"/>
-      <c r="H51" s="52" t="n"/>
-      <c r="I51" s="52" t="n"/>
-      <c r="J51" s="52" t="n"/>
-      <c r="K51" s="52" t="n"/>
-      <c r="L51" s="52" t="n"/>
-      <c r="M51" s="52" t="n"/>
-      <c r="N51" s="52" t="n"/>
-      <c r="O51" s="52" t="n"/>
-      <c r="P51" s="52" t="n"/>
-      <c r="Q51" s="66">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A51" s="79" t="n"/>
+      <c r="B51" s="79" t="n"/>
+      <c r="C51" s="79" t="n"/>
+      <c r="D51" s="79" t="n"/>
+      <c r="E51" s="79" t="n"/>
+      <c r="F51" s="79" t="n"/>
+      <c r="G51" s="79" t="n"/>
+      <c r="H51" s="79" t="n"/>
+      <c r="I51" s="79" t="n"/>
+      <c r="J51" s="79" t="n"/>
+      <c r="K51" s="79" t="n"/>
+      <c r="L51" s="79" t="n"/>
+      <c r="M51" s="79" t="n"/>
+      <c r="N51" s="79" t="n"/>
+      <c r="O51" s="79" t="n"/>
+      <c r="P51" s="79" t="n"/>
+      <c r="Q51" s="80" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="52" t="n"/>
-      <c r="B52" s="52" t="n"/>
-      <c r="C52" s="52" t="n"/>
-      <c r="D52" s="52" t="n"/>
-      <c r="E52" s="52" t="n"/>
-      <c r="F52" s="52" t="n"/>
-      <c r="G52" s="52" t="n"/>
-      <c r="H52" s="52" t="n"/>
-      <c r="I52" s="52" t="n"/>
-      <c r="J52" s="52" t="n"/>
-      <c r="K52" s="52" t="n"/>
-      <c r="L52" s="52" t="n"/>
-      <c r="M52" s="52" t="n"/>
-      <c r="N52" s="52" t="n"/>
-      <c r="O52" s="52" t="n"/>
-      <c r="P52" s="52" t="n"/>
-      <c r="Q52" s="66">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A52" s="79" t="n"/>
+      <c r="B52" s="79" t="n"/>
+      <c r="C52" s="79" t="n"/>
+      <c r="D52" s="79" t="n"/>
+      <c r="E52" s="79" t="n"/>
+      <c r="F52" s="79" t="n"/>
+      <c r="G52" s="79" t="n"/>
+      <c r="H52" s="79" t="n"/>
+      <c r="I52" s="79" t="n"/>
+      <c r="J52" s="79" t="n"/>
+      <c r="K52" s="79" t="n"/>
+      <c r="L52" s="79" t="n"/>
+      <c r="M52" s="79" t="n"/>
+      <c r="N52" s="79" t="n"/>
+      <c r="O52" s="79" t="n"/>
+      <c r="P52" s="79" t="n"/>
+      <c r="Q52" s="80" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="52" t="n"/>
-      <c r="B53" s="52" t="n"/>
-      <c r="C53" s="52" t="n"/>
-      <c r="D53" s="52" t="n"/>
-      <c r="E53" s="52" t="n"/>
-      <c r="F53" s="52" t="n"/>
-      <c r="G53" s="52" t="n"/>
-      <c r="H53" s="52" t="n"/>
-      <c r="I53" s="52" t="n"/>
-      <c r="J53" s="52" t="n"/>
-      <c r="K53" s="52" t="n"/>
-      <c r="L53" s="52" t="n"/>
-      <c r="M53" s="52" t="n"/>
-      <c r="N53" s="52" t="n"/>
-      <c r="O53" s="52" t="n"/>
-      <c r="P53" s="52" t="n"/>
-      <c r="Q53" s="66">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A53" s="79" t="n"/>
+      <c r="B53" s="79" t="n"/>
+      <c r="C53" s="79" t="n"/>
+      <c r="D53" s="79" t="n"/>
+      <c r="E53" s="79" t="n"/>
+      <c r="F53" s="79" t="n"/>
+      <c r="G53" s="79" t="n"/>
+      <c r="H53" s="79" t="n"/>
+      <c r="I53" s="79" t="n"/>
+      <c r="J53" s="79" t="n"/>
+      <c r="K53" s="79" t="n"/>
+      <c r="L53" s="79" t="n"/>
+      <c r="M53" s="79" t="n"/>
+      <c r="N53" s="79" t="n"/>
+      <c r="O53" s="79" t="n"/>
+      <c r="P53" s="79" t="n"/>
+      <c r="Q53" s="80" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="52" t="n"/>
-      <c r="B54" s="52" t="n"/>
-      <c r="C54" s="52" t="n"/>
-      <c r="D54" s="52" t="n"/>
-      <c r="E54" s="52" t="n"/>
-      <c r="F54" s="52" t="n"/>
-      <c r="G54" s="52" t="n"/>
-      <c r="H54" s="52" t="n"/>
-      <c r="I54" s="52" t="n"/>
-      <c r="J54" s="52" t="n"/>
-      <c r="K54" s="52" t="n"/>
-      <c r="L54" s="52" t="n"/>
-      <c r="M54" s="52" t="n"/>
-      <c r="N54" s="52" t="n"/>
-      <c r="O54" s="52" t="n"/>
-      <c r="P54" s="52" t="n"/>
-      <c r="Q54" s="66">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
+      <c r="A54" s="79" t="n"/>
+      <c r="B54" s="79" t="n"/>
+      <c r="C54" s="79" t="n"/>
+      <c r="D54" s="79" t="n"/>
+      <c r="E54" s="79" t="n"/>
+      <c r="F54" s="79" t="n"/>
+      <c r="G54" s="79" t="n"/>
+      <c r="H54" s="79" t="n"/>
+      <c r="I54" s="79" t="n"/>
+      <c r="J54" s="79" t="n"/>
+      <c r="K54" s="79" t="n"/>
+      <c r="L54" s="79" t="n"/>
+      <c r="M54" s="79" t="n"/>
+      <c r="N54" s="79" t="n"/>
+      <c r="O54" s="79" t="n"/>
+      <c r="P54" s="79" t="n"/>
+      <c r="Q54" s="80" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="52" t="n"/>
-      <c r="B55" s="52" t="n"/>
-      <c r="C55" s="52" t="n"/>
-      <c r="D55" s="52" t="n"/>
-      <c r="E55" s="52" t="n"/>
-      <c r="F55" s="52" t="n"/>
-      <c r="G55" s="52" t="n"/>
-      <c r="H55" s="52" t="n"/>
-      <c r="I55" s="52" t="n"/>
-      <c r="J55" s="52" t="n"/>
-      <c r="K55" s="52" t="n"/>
-      <c r="L55" s="52" t="n"/>
-      <c r="M55" s="52" t="n"/>
-      <c r="N55" s="52" t="n"/>
-      <c r="O55" s="52" t="n"/>
-      <c r="P55" s="52" t="n"/>
-      <c r="Q55" s="66">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
+      <c r="A55" s="79" t="n"/>
+      <c r="B55" s="79" t="n"/>
+      <c r="C55" s="79" t="n"/>
+      <c r="D55" s="79" t="n"/>
+      <c r="E55" s="79" t="n"/>
+      <c r="F55" s="79" t="n"/>
+      <c r="G55" s="79" t="n"/>
+      <c r="H55" s="79" t="n"/>
+      <c r="I55" s="79" t="n"/>
+      <c r="J55" s="79" t="n"/>
+      <c r="K55" s="79" t="n"/>
+      <c r="L55" s="79" t="n"/>
+      <c r="M55" s="79" t="n"/>
+      <c r="N55" s="79" t="n"/>
+      <c r="O55" s="79" t="n"/>
+      <c r="P55" s="79" t="n"/>
+      <c r="Q55" s="80" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="52" t="n"/>
-      <c r="B56" s="52" t="n"/>
-      <c r="C56" s="52" t="n"/>
-      <c r="D56" s="52" t="n"/>
-      <c r="E56" s="52" t="n"/>
-      <c r="F56" s="52" t="n"/>
-      <c r="G56" s="52" t="n"/>
-      <c r="H56" s="52" t="n"/>
-      <c r="I56" s="52" t="n"/>
-      <c r="J56" s="52" t="n"/>
-      <c r="K56" s="52" t="n"/>
-      <c r="L56" s="52" t="n"/>
-      <c r="M56" s="52" t="n"/>
-      <c r="N56" s="52" t="n"/>
-      <c r="O56" s="52" t="n"/>
-      <c r="P56" s="52" t="n"/>
-      <c r="Q56" s="66">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
+      <c r="A56" s="79" t="n"/>
+      <c r="B56" s="79" t="n"/>
+      <c r="C56" s="79" t="n"/>
+      <c r="D56" s="79" t="n"/>
+      <c r="E56" s="79" t="n"/>
+      <c r="F56" s="79" t="n"/>
+      <c r="G56" s="79" t="n"/>
+      <c r="H56" s="79" t="n"/>
+      <c r="I56" s="79" t="n"/>
+      <c r="J56" s="79" t="n"/>
+      <c r="K56" s="79" t="n"/>
+      <c r="L56" s="79" t="n"/>
+      <c r="M56" s="79" t="n"/>
+      <c r="N56" s="79" t="n"/>
+      <c r="O56" s="79" t="n"/>
+      <c r="P56" s="79" t="n"/>
+      <c r="Q56" s="80" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="52" t="n"/>
-      <c r="B57" s="52" t="n"/>
-      <c r="C57" s="52" t="n"/>
-      <c r="D57" s="52" t="n"/>
-      <c r="E57" s="52" t="n"/>
-      <c r="F57" s="52" t="n"/>
-      <c r="G57" s="52" t="n"/>
-      <c r="H57" s="52" t="n"/>
-      <c r="I57" s="52" t="n"/>
-      <c r="J57" s="52" t="n"/>
-      <c r="K57" s="52" t="n"/>
-      <c r="L57" s="52" t="n"/>
-      <c r="M57" s="52" t="n"/>
-      <c r="N57" s="52" t="n"/>
-      <c r="O57" s="52" t="n"/>
-      <c r="P57" s="52" t="n"/>
-      <c r="Q57" s="66">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
+      <c r="A57" s="79" t="n"/>
+      <c r="B57" s="79" t="n"/>
+      <c r="C57" s="79" t="n"/>
+      <c r="D57" s="79" t="n"/>
+      <c r="E57" s="79" t="n"/>
+      <c r="F57" s="79" t="n"/>
+      <c r="G57" s="79" t="n"/>
+      <c r="H57" s="79" t="n"/>
+      <c r="I57" s="79" t="n"/>
+      <c r="J57" s="79" t="n"/>
+      <c r="K57" s="79" t="n"/>
+      <c r="L57" s="79" t="n"/>
+      <c r="M57" s="79" t="n"/>
+      <c r="N57" s="79" t="n"/>
+      <c r="O57" s="79" t="n"/>
+      <c r="P57" s="79" t="n"/>
+      <c r="Q57" s="80" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="52" t="n"/>
-      <c r="B58" s="52" t="n"/>
-      <c r="C58" s="52" t="n"/>
-      <c r="D58" s="52" t="n"/>
-      <c r="E58" s="52" t="n"/>
-      <c r="F58" s="52" t="n"/>
-      <c r="G58" s="52" t="n"/>
-      <c r="H58" s="52" t="n"/>
-      <c r="I58" s="52" t="n"/>
-      <c r="J58" s="52" t="n"/>
-      <c r="K58" s="52" t="n"/>
-      <c r="L58" s="52" t="n"/>
-      <c r="M58" s="52" t="n"/>
-      <c r="N58" s="52" t="n"/>
-      <c r="O58" s="52" t="n"/>
-      <c r="P58" s="52" t="n"/>
-      <c r="Q58" s="66">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
+      <c r="A58" s="79" t="n"/>
+      <c r="B58" s="79" t="n"/>
+      <c r="C58" s="79" t="n"/>
+      <c r="D58" s="79" t="n"/>
+      <c r="E58" s="79" t="n"/>
+      <c r="F58" s="79" t="n"/>
+      <c r="G58" s="79" t="n"/>
+      <c r="H58" s="79" t="n"/>
+      <c r="I58" s="79" t="n"/>
+      <c r="J58" s="79" t="n"/>
+      <c r="K58" s="79" t="n"/>
+      <c r="L58" s="79" t="n"/>
+      <c r="M58" s="79" t="n"/>
+      <c r="N58" s="79" t="n"/>
+      <c r="O58" s="79" t="n"/>
+      <c r="P58" s="79" t="n"/>
+      <c r="Q58" s="80" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="52" t="n"/>
-      <c r="B59" s="52" t="n"/>
-      <c r="C59" s="52" t="n"/>
-      <c r="D59" s="52" t="n"/>
-      <c r="E59" s="52" t="n"/>
-      <c r="F59" s="52" t="n"/>
-      <c r="G59" s="52" t="n"/>
-      <c r="H59" s="52" t="n"/>
-      <c r="I59" s="52" t="n"/>
-      <c r="J59" s="52" t="n"/>
-      <c r="K59" s="52" t="n"/>
-      <c r="L59" s="52" t="n"/>
-      <c r="M59" s="52" t="n"/>
-      <c r="N59" s="52" t="n"/>
-      <c r="O59" s="52" t="n"/>
-      <c r="P59" s="52" t="n"/>
-      <c r="Q59" s="66">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
+      <c r="A59" s="79" t="n"/>
+      <c r="B59" s="79" t="n"/>
+      <c r="C59" s="79" t="n"/>
+      <c r="D59" s="79" t="n"/>
+      <c r="E59" s="79" t="n"/>
+      <c r="F59" s="79" t="n"/>
+      <c r="G59" s="79" t="n"/>
+      <c r="H59" s="79" t="n"/>
+      <c r="I59" s="79" t="n"/>
+      <c r="J59" s="79" t="n"/>
+      <c r="K59" s="79" t="n"/>
+      <c r="L59" s="79" t="n"/>
+      <c r="M59" s="79" t="n"/>
+      <c r="N59" s="79" t="n"/>
+      <c r="O59" s="79" t="n"/>
+      <c r="P59" s="79" t="n"/>
+      <c r="Q59" s="80" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="52" t="n"/>
-      <c r="B60" s="52" t="n"/>
-      <c r="C60" s="52" t="n"/>
-      <c r="D60" s="52" t="n"/>
-      <c r="E60" s="52" t="n"/>
-      <c r="F60" s="52" t="n"/>
-      <c r="G60" s="52" t="n"/>
-      <c r="H60" s="52" t="n"/>
-      <c r="I60" s="52" t="n"/>
-      <c r="J60" s="52" t="n"/>
-      <c r="K60" s="52" t="n"/>
-      <c r="L60" s="52" t="n"/>
-      <c r="M60" s="52" t="n"/>
-      <c r="N60" s="52" t="n"/>
-      <c r="O60" s="52" t="n"/>
-      <c r="P60" s="52" t="n"/>
-      <c r="Q60" s="66">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
+      <c r="A60" s="79" t="n"/>
+      <c r="B60" s="79" t="n"/>
+      <c r="C60" s="79" t="n"/>
+      <c r="D60" s="79" t="n"/>
+      <c r="E60" s="79" t="n"/>
+      <c r="F60" s="79" t="n"/>
+      <c r="G60" s="79" t="n"/>
+      <c r="H60" s="79" t="n"/>
+      <c r="I60" s="79" t="n"/>
+      <c r="J60" s="79" t="n"/>
+      <c r="K60" s="79" t="n"/>
+      <c r="L60" s="79" t="n"/>
+      <c r="M60" s="79" t="n"/>
+      <c r="N60" s="79" t="n"/>
+      <c r="O60" s="79" t="n"/>
+      <c r="P60" s="79" t="n"/>
+      <c r="Q60" s="80" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="52" t="n"/>
-      <c r="B61" s="52" t="n"/>
-      <c r="C61" s="52" t="n"/>
-      <c r="D61" s="52" t="n"/>
-      <c r="E61" s="52" t="n"/>
-      <c r="F61" s="52" t="n"/>
-      <c r="G61" s="52" t="n"/>
-      <c r="H61" s="52" t="n"/>
-      <c r="I61" s="52" t="n"/>
-      <c r="J61" s="52" t="n"/>
-      <c r="K61" s="52" t="n"/>
-      <c r="L61" s="52" t="n"/>
-      <c r="M61" s="52" t="n"/>
-      <c r="N61" s="52" t="n"/>
-      <c r="O61" s="52" t="n"/>
-      <c r="P61" s="52" t="n"/>
-      <c r="Q61" s="66">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
+      <c r="A61" s="79" t="n"/>
+      <c r="B61" s="79" t="n"/>
+      <c r="C61" s="79" t="n"/>
+      <c r="D61" s="79" t="n"/>
+      <c r="E61" s="79" t="n"/>
+      <c r="F61" s="79" t="n"/>
+      <c r="G61" s="79" t="n"/>
+      <c r="H61" s="79" t="n"/>
+      <c r="I61" s="79" t="n"/>
+      <c r="J61" s="79" t="n"/>
+      <c r="K61" s="79" t="n"/>
+      <c r="L61" s="79" t="n"/>
+      <c r="M61" s="79" t="n"/>
+      <c r="N61" s="79" t="n"/>
+      <c r="O61" s="79" t="n"/>
+      <c r="P61" s="79" t="n"/>
+      <c r="Q61" s="80" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="52" t="n"/>
-      <c r="B62" s="52" t="n"/>
-      <c r="C62" s="52" t="n"/>
-      <c r="D62" s="52" t="n"/>
-      <c r="E62" s="52" t="n"/>
-      <c r="F62" s="52" t="n"/>
-      <c r="G62" s="52" t="n"/>
-      <c r="H62" s="52" t="n"/>
-      <c r="I62" s="52" t="n"/>
-      <c r="J62" s="52" t="n"/>
-      <c r="K62" s="52" t="n"/>
-      <c r="L62" s="52" t="n"/>
-      <c r="M62" s="52" t="n"/>
-      <c r="N62" s="52" t="n"/>
-      <c r="O62" s="52" t="n"/>
-      <c r="P62" s="52" t="n"/>
-      <c r="Q62" s="66">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
+      <c r="A62" s="79" t="n"/>
+      <c r="B62" s="79" t="n"/>
+      <c r="C62" s="79" t="n"/>
+      <c r="D62" s="79" t="n"/>
+      <c r="E62" s="79" t="n"/>
+      <c r="F62" s="79" t="n"/>
+      <c r="G62" s="79" t="n"/>
+      <c r="H62" s="79" t="n"/>
+      <c r="I62" s="79" t="n"/>
+      <c r="J62" s="79" t="n"/>
+      <c r="K62" s="79" t="n"/>
+      <c r="L62" s="79" t="n"/>
+      <c r="M62" s="79" t="n"/>
+      <c r="N62" s="79" t="n"/>
+      <c r="O62" s="79" t="n"/>
+      <c r="P62" s="79" t="n"/>
+      <c r="Q62" s="80" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q62"/>
@@ -3403,18 +3233,18 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4857,10 +4687,10 @@
           <t>مرجع سریع سناریوها و ثابت‌های ماژول EspLink</t>
         </is>
       </c>
-      <c r="B1" s="69" t="n"/>
-      <c r="C1" s="69" t="n"/>
-      <c r="D1" s="69" t="n"/>
-      <c r="E1" s="70" t="n"/>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="39" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="52" t="n"/>
@@ -5102,18 +4932,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — ماژول EspLink</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
-      <c r="D1" s="52" t="n"/>
-      <c r="E1" s="52" t="n"/>
-      <c r="F1" s="52" t="n"/>
-      <c r="G1" s="52" t="n"/>
-      <c r="H1" s="52" t="n"/>
-      <c r="I1" s="52" t="n"/>
-      <c r="J1" s="52" t="n"/>
-      <c r="K1" s="52" t="n"/>
-      <c r="L1" s="52" t="n"/>
-      <c r="M1" s="52" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="49" t="inlineStr">
@@ -5121,18 +4939,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="69" t="n"/>
-      <c r="C2" s="69" t="n"/>
-      <c r="D2" s="69" t="n"/>
-      <c r="E2" s="69" t="n"/>
-      <c r="F2" s="69" t="n"/>
-      <c r="G2" s="69" t="n"/>
-      <c r="H2" s="69" t="n"/>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="70" t="n"/>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="38" t="n"/>
+      <c r="G2" s="38" t="n"/>
+      <c r="H2" s="38" t="n"/>
+      <c r="I2" s="38" t="n"/>
+      <c r="J2" s="38" t="n"/>
+      <c r="K2" s="38" t="n"/>
+      <c r="L2" s="38" t="n"/>
+      <c r="M2" s="39" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="71" t="inlineStr">
@@ -5231,8 +5049,6 @@
           <t>تأیید نهایی اعتبارسنجی — ماژول EspLink</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
@@ -5240,8 +5056,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -5249,8 +5063,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
@@ -5637,8 +5449,6 @@
           <t>ماشین حالت ماژول لینک ESP (EspLink)</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="52" t="n"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -951,6 +951,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="78" t="inlineStr">
         <is>
@@ -1272,7 +1273,7 @@
       </c>
       <c r="C7" s="60" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="59" t="inlineStr">
@@ -1344,7 +1345,7 @@
       </c>
       <c r="C8" s="55" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="54" t="inlineStr">
@@ -2023,226 +2024,226 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="67.5" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="53" t="inlineStr">
         <is>
+          <t>EL-020</t>
+        </is>
+      </c>
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>قفل ترکیب چشمک سبز در پنل</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="inlineStr">
+        <is>
+          <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
+گام ۲: ببین پنل چه می‌کند.
+گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
+        </is>
+      </c>
+      <c r="F17" s="61" t="inlineStr">
+        <is>
+          <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
+        </is>
+      </c>
+      <c r="G17" s="61" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H17" s="59" t="inlineStr">
+        <is>
+          <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
+        </is>
+      </c>
+      <c r="I17" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="59" t="inlineStr">
+        <is>
+          <t>باید ببینید: پنل جلوی ترکیب ناسازگار چشمک سبز را می‌گیرد و ترکیب درست را قبول می‌کند. اگر ترکیب بد به دستگاه رسید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K17" s="59" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L17" s="57" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="59" t="n"/>
+      <c r="N17" s="59" t="n"/>
+      <c r="O17" s="61" t="inlineStr">
+        <is>
+          <t>8efddaa</t>
+        </is>
+      </c>
+      <c r="P17" s="61" t="n"/>
+      <c r="Q17" s="62">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="67.5" customHeight="1">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B17" s="54" t="inlineStr">
+      <c r="B18" s="54" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C17" s="55" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D17" s="54" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه در حال کار است</t>
         </is>
       </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>گام ۱: کاری کن یک پیام هشدار (alert) در پنل بیاید (مثلاً یک خطای واقعی مثل قطع باتری).
 گام ۲: متن پیام را بخوان و تأییدش کن.
 گام ۳: ببین کار دستگاه حین پیام مختل نشده.</t>
         </is>
       </c>
-      <c r="F17" s="56" t="inlineStr">
+      <c r="F18" s="56" t="inlineStr">
         <is>
           <t>هشدار واقعی در پنل</t>
         </is>
       </c>
-      <c r="G17" s="56" t="inlineStr">
+      <c r="G18" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H17" s="54" t="inlineStr">
+      <c r="H18" s="54" t="inlineStr">
         <is>
           <t>پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد</t>
         </is>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="I18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="54" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>باید ببینید: پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد. اگر هنگ یا پیام اشتباه دیدید، قبول نیست.</t>
         </is>
       </c>
-      <c r="K17" s="54" t="n"/>
-      <c r="L17" s="65" t="inlineStr">
+      <c r="K18" s="54" t="n"/>
+      <c r="L18" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M17" s="54" t="n"/>
-      <c r="N17" s="54" t="inlineStr">
+      <c r="M18" s="54" t="n"/>
+      <c r="N18" s="54" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O17" s="56" t="inlineStr">
+      <c r="O18" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P17" s="56" t="n"/>
-      <c r="Q17" s="58">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="67.5" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="P18" s="56" t="n"/>
+      <c r="Q18" s="58">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="53" t="inlineStr">
         <is>
           <t>EL-018</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>پنل دیالوگ confirm</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
         <is>
           <t>پنل باز است</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E19" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید (confirm) بیاید.
 گام ۲: این بار لغو (Cancel) را بزن.
 گام ۳: مقدار را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F18" s="61" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>لغو کردن پیام تأیید</t>
         </is>
       </c>
-      <c r="G18" s="61" t="inlineStr">
+      <c r="G19" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="59" t="inlineStr">
+      <c r="H19" s="59" t="inlineStr">
         <is>
           <t>با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست</t>
         </is>
       </c>
-      <c r="I18" s="59" t="inlineStr">
+      <c r="I19" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="59" t="inlineStr">
+      <c r="J19" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: با لغو، هیچ تغییری اعمال نشده و مقدار قبلی سر جاست. اگر با وجود لغو اعمال شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K18" s="59" t="n"/>
-      <c r="L18" s="65" t="inlineStr">
+      <c r="K19" s="59" t="n"/>
+      <c r="L19" s="65" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M18" s="59" t="n"/>
-      <c r="N18" s="59" t="inlineStr">
+      <c r="M19" s="59" t="n"/>
+      <c r="N19" s="59" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O18" s="61" t="inlineStr">
+      <c r="O19" s="61" t="inlineStr">
         <is>
           <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P18" s="61" t="n"/>
-      <c r="Q18" s="62">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t>EL-020</t>
-        </is>
-      </c>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>قفل ترکیب چشمک سبز در پنل</t>
-        </is>
-      </c>
-      <c r="C19" s="60" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D19" s="59" t="inlineStr">
-        <is>
-          <t>پنل باز؛ تنظیم‌های چراغ سبز شارژ کامل را می‌بینی</t>
-        </is>
-      </c>
-      <c r="E19" s="59" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل عددی بفرست که بخواهد سبز ثابتِ «شارژ کامل» را زودتر از پرشدن واقعی باتری روشن کند (ترکیب ناسازگار).
-گام ۲: ببین پنل چه می‌کند.
-گام ۳: یک ترکیب درست بفرست و قبول‌شدنش را ببین.</t>
-        </is>
-      </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>ترکیب ناسازگار و بعد سازگار از پنل</t>
-        </is>
-      </c>
-      <c r="G19" s="61" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H19" s="59" t="inlineStr">
-        <is>
-          <t>پنل جلوی ترکیب ناسازگار را می‌گیرد و نمی‌گذارد به دستگاه برسد؛ ترکیب درست قبول می‌شود</t>
-        </is>
-      </c>
-      <c r="I19" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="59" t="inlineStr">
-        <is>
-          <t>باید ببینید: پنل جلوی ترکیب ناسازگار چشمک سبز را می‌گیرد و ترکیب درست را قبول می‌کند. اگر ترکیب بد به دستگاه رسید، قبول نیست.</t>
-        </is>
-      </c>
-      <c r="K19" s="59" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: منطق نگهبان در ۶ حالت (مسدود/آزاد) درست بود و هر دو گیت سبز؛ تست پنل زنده/برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="L19" s="57" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M19" s="59" t="n"/>
-      <c r="N19" s="59" t="n"/>
-      <c r="O19" s="61" t="inlineStr">
-        <is>
-          <t>8efddaa</t>
         </is>
       </c>
       <c r="P19" s="61" t="n"/>
@@ -3243,8 +3244,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -899,7 +899,10 @@
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
         <is>
-          <t>EspLink | پل UART 921600 8N1 با DMA دوطرفه؛ پروتکل v1.2 (SET_PARAM/GET_PARAMS/TLM_LIVE/PARAM_REPORT/PARAMS_BULK) + مود تست دستی ID19</t>
+          <t>EspLink | این ماژول پل ارتباطی با ESP است.
+ارتباط سریال (UART) با سرعت 921600 و قالب 8N1 است و از DMA دوطرفه استفاده می‌کند.
+پروتکل نسخهٔ 1.2 است: تنظیم پارامتر (SET_PARAM)، خواندن پارامترها (GET_PARAMS)، دادهٔ زنده (TLM_LIVE)، گزارش پارامتر (PARAM_REPORT) و فرستادن یکجای پارامترها (PARAMS_BULK).
+یک مود تست دستی هم هست (شناسهٔ 19).</t>
         </is>
       </c>
     </row>
@@ -916,21 +919,23 @@
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
-          <t>فعال‌سازی با MODULE_ESP=1 (فقط همان یک خط)؛ CH_PD از PA8 توسط برد کنترل می‌شود.</t>
+          <t>برای فعال‌کردن، فقط یک خط را عوض کن: MODULE_ESP=1.
+پایهٔ CH_PD از PA8 و توسط خود برد کنترل می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="50" t="inlineStr">
         <is>
-          <t>قرارداد کامل در ESP_AGENT_SPEC.md v1.2؛ محدودیت‌های سمت ESP در README همین ماژول.</t>
+          <t>قرارداد کامل ارتباط در فایل ESP_AGENT_SPEC.md (نسخهٔ 1.2) است.
+محدودیت‌های سمت ESP در README همین ماژول نوشته شده است.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="48" t="inlineStr">
         <is>
-          <t>پنل وب سمت ESP در esp_link_panel/ (ممیزی خط‌به‌خط، کامیت 32098b4).</t>
+          <t>برنامهٔ پنل وب در پوشهٔ esp_link_panel/ است. ممیزی خط‌به‌خط انجام شده است (کامیت 32098b4).</t>
         </is>
       </c>
     </row>
@@ -940,14 +945,15 @@
     <row r="9">
       <c r="A9" s="48" t="inlineStr">
         <is>
-          <t>هشدار: تست‌های مود دستی فقط با بار ایمن (electronic load با clamp) و منبع محدودشده.</t>
+          <t>هشدار: تست‌های مود دستی فقط با بار ایمن انجام شود: بار الکترونیکی با محدودکننده و منبع محدودشده.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="48" t="inlineStr">
         <is>
-          <t>یادداشت: تست‌های Host و DOM پنل وب (خود برنامهٔ ESP) در این فرم ثبت شده‌اند؛ هیچ‌کدام جای تست واقعی برد، فلش و UART را نمی‌گیرند.</t>
+          <t>یادداشت: تست‌های روی کامپیوتر (Host) و تست‌های خود پنل وب (DOM) در این فرم نوشته شده‌اند.
+ولی هیچ‌کدام جای تست واقعی را نمی‌گیرند: برد، فلش و ارتباط سریال (UART) باید روی برد واقعی تست شوند.</t>
         </is>
       </c>
     </row>
@@ -955,8 +961,12 @@
     <row r="12">
       <c r="A12" s="78" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1083,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -1098,12 +1108,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -1179,7 +1189,7 @@
       <c r="N5" s="54" t="n"/>
       <c r="O5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
@@ -1251,7 +1261,7 @@
       <c r="N6" s="59" t="n"/>
       <c r="O6" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="61" t="n"/>
@@ -1323,7 +1333,7 @@
       <c r="N7" s="59" t="n"/>
       <c r="O7" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="61" t="n"/>
@@ -1395,7 +1405,7 @@
       <c r="N8" s="54" t="n"/>
       <c r="O8" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="56" t="n"/>
@@ -1466,7 +1476,7 @@
       <c r="N9" s="54" t="n"/>
       <c r="O9" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="56" t="n"/>
@@ -1537,7 +1547,7 @@
       <c r="N10" s="59" t="n"/>
       <c r="O10" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="61" t="n"/>
@@ -1609,7 +1619,7 @@
       <c r="N11" s="59" t="n"/>
       <c r="O11" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="61" t="n"/>
@@ -1681,7 +1691,7 @@
       <c r="N12" s="54" t="n"/>
       <c r="O12" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="56" t="n"/>
@@ -1714,8 +1724,8 @@
       <c r="E13" s="54" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ کالیبراسیون را بفرست.
-گام ۲: همان را از پنل بخوان (read-back).
-گام ۳: عدد برگشتی را با فرستاده مقایسه کن.</t>
+گام ۲: همان نقطه را از پنل بخوان.
+گام ۳: عدد برگشتی را با عدد فرستاده مقایسه کن.</t>
         </is>
       </c>
       <c r="F13" s="56" t="inlineStr">
@@ -1745,7 +1755,10 @@
       </c>
       <c r="K13" s="54" t="inlineStr">
         <is>
-          <t>Host PASS: DOM 331 check شامل summary نام‌محور، checkbox انتخاب همهٔ نمونه‌ها، modal یک‌تأییدی و write/readback همهٔ پارامترهای معتبر؛ Charger 53 check؛ برد اجرا نشده</t>
+          <t>تست روی کامپیوتر قبول شد:
+پنل (DOM): 331 بررسی. نام‌محور بودن خلاصه، تیک انتخاب همهٔ نمونه‌ها، پنجرهٔ تأیید تکی و نوشتن و خواندن همهٔ پارامترهای درست چک شد.
+شارژر: 53 بررسی.
+تست روی برد اجرا نشده است.</t>
         </is>
       </c>
       <c r="L13" s="57" t="inlineStr">
@@ -1755,7 +1768,7 @@
       </c>
       <c r="M13" s="54" t="inlineStr">
         <is>
-          <t>Host جای تست برد را نمی‌گیرد؛ برد باید با build جدید فلش شود</t>
+          <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. برد باید با بیلد تازه فلش شود.</t>
         </is>
       </c>
       <c r="N13" s="63" t="inlineStr">
@@ -1828,7 +1841,10 @@
       </c>
       <c r="K14" s="59" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل preflight، readback همهٔ calibrationهای معتبر، انتخاب انحصاری SWEEP/دستی با گام، تم کلیدهای پنل و update مستقل؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>تست روی کامپیوتر قبول شد:
+CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 324 بررسی.
+چک‌ها: پیش‌بررسی (preflight)، خواندن دوبارهٔ همهٔ کالیبراسیون‌های درست، انتخاب جدا بین جاروب (SWEEP) و دستی با گام، تم کلیدهای پنل و به‌روزرسانی جدا.
+اجرای روی برد فیزیکی انجام نشده است.</t>
         </is>
       </c>
       <c r="L14" s="57" t="inlineStr">
@@ -1838,7 +1854,7 @@
       </c>
       <c r="M14" s="59" t="inlineStr">
         <is>
-          <t>Host جای تست برد را نمی‌گیرد؛ با firmware جدید روی برد واقعی تکرار شود</t>
+          <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. با برنامهٔ تازه روی برد واقعی تکرار شود.</t>
         </is>
       </c>
       <c r="N14" s="64" t="inlineStr">
@@ -1911,7 +1927,10 @@
       </c>
       <c r="K15" s="54" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut 159 check، ESP 112 check، DOM پنل 324 check؛ شامل گیت readback کالیبراسیون، update مستقل، کلیدهای factory-reset یکدست و summary صفرنقطه؛ اجرای برد فیزیکی انجام نشده</t>
+          <t>تست روی کامپیوتر قبول شد:
+CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 324 بررسی.
+چک‌ها: گیت خواندن دوبارهٔ کالیبراسیون، به‌روزرسانی جدا، کلیدهای برگشت به کارخانه یکدست و خلاصهٔ نقطهٔ صفر.
+اجرای روی برد فیزیکی انجام نشده است.</t>
         </is>
       </c>
       <c r="L15" s="57" t="inlineStr">
@@ -1921,7 +1940,7 @@
       </c>
       <c r="M15" s="54" t="inlineStr">
         <is>
-          <t>Host جای تست برد را نمی‌گیرد؛ transition صفرنقطه و invalid-channel باید روی برد واقعی هم تکرار شود</t>
+          <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. گذر نقطهٔ صفر و کانال نامعتبر باید روی برد واقعی هم تکرار شود.</t>
         </is>
       </c>
       <c r="N15" s="63" t="inlineStr">
@@ -1995,7 +2014,10 @@
       </c>
       <c r="K16" s="59" t="inlineStr">
         <is>
-          <t>Host PASS: parser=14، NVM، CalLut=159، ESP=112، DOM=331 و Charger=53؛ audit consistency با stamp و preview رسمی PASS؛ تست فیزیکی برد انجام نشده</t>
+          <t>تست روی کامپیوتر قبول شد:
+پارسر: 14 بررسی. حافظهٔ ماندگار (NVM). CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 331 بررسی. شارژر: 53 بررسی.
+ممیزی سازگاری، مهر نسخه (stamp) و پیش‌نمایش رسمی هم قبول شدند.
+تست فیزیکی برد انجام نشده است.</t>
         </is>
       </c>
       <c r="L16" s="57" t="inlineStr">
@@ -2005,7 +2027,8 @@
       </c>
       <c r="M16" s="59" t="inlineStr">
         <is>
-          <t>Host جای تست فیزیکی STM32/ESP، UART، فلش و persistence را نمی‌گیرد؛ روی برد واقعی با تزریق/اندازه‌گیری flush تکرار شود</t>
+          <t>تست روی کامپیوتر جای تست فیزیکی را نمی‌گیرد: نه STM32 و ESP، نه ارتباط سریال، نه فلش و نه ماندگاری.
+روی برد واقعی با تزریق و اندازه‌گیری دوباره انجام شود و خالی‌کردن حافظه (flush) هم چک شود.</t>
         </is>
       </c>
       <c r="N16" s="64" t="inlineStr">
@@ -2123,9 +2146,9 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>گام ۱: کاری کن یک پیام هشدار (alert) در پنل بیاید (مثلاً یک خطای واقعی مثل قطع باتری).
+          <t>گام ۱: کاری کن یک پیام هشدار در پنل بیاید. مثلاً یک خطای واقعی بساز، مثل قطع باتری.
 گام ۲: متن پیام را بخوان و تأییدش کن.
-گام ۳: ببین کار دستگاه حین پیام مختل نشده.</t>
+گام ۳: ببین کار دستگاه هنگام پیام به هم نریخته باشد.</t>
         </is>
       </c>
       <c r="F18" s="56" t="inlineStr">
@@ -2199,8 +2222,8 @@
       </c>
       <c r="E19" s="59" t="inlineStr">
         <is>
-          <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید (confirm) بیاید.
-گام ۲: این بار لغو (Cancel) را بزن.
+          <t>گام ۱: یک تغییر مهم را در پنل شروع کن تا پیام تأیید بیاید.
+گام ۲: این بار دکمهٔ «لغو» (Cancel) را بزن.
 گام ۳: مقدار را دوباره بخوان.</t>
         </is>
       </c>
@@ -2314,7 +2337,7 @@
       <c r="N20" s="54" t="n"/>
       <c r="O20" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P20" s="56" t="n"/>
@@ -2385,7 +2408,7 @@
       <c r="N21" s="59" t="n"/>
       <c r="O21" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P21" s="61" t="n"/>
@@ -3389,7 +3412,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -3414,12 +3437,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -3496,7 +3519,7 @@
       <c r="N5" s="54" t="n"/>
       <c r="O5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
@@ -4095,7 +4118,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -4120,12 +4143,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -4203,7 +4226,7 @@
       <c r="N5" s="59" t="n"/>
       <c r="O5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="61" t="n"/>
@@ -5001,7 +5024,7 @@
       </c>
       <c r="J3" s="71" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="71" t="inlineStr">
@@ -5120,12 +5143,12 @@
     <row r="8">
       <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="52" t="n"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -193,7 +193,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +233,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -321,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -517,6 +527,39 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -890,7 +933,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول EspLink</t>
         </is>
@@ -907,7 +950,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="82" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -917,7 +960,7 @@
       <c r="A4" s="48" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>برای فعال‌کردن، فقط یک خط را عوض کن: MODULE_ESP=1.
 پایهٔ CH_PD از PA8 و توسط خود برد کنترل می‌شود.</t>
@@ -925,7 +968,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>قرارداد کامل ارتباط در فایل ESP_AGENT_SPEC.md (نسخهٔ 1.2) است.
 محدودیت‌های سمت ESP در README همین ماژول نوشته شده است.</t>
@@ -933,7 +976,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>برنامهٔ پنل وب در پوشهٔ esp_link_panel/ است. ممیزی خط‌به‌خط انجام شده است (کامیت 32098b4).</t>
         </is>
@@ -943,14 +986,14 @@
       <c r="A8" s="48" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>هشدار: تست‌های مود دستی فقط با بار ایمن انجام شود: بار الکترونیکی با محدودکننده و منبع محدودشده.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های روی کامپیوتر (Host) و تست‌های خود پنل وب (DOM) در این فرم نوشته شده‌اند.
 ولی هیچ‌کدام جای تست واقعی را نمی‌گیرند: برد، فلش و ارتباط سریال (UART) باید روی برد واقعی تست شوند.</t>
@@ -959,7 +1002,7 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>اولویت‌ها ساده‌اند:
 «بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
@@ -1020,7 +1063,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول EspLink</t>
         </is>
@@ -1041,87 +1084,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1133,48 +1176,48 @@
           <t>EL-001</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>CH_PD و بوت</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>کابل ESP و پنل آماده است؛ دستگاه خاموش</t>
         </is>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: پنل را باز کن و ببین ارتباط برقرار و عددها زنده می‌شوند.</t>
         </is>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>روشن‌کردن دستگاه با پنل</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>پنل بالا می‌آید و عددهای زندهٔ دستگاه را نشان می‌دهد</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>ارتباط پایدار</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: پنل بالا می‌آید و عددهای زندهٔ دستگاه را نشان می‌دهد. اگر پنل نیامد یا عددی نبود، قبول نیست.</t>
         </is>
@@ -1187,13 +1230,13 @@
       </c>
       <c r="M5" s="54" t="n"/>
       <c r="N5" s="54" t="n"/>
-      <c r="O5" s="56" t="inlineStr">
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
-      <c r="Q5" s="58">
+      <c r="Q5" s="62">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -1204,49 +1247,49 @@
           <t>EL-002</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>تله‌متری زنده</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="87" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="86" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل باز است؛ یک مولتی‌متر دستی داری</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="86" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ باتری و ورودی را روی پنل بخوان.
 گام ۲: همان‌ها را با مولتی‌متر روی ترمینال اندازه بگیر.
 گام ۳: ولتاژ ورودی را کمی عوض کن و تازه‌شدن عدد پنل را ببین.</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="88" t="inlineStr">
         <is>
           <t>مقایسهٔ زندهٔ پنل با مولتی‌متر</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr">
+      <c r="H6" s="86" t="inlineStr">
         <is>
           <t>عددهای پنل زنده و نزدیک مولتی‌مترند و با تغییر ولتاژ همان لحظه عوض می‌شوند</t>
         </is>
       </c>
-      <c r="I6" s="59" t="inlineStr">
+      <c r="I6" s="86" t="inlineStr">
         <is>
           <t>به‌روزرسانی پیوسته</t>
         </is>
       </c>
-      <c r="J6" s="59" t="inlineStr">
+      <c r="J6" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: عددهای پنل زنده‌اند، نزدیک مولتی‌مترند و با تغییر ولتاژ همان لحظه عوض می‌شوند. اگر عدد یخ زد یا خیلی دور بود، قبول نیست.</t>
         </is>
@@ -1259,13 +1302,13 @@
       </c>
       <c r="M6" s="59" t="n"/>
       <c r="N6" s="59" t="n"/>
-      <c r="O6" s="61" t="inlineStr">
+      <c r="O6" s="88" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="61" t="n"/>
-      <c r="Q6" s="62">
+      <c r="Q6" s="89">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -1348,49 +1391,49 @@
           <t>EL-005</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>پارامتر ۱۹ مود دستی</t>
         </is>
       </c>
-      <c r="C8" s="55" t="inlineStr">
+      <c r="C8" s="87" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="86" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E8" s="54" t="inlineStr">
+      <c r="E8" s="86" t="inlineStr">
         <is>
           <t>گام ۱: پارامتر مود تست دستی شارژر (شمارهٔ ۱۹) را از پنل روشن کن.
 گام ۲: ببین شارژر به مود دستی می‌رود.
 گام ۳: خاموشش کن و برگشت به شارژ خودکار را ببین.</t>
         </is>
       </c>
-      <c r="F8" s="56" t="inlineStr">
+      <c r="F8" s="88" t="inlineStr">
         <is>
           <t>روشن/خاموش پارامتر ۱۹ از پنل</t>
         </is>
       </c>
-      <c r="G8" s="56" t="inlineStr">
+      <c r="G8" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="54" t="inlineStr">
+      <c r="H8" s="86" t="inlineStr">
         <is>
           <t>با روشن‌کردن، شارژر دستی و با خاموش‌کردن، خودکار می‌شود</t>
         </is>
       </c>
-      <c r="I8" s="54" t="inlineStr">
+      <c r="I8" s="86" t="inlineStr">
         <is>
           <t>تابع پنل</t>
         </is>
       </c>
-      <c r="J8" s="54" t="inlineStr">
+      <c r="J8" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: با روشن‌کردن مود دستی شارژر دستی و با خاموش‌کردنش خودکار می‌شود. اگر در یک مود گیر کرد، قبول نیست.</t>
         </is>
@@ -1403,13 +1446,13 @@
       </c>
       <c r="M8" s="54" t="n"/>
       <c r="N8" s="54" t="n"/>
-      <c r="O8" s="56" t="inlineStr">
+      <c r="O8" s="88" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="56" t="n"/>
-      <c r="Q8" s="58">
+      <c r="Q8" s="89">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -1420,48 +1463,48 @@
           <t>EL-003</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>GET_PARAMS → BULK</t>
         </is>
       </c>
-      <c r="C9" s="55" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E9" s="54" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>گام ۱: از پنل فهرست پارامترها را کامل بخوان.
 گام ۲: چند مقدار معلوم (مثلاً سقف جریان شارژ) را با رفتار واقعی دستگاه مقایسه کن.</t>
         </is>
       </c>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>خواندن کامل پارامترها از پنل</t>
         </is>
       </c>
-      <c r="G9" s="56" t="inlineStr">
+      <c r="G9" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="54" t="inlineStr">
+      <c r="H9" s="59" t="inlineStr">
         <is>
           <t>همهٔ پارامترها با مقدارهای واقعی دستگاه برمی‌گردند</t>
         </is>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="I9" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J9" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: همهٔ پارامترها با مقدارهای واقعی دستگاه در پنل برمی‌گردند. اگر مقدار خالی یا اشتباه بود، قبول نیست.</t>
         </is>
@@ -1474,13 +1517,13 @@
       </c>
       <c r="M9" s="54" t="n"/>
       <c r="N9" s="54" t="n"/>
-      <c r="O9" s="56" t="inlineStr">
+      <c r="O9" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="56" t="n"/>
-      <c r="Q9" s="58">
+      <c r="Q9" s="62">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -1491,48 +1534,48 @@
           <t>EL-006</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>تغذیه ددمن با هر فریم</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="86" t="inlineStr">
         <is>
           <t>پنل باز است و دستگاه در حال کار عادی</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="86" t="inlineStr">
         <is>
           <t>گام ۱: پنل را نیم ساعت باز نگه دار و دستگاه را به کارش بگذار.
 گام ۲: هر از چندی نگاه کن ارتباط زنده مانده یا نه.</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
+      <c r="F10" s="88" t="inlineStr">
         <is>
           <t>نیم ساعت ارتباط باز</t>
         </is>
       </c>
-      <c r="G10" s="61" t="inlineStr">
+      <c r="G10" s="88" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H10" s="59" t="inlineStr">
+      <c r="H10" s="86" t="inlineStr">
         <is>
           <t>ارتباط در تمام مدت زنده می‌ماند و عددها تازه می‌شوند</t>
         </is>
       </c>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="I10" s="86" t="inlineStr">
         <is>
           <t>بدون افتادن</t>
         </is>
       </c>
-      <c r="J10" s="59" t="inlineStr">
+      <c r="J10" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: ارتباط در تمام مدت زنده می‌ماند و عددها تازه می‌شوند. اگر بی‌دلیل افتاد، قبول نیست.</t>
         </is>
@@ -1545,13 +1588,13 @@
       </c>
       <c r="M10" s="59" t="n"/>
       <c r="N10" s="59" t="n"/>
-      <c r="O10" s="61" t="inlineStr">
+      <c r="O10" s="88" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="61" t="n"/>
-      <c r="Q10" s="62">
+      <c r="Q10" s="89">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -1634,49 +1677,49 @@
           <t>EL-011</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>state 9 و b5</t>
         </is>
       </c>
-      <c r="C12" s="55" t="inlineStr">
+      <c r="C12" s="87" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="54" t="inlineStr">
+      <c r="D12" s="86" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E12" s="54" t="inlineStr">
+      <c r="E12" s="86" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را به شارژ بزن و وضعیت شارژر را در پنل بخوان.
 گام ۲: شارژ را قطع کن (برق شهر را بکش) و دوباره وضعیت را بخوان.
 گام ۳: هر دو را با چیزی که روی دستگاه می‌بینی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F12" s="56" t="inlineStr">
+      <c r="F12" s="88" t="inlineStr">
         <is>
           <t>شروع و قطع شارژ جلوی پنل</t>
         </is>
       </c>
-      <c r="G12" s="56" t="inlineStr">
+      <c r="G12" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="54" t="inlineStr">
+      <c r="H12" s="86" t="inlineStr">
         <is>
           <t>وضعیت شارژر در پنل در هر دو حالت با واقعیت یکی است</t>
         </is>
       </c>
-      <c r="I12" s="54" t="inlineStr">
+      <c r="I12" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="54" t="inlineStr">
+      <c r="J12" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: وضعیت شارژر در پنل در هر دو حالت با واقعیت دستگاه یکی است. اگر پنل وضعیت دروغ نشان داد، قبول نیست.</t>
         </is>
@@ -1689,13 +1732,13 @@
       </c>
       <c r="M12" s="54" t="n"/>
       <c r="N12" s="54" t="n"/>
-      <c r="O12" s="56" t="inlineStr">
+      <c r="O12" s="88" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="56" t="n"/>
-      <c r="Q12" s="58">
+      <c r="Q12" s="89">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -1706,54 +1749,54 @@
           <t>EL-013</t>
         </is>
       </c>
-      <c r="B13" s="54" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>کالیبراسیون و read-back</t>
         </is>
       </c>
-      <c r="C13" s="55" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>پنل باز و راهنمای کالیبراسیون را می‌دانی</t>
         </is>
       </c>
-      <c r="E13" s="54" t="inlineStr">
+      <c r="E13" s="59" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ کالیبراسیون را بفرست.
 گام ۲: همان نقطه را از پنل بخوان.
 گام ۳: عدد برگشتی را با عدد فرستاده مقایسه کن.</t>
         </is>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>فرستادن و خواندن کالیبراسیون</t>
         </is>
       </c>
-      <c r="G13" s="56" t="inlineStr">
+      <c r="G13" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="54" t="inlineStr">
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>عدد برگشتی دقیقاً همان فرستاده است</t>
         </is>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J13" s="54" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: عدد برگشتی از دستگاه دقیقاً همان عدد فرستاده‌شده است. اگر اختلاف دیدید، قبول نیست.</t>
         </is>
       </c>
-      <c r="K13" s="54" t="inlineStr">
+      <c r="K13" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد:
 پنل (DOM): 331 بررسی. نام‌محور بودن خلاصه، تیک انتخاب همهٔ نمونه‌ها، پنجرهٔ تأیید تکی و نوشتن و خواندن همهٔ پارامترهای درست چک شد.
@@ -1766,23 +1809,23 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="54" t="inlineStr">
+      <c r="M13" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. برد باید با بیلد تازه فلش شود.</t>
         </is>
       </c>
-      <c r="N13" s="63" t="inlineStr">
+      <c r="N13" s="64" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/Tester/host_test_charger.py؛ tools/check_firmware_syntax.sh</t>
         </is>
       </c>
-      <c r="O13" s="56" t="inlineStr">
+      <c r="O13" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P13" s="56" t="n"/>
-      <c r="Q13" s="58">
+      <c r="Q13" s="62">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
@@ -1793,53 +1836,53 @@
           <t>EL-014</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="86" t="inlineStr">
         <is>
           <t>LUT readback عددبه‌عدد</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="87" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="86" t="inlineStr">
         <is>
           <t>پنل باز و یک جدول LUT ذخیره شده است</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="E14" s="86" t="inlineStr">
         <is>
           <t>گام ۱: جدول را از پنل کامل بخوان.
 گام ۲: چند عددش را با جدولی که قبلاً فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F14" s="61" t="inlineStr">
+      <c r="F14" s="88" t="inlineStr">
         <is>
           <t>خواندن کامل جدول از پنل</t>
         </is>
       </c>
-      <c r="G14" s="61" t="inlineStr">
+      <c r="G14" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="59" t="inlineStr">
+      <c r="H14" s="86" t="inlineStr">
         <is>
           <t>جدول عددبه‌عدد همان ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست</t>
         </is>
       </c>
-      <c r="I14" s="59" t="inlineStr">
+      <c r="I14" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="59" t="inlineStr">
+      <c r="J14" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: جدول برگشتی عددبه‌عدد همان جدول ذخیره‌شده است؛ هیچ عددی جابه‌جا یا کم نیست. اگر اختلافی دیدید، قبول نیست.</t>
         </is>
       </c>
-      <c r="K14" s="59" t="inlineStr">
+      <c r="K14" s="86" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد:
 CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 324 بررسی.
@@ -1852,23 +1895,23 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="59" t="inlineStr">
+      <c r="M14" s="86" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. با برنامهٔ تازه روی برد واقعی تکرار شود.</t>
         </is>
       </c>
-      <c r="N14" s="64" t="inlineStr">
+      <c r="N14" s="90" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/run_esp_tests.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O14" s="61" t="inlineStr">
+      <c r="O14" s="88" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P14" s="61" t="n"/>
-      <c r="Q14" s="62">
+      <c r="Q14" s="89">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -1879,53 +1922,53 @@
           <t>EL-015</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>صفرنقطه و کانال نامعتبر</t>
         </is>
       </c>
-      <c r="C15" s="55" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="54" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr">
         <is>
           <t>پنل باز و جدول سالمی ذخیره است</t>
         </is>
       </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="E15" s="59" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک نقطهٔ صفر یا کانال ناموجود بفرست.
 گام ۲: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F15" s="56" t="inlineStr">
+      <c r="F15" s="61" t="inlineStr">
         <is>
           <t>فرستادن نقطهٔ صفر/کانال بد</t>
         </is>
       </c>
-      <c r="G15" s="56" t="inlineStr">
+      <c r="G15" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="54" t="inlineStr">
+      <c r="H15" s="59" t="inlineStr">
         <is>
           <t>دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند</t>
         </is>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="I15" s="59" t="inlineStr">
         <is>
           <t>حفظ جدول قبلی</t>
         </is>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="J15" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: دستگاه ورودی خراب را نمی‌پذیرد و جدول قبلی سالم می‌ماند. اگر جدول خراب شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K15" s="54" t="inlineStr">
+      <c r="K15" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد:
 CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 324 بررسی.
@@ -1938,23 +1981,23 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="54" t="inlineStr">
+      <c r="M15" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. گذر نقطهٔ صفر و کانال نامعتبر باید روی برد واقعی هم تکرار شود.</t>
         </is>
       </c>
-      <c r="N15" s="63" t="inlineStr">
+      <c r="N15" s="64" t="inlineStr">
         <is>
           <t>esp_link_panel/Tester/host_test_scenario_cards.js؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O15" s="56" t="inlineStr">
+      <c r="O15" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P15" s="56" t="n"/>
-      <c r="Q15" s="58">
+      <c r="Q15" s="62">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
@@ -1965,54 +2008,54 @@
           <t>EL-016</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="87" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="86" t="inlineStr">
         <is>
           <t>پنل باز و جدولی ذخیره است</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E16" s="86" t="inlineStr">
         <is>
           <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
 گام ۲: برق دستگاه را قطع و وصل کن.
 گام ۳: جدول را دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F16" s="61" t="inlineStr">
+      <c r="F16" s="88" t="inlineStr">
         <is>
           <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G16" s="61" t="inlineStr">
+      <c r="G16" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="59" t="inlineStr">
+      <c r="H16" s="86" t="inlineStr">
         <is>
           <t>جدول پاک مانده و بعد از روشن‌شدن برنمی‌گردد</t>
         </is>
       </c>
-      <c r="I16" s="59" t="inlineStr">
+      <c r="I16" s="86" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J16" s="59" t="inlineStr">
+      <c r="J16" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: جدول پاک‌شده بعد از خاموش و روشن‌کردن هم برنمی‌گردد. اگر برگشت، قبول نیست.</t>
         </is>
       </c>
-      <c r="K16" s="59" t="inlineStr">
+      <c r="K16" s="86" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد:
 پارسر: 14 بررسی. حافظهٔ ماندگار (NVM). CalLut: 159 بررسی. ESP: 112 بررسی. پنل (DOM): 331 بررسی. شارژر: 53 بررسی.
@@ -2025,24 +2068,24 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="59" t="inlineStr">
+      <c r="M16" s="86" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست فیزیکی را نمی‌گیرد: نه STM32 و ESP، نه ارتباط سریال، نه فلش و نه ماندگاری.
 روی برد واقعی با تزریق و اندازه‌گیری دوباره انجام شود و خالی‌کردن حافظه (flush) هم چک شود.</t>
         </is>
       </c>
-      <c r="N16" s="64" t="inlineStr">
+      <c r="N16" s="90" t="inlineStr">
         <is>
           <t>Firmware/Modules/EspLink/Tester/run_host_test_parser.sh؛ run_host_test_nvm.sh؛ Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js؛ tools/audit_consistency.py</t>
         </is>
       </c>
-      <c r="O16" s="61" t="inlineStr">
+      <c r="O16" s="88" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P16" s="61" t="n"/>
-      <c r="Q16" s="62">
+      <c r="Q16" s="89">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -2129,49 +2172,49 @@
           <t>EL-017</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="86" t="inlineStr">
         <is>
           <t>پنل دیالوگ alert</t>
         </is>
       </c>
-      <c r="C18" s="55" t="inlineStr">
+      <c r="C18" s="87" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D18" s="54" t="inlineStr">
+      <c r="D18" s="86" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه در حال کار است</t>
         </is>
       </c>
-      <c r="E18" s="54" t="inlineStr">
+      <c r="E18" s="86" t="inlineStr">
         <is>
           <t>گام ۱: کاری کن یک پیام هشدار در پنل بیاید. مثلاً یک خطای واقعی بساز، مثل قطع باتری.
 گام ۲: متن پیام را بخوان و تأییدش کن.
 گام ۳: ببین کار دستگاه هنگام پیام به هم نریخته باشد.</t>
         </is>
       </c>
-      <c r="F18" s="56" t="inlineStr">
+      <c r="F18" s="88" t="inlineStr">
         <is>
           <t>هشدار واقعی در پنل</t>
         </is>
       </c>
-      <c r="G18" s="56" t="inlineStr">
+      <c r="G18" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="54" t="inlineStr">
+      <c r="H18" s="86" t="inlineStr">
         <is>
           <t>پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد</t>
         </is>
       </c>
-      <c r="I18" s="54" t="inlineStr">
+      <c r="I18" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="54" t="inlineStr">
+      <c r="J18" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: پیام درست و خوانا می‌آید، با تأیید بسته می‌شود و کار دستگاه ادامه دارد. اگر هنگ یا پیام اشتباه دیدید، قبول نیست.</t>
         </is>
@@ -2183,18 +2226,18 @@
         </is>
       </c>
       <c r="M18" s="54" t="n"/>
-      <c r="N18" s="54" t="inlineStr">
+      <c r="N18" s="86" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O18" s="56" t="inlineStr">
+      <c r="O18" s="88" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P18" s="56" t="n"/>
-      <c r="Q18" s="58">
+      <c r="Q18" s="89">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -2281,48 +2324,48 @@
           <t>EL-007</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>سرریز ring</t>
         </is>
       </c>
-      <c r="C20" s="56" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D20" s="54" t="inlineStr">
+      <c r="D20" s="86" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E20" s="54" t="inlineStr">
+      <c r="E20" s="86" t="inlineStr">
         <is>
           <t>گام ۱: چند پارامتر را پشت سر هم و سریع از پنل عوض کن.
 گام ۲: بعد همه را یکی‌یکی بخوان و با چیزی که فرستادی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F20" s="56" t="inlineStr">
+      <c r="F20" s="88" t="inlineStr">
         <is>
           <t>تغییر سریع چند پارامتر</t>
         </is>
       </c>
-      <c r="G20" s="56" t="inlineStr">
+      <c r="G20" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="54" t="inlineStr">
+      <c r="H20" s="86" t="inlineStr">
         <is>
           <t>هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند</t>
         </is>
       </c>
-      <c r="I20" s="54" t="inlineStr">
+      <c r="I20" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="54" t="inlineStr">
+      <c r="J20" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: هیچ تغییری گم نمی‌شود و پنل و دستگاه هنگ نمی‌کنند. اگر تغییری گم شد یا هنگ دیدید، قبول نیست.</t>
         </is>
@@ -2335,13 +2378,13 @@
       </c>
       <c r="M20" s="54" t="n"/>
       <c r="N20" s="54" t="n"/>
-      <c r="O20" s="56" t="inlineStr">
+      <c r="O20" s="88" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P20" s="56" t="n"/>
-      <c r="Q20" s="58">
+      <c r="Q20" s="89">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
@@ -2423,49 +2466,49 @@
           <t>EL-019</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>صف دیالوگ PMQ</t>
         </is>
       </c>
-      <c r="C22" s="56" t="inlineStr">
+      <c r="C22" s="88" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D22" s="54" t="inlineStr">
+      <c r="D22" s="86" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E22" s="54" t="inlineStr">
+      <c r="E22" s="86" t="inlineStr">
         <is>
           <t>گام ۱: پشت سر هم چند پیام/دیالوگ بساز (چند خطا یا چند تأیید).
 گام ۲: ببین به نوبت نشان داده می‌شوند.
 گام ۳: همه را ببند.</t>
         </is>
       </c>
-      <c r="F22" s="56" t="inlineStr">
+      <c r="F22" s="88" t="inlineStr">
         <is>
           <t>چند پیام پشت سر هم</t>
         </is>
       </c>
-      <c r="G22" s="56" t="inlineStr">
+      <c r="G22" s="88" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H22" s="54" t="inlineStr">
+      <c r="H22" s="86" t="inlineStr">
         <is>
           <t>پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند</t>
         </is>
       </c>
-      <c r="I22" s="54" t="inlineStr">
+      <c r="I22" s="86" t="inlineStr">
         <is>
           <t>صف مرتب</t>
         </is>
       </c>
-      <c r="J22" s="54" t="inlineStr">
+      <c r="J22" s="86" t="inlineStr">
         <is>
           <t>باید ببینید: پیام‌ها به نوبت و بدون گم‌شدن و قاطی‌شدن نشان داده می‌شوند. اگر پیامی گم یا قاطی شد، قبول نیست.</t>
         </is>
@@ -2478,13 +2521,13 @@
       </c>
       <c r="M22" s="54" t="n"/>
       <c r="N22" s="54" t="n"/>
-      <c r="O22" s="56" t="inlineStr">
+      <c r="O22" s="88" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P22" s="56" t="n"/>
-      <c r="Q22" s="58">
+      <c r="Q22" s="89">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
@@ -3305,7 +3348,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -3370,87 +3413,87 @@
       <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3462,49 +3505,49 @@
           <t>EL-009</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>فیزیکال 921600</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>اسکوپ روی PA9/PA10</t>
         </is>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: اسیلوسکوپ را روی پایه‌های PA9 و PA10 (UART) بگذار.
 گام ۲: شکل موج و نرخ باد را بخوان: باید 921600 با قالب 8N1 باشد.
 گام ۳: 60 ثانیه تبادل واقعی را زیر نظر بگیر؛ هیچ فریم خرابی نباید دیده شود.</t>
         </is>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>921600 8N1 با درام DDR و بدون خطا</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>بدون فریم خراب در 60s</t>
         </is>
@@ -3517,13 +3560,13 @@
       </c>
       <c r="M5" s="54" t="n"/>
       <c r="N5" s="54" t="n"/>
-      <c r="O5" s="56" t="inlineStr">
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
-      <c r="Q5" s="58" t="inlineStr">
+      <c r="Q5" s="62" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3984,7 +4027,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4011,7 +4054,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -4076,87 +4119,87 @@
       <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4706,7 +4749,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="92" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول EspLink</t>
         </is>
@@ -4951,14 +4994,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول EspLink</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="82" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
@@ -5068,7 +5111,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول EspLink</t>
         </is>
@@ -5305,7 +5348,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5317,7 +5360,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -5373,7 +5416,7 @@
       <c r="B7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="76" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -5409,7 +5452,7 @@
       <c r="B12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -5460,7 +5503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5474,11 +5517,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="52" t="n"/>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -5490,7 +5529,6 @@
           <t>EspLink_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5503,7 +5541,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="52" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -5516,7 +5553,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="52" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -5524,13 +5560,13 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="52" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -5538,7 +5574,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,8 +192,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -243,6 +259,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -560,6 +581,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -926,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1000,7 +1042,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="85" t="inlineStr">
         <is>
@@ -1010,6 +1051,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1060,12 +1113,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول EspLink</t>
+        </is>
+      </c>
+      <c r="T1" s="96" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1075,6 +1136,14 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="T2" s="97" t="inlineStr">
+        <is>
+          <t>ارتباط برقرار است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U2" s="98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -1082,6 +1151,11 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="T3" s="99" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="82" t="inlineStr">
@@ -1167,6 +1241,11 @@
       <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="R4" s="82" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
         </is>
       </c>
     </row>
@@ -1240,6 +1319,10 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="95">
+        <f>IF($U$2=1,"ESP بالا آمده و ارتباط برقرار است؛ پنل باید باز شود","ارتباط نیست: پنل داده‌ای ندارد")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="53" t="inlineStr">
@@ -1312,6 +1395,10 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="95">
+        <f>IF($U$2=1,"تله‌متری زنده در پنل تازه می‌شود","تله‌متری تازه نمی‌شود؛ آخرین عددها می‌مانند")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="53" t="inlineStr">
@@ -1384,6 +1471,11 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="53" t="inlineStr">
@@ -1456,6 +1548,11 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="53" t="inlineStr">
@@ -1527,6 +1624,11 @@
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
+      <c r="R9" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="53" t="inlineStr">
@@ -1598,6 +1700,11 @@
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
+      <c r="R10" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="53" t="inlineStr">
@@ -1670,6 +1777,11 @@
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
+      <c r="R11" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="53" t="inlineStr">
@@ -1741,6 +1853,11 @@
       <c r="Q12" s="89">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
+      </c>
+      <c r="R12" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
@@ -1829,6 +1946,11 @@
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
+      <c r="R13" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="53" t="inlineStr">
@@ -1915,6 +2037,11 @@
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
+      <c r="R14" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="67.5" customHeight="1">
       <c r="A15" s="53" t="inlineStr">
@@ -2001,6 +2128,11 @@
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
+      <c r="R15" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="81" customHeight="1">
       <c r="A16" s="53" t="inlineStr">
@@ -2089,6 +2221,11 @@
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
+      <c r="R16" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="53" t="inlineStr">
@@ -2165,6 +2302,11 @@
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
+      <c r="R17" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="67.5" customHeight="1">
       <c r="A18" s="53" t="inlineStr">
@@ -2241,6 +2383,11 @@
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
+      <c r="R18" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="67.5" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
@@ -2317,6 +2464,11 @@
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
+      <c r="R19" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="53" t="inlineStr">
@@ -2388,6 +2540,11 @@
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
+      <c r="R20" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
@@ -2459,6 +2616,11 @@
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
+      <c r="R21" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="A22" s="53" t="inlineStr">
@@ -2530,6 +2692,11 @@
       <c r="Q22" s="89">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
+      </c>
+      <c r="R22" s="100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3294,9 +3461,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q62"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
@@ -5503,7 +5672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5517,7 +5686,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -5566,7 +5734,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1093,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3458,6 +3458,65 @@
       <c r="O62" s="79" t="n"/>
       <c r="P62" s="79" t="n"/>
       <c r="Q62" s="80" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EL-030</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ماندگاری حاشیه‌های اشمیت ورودی</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>پنل کالیبراسیون و برد در دسترس است</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>گام ۱: در پنل q169/q170 را مثلاً ۷۰۰/۸۰۰ بگذار و ارسال کن.
+گام ۲: از پنل بازخوانی کن.
+گام ۳: برد را ری‌استارت کن و دوباره بخوان.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>شناسه‌های ۱۶۹/۱۷۰، NVM نسخه ۱۲ با ۱۷۲ جای</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>سه دقیقه</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>مقادیر ارسال‌شده بازخوانی و پس از ری‌استارت حفظ می‌شوند</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ماندگار</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PASS: read-back و پس از ری‌استارت همان مقادیر. FAIL: پیش‌فرض برگشت یا NAK.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q62"/>

--- a/Firmware/Modules/EspLink/EspLink_Validation.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$62</definedName>
